--- a/ID601/Jig/ID601_ES/Docs/GT/ID601_Test_Doc_260922.xlsx
+++ b/ID601/Jig/ID601_ES/Docs/GT/ID601_Test_Doc_260922.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sosbi\OneDrive\바탕 화면\ID문서\Test_Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\ID601\Jig\ID601_ES\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD11AB0-9848-4EA0-A3BC-2F3A1185C843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB17DB25-3BC4-42FE-8BB7-F16100779E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16470" yWindow="4370" windowWidth="20690" windowHeight="12190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register_Table" sheetId="2" r:id="rId1"/>
@@ -3829,6 +3829,21 @@
     <xf numFmtId="180" fontId="32" fillId="0" borderId="30" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3842,12 +3857,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3961,13 +3970,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3979,13 +3985,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4030,8 +4033,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4092,21 +4107,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="30" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11331,13 +11331,13 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="208" t="s">
+      <c r="A3" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="242" t="s">
         <v>355</v>
       </c>
       <c r="D3" s="38" t="s">
@@ -11361,27 +11361,27 @@
       <c r="J3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="219" t="s">
+      <c r="K3" s="222" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="219"/>
-      <c r="M3" s="219"/>
-      <c r="N3" s="219"/>
-      <c r="O3" s="217"/>
-      <c r="P3" s="215" cm="1">
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="222"/>
+      <c r="O3" s="220"/>
+      <c r="P3" s="218" cm="1">
         <f t="array" ref="P3">SUMPRODUCT($D4:$O4, 2^(COLUMN($O4)-COLUMN($D4:$O4)))</f>
         <v>256</v>
       </c>
-      <c r="Q3" s="187" t="str">
+      <c r="Q3" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P3, 3)</f>
         <v>0x100</v>
       </c>
-      <c r="R3" s="183"/>
+      <c r="R3" s="178"/>
     </row>
     <row r="4" spans="1:18" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="240"/>
-      <c r="B4" s="211"/>
-      <c r="C4" s="181"/>
+      <c r="A4" s="241"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="186"/>
       <c r="D4" s="54">
         <v>0</v>
       </c>
@@ -11418,28 +11418,28 @@
       <c r="O4" s="53">
         <v>0</v>
       </c>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="188"/>
-      <c r="R4" s="184"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="191"/>
+      <c r="R4" s="179"/>
     </row>
     <row r="5" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="211" t="s">
         <v>349</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="213" t="s">
         <v>348</v>
       </c>
-      <c r="C5" s="180" t="s">
+      <c r="C5" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="222" t="s">
+      <c r="D5" s="231" t="s">
         <v>347</v>
       </c>
-      <c r="E5" s="219"/>
-      <c r="F5" s="219"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="219"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
       <c r="J5" s="32" t="s">
         <v>346</v>
       </c>
@@ -11458,20 +11458,20 @@
       <c r="O5" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="P5" s="215" cm="1">
+      <c r="P5" s="218" cm="1">
         <f t="array" ref="P5">SUMPRODUCT($D6:$O6, 2^(COLUMN($O6)-COLUMN($D6:$O6)))</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="191" t="str">
+      <c r="Q5" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P5, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R5" s="183"/>
+      <c r="R5" s="178"/>
     </row>
     <row r="6" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="209"/>
-      <c r="B6" s="211"/>
-      <c r="C6" s="181"/>
+      <c r="A6" s="212"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="186"/>
       <c r="D6" s="20">
         <v>0</v>
       </c>
@@ -11508,18 +11508,18 @@
       <c r="O6" s="60">
         <v>0</v>
       </c>
-      <c r="P6" s="216"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="184"/>
+      <c r="P6" s="219"/>
+      <c r="Q6" s="195"/>
+      <c r="R6" s="179"/>
     </row>
     <row r="7" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="208" t="s">
+      <c r="A7" s="211" t="s">
         <v>340</v>
       </c>
-      <c r="B7" s="210" t="s">
+      <c r="B7" s="213" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="180" t="s">
+      <c r="C7" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="34" t="s">
@@ -11540,28 +11540,28 @@
       <c r="I7" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="217" t="s">
+      <c r="J7" s="220" t="s">
         <v>339</v>
       </c>
-      <c r="K7" s="213"/>
-      <c r="L7" s="213"/>
-      <c r="M7" s="213"/>
-      <c r="N7" s="213"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="215" cm="1">
+      <c r="K7" s="216"/>
+      <c r="L7" s="216"/>
+      <c r="M7" s="216"/>
+      <c r="N7" s="216"/>
+      <c r="O7" s="217"/>
+      <c r="P7" s="218" cm="1">
         <f t="array" ref="P7">SUMPRODUCT($D8:$O8, 2^(COLUMN($O8)-COLUMN($D8:$O8)))</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="191" t="str">
+      <c r="Q7" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P7, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R7" s="183"/>
+      <c r="R7" s="178"/>
     </row>
     <row r="8" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="209"/>
-      <c r="B8" s="211"/>
-      <c r="C8" s="181"/>
+      <c r="A8" s="212"/>
+      <c r="B8" s="214"/>
+      <c r="C8" s="186"/>
       <c r="D8" s="30">
         <v>0</v>
       </c>
@@ -11598,50 +11598,50 @@
       <c r="O8" s="60">
         <v>0</v>
       </c>
-      <c r="P8" s="216"/>
-      <c r="Q8" s="192"/>
-      <c r="R8" s="184"/>
+      <c r="P8" s="219"/>
+      <c r="Q8" s="195"/>
+      <c r="R8" s="179"/>
     </row>
     <row r="9" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="182" t="s">
         <v>338</v>
       </c>
-      <c r="B9" s="210" t="s">
+      <c r="B9" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="267" t="s">
+      <c r="C9" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="212" t="s">
+      <c r="D9" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="213"/>
-      <c r="F9" s="213"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="217" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="231"/>
+      <c r="H9" s="220" t="s">
         <v>524</v>
       </c>
-      <c r="I9" s="213"/>
-      <c r="J9" s="213"/>
-      <c r="K9" s="213"/>
-      <c r="L9" s="213"/>
-      <c r="M9" s="213"/>
-      <c r="N9" s="213"/>
-      <c r="O9" s="214"/>
-      <c r="P9" s="189" cm="1">
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
+      <c r="M9" s="216"/>
+      <c r="N9" s="216"/>
+      <c r="O9" s="217"/>
+      <c r="P9" s="192" cm="1">
         <f t="array" ref="P9">SUMPRODUCT($D10:$O10, 2^(COLUMN($O10)-COLUMN($D10:$O10)))</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="191" t="str">
+      <c r="Q9" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P9, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R9" s="183"/>
+      <c r="R9" s="178"/>
     </row>
     <row r="10" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="229"/>
-      <c r="B10" s="211"/>
-      <c r="C10" s="268"/>
+      <c r="A10" s="181"/>
+      <c r="B10" s="214"/>
+      <c r="C10" s="226"/>
       <c r="D10" s="45">
         <v>0</v>
       </c>
@@ -11678,50 +11678,50 @@
       <c r="O10" s="42">
         <v>0</v>
       </c>
-      <c r="P10" s="190"/>
-      <c r="Q10" s="192"/>
-      <c r="R10" s="184"/>
+      <c r="P10" s="193"/>
+      <c r="Q10" s="195"/>
+      <c r="R10" s="179"/>
     </row>
     <row r="11" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="230" t="s">
         <v>336</v>
       </c>
-      <c r="B11" s="210" t="s">
+      <c r="B11" s="213" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="267" t="s">
+      <c r="C11" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="269" t="s">
+      <c r="D11" s="250" t="s">
         <v>335</v>
       </c>
-      <c r="E11" s="266"/>
-      <c r="F11" s="266"/>
-      <c r="G11" s="266"/>
-      <c r="H11" s="266"/>
-      <c r="I11" s="266"/>
-      <c r="J11" s="266"/>
-      <c r="K11" s="266"/>
-      <c r="L11" s="266" t="s">
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248" t="s">
         <v>525</v>
       </c>
-      <c r="M11" s="266"/>
-      <c r="N11" s="266"/>
-      <c r="O11" s="270"/>
-      <c r="P11" s="189" cm="1">
+      <c r="M11" s="248"/>
+      <c r="N11" s="248"/>
+      <c r="O11" s="249"/>
+      <c r="P11" s="192" cm="1">
         <f t="array" ref="P11">SUMPRODUCT($D12:$O12, 2^(COLUMN($O12)-COLUMN($D12:$O12)))</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="191" t="str">
+      <c r="Q11" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P11, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R11" s="183"/>
+      <c r="R11" s="178"/>
     </row>
     <row r="12" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="229"/>
-      <c r="B12" s="211"/>
-      <c r="C12" s="268"/>
+      <c r="A12" s="181"/>
+      <c r="B12" s="214"/>
+      <c r="C12" s="226"/>
       <c r="D12" s="45">
         <v>0</v>
       </c>
@@ -11758,18 +11758,18 @@
       <c r="O12" s="42">
         <v>0</v>
       </c>
-      <c r="P12" s="190"/>
-      <c r="Q12" s="192"/>
-      <c r="R12" s="184"/>
+      <c r="P12" s="193"/>
+      <c r="Q12" s="195"/>
+      <c r="R12" s="179"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A13" s="208" t="s">
+      <c r="A13" s="211" t="s">
         <v>334</v>
       </c>
-      <c r="B13" s="210" t="s">
+      <c r="B13" s="213" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="267" t="s">
+      <c r="C13" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="39" t="s">
@@ -11808,20 +11808,20 @@
       <c r="O13" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="P13" s="189" cm="1">
+      <c r="P13" s="192" cm="1">
         <f t="array" ref="P13">SUMPRODUCT($D14:$O14, 2^(COLUMN($O14)-COLUMN($D14:$O14)))</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="191" t="str">
+      <c r="Q13" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P13, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R13" s="183"/>
+      <c r="R13" s="178"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="209"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="268"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="226"/>
       <c r="D14" s="36">
         <v>0</v>
       </c>
@@ -11858,31 +11858,31 @@
       <c r="O14" s="29">
         <v>0</v>
       </c>
-      <c r="P14" s="190"/>
-      <c r="Q14" s="192"/>
-      <c r="R14" s="184"/>
+      <c r="P14" s="193"/>
+      <c r="Q14" s="195"/>
+      <c r="R14" s="179"/>
     </row>
     <row r="15" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="211" t="s">
         <v>321</v>
       </c>
-      <c r="B15" s="210" t="s">
+      <c r="B15" s="213" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="267" t="s">
+      <c r="C15" s="225" t="s">
         <v>320</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="217" t="s">
+      <c r="E15" s="220" t="s">
         <v>319</v>
       </c>
-      <c r="F15" s="222"/>
-      <c r="G15" s="217" t="s">
+      <c r="F15" s="231"/>
+      <c r="G15" s="220" t="s">
         <v>318</v>
       </c>
-      <c r="H15" s="222"/>
+      <c r="H15" s="231"/>
       <c r="I15" s="32" t="s">
         <v>317</v>
       </c>
@@ -11904,20 +11904,20 @@
       <c r="O15" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="P15" s="189" cm="1">
+      <c r="P15" s="192" cm="1">
         <f t="array" ref="P15">SUMPRODUCT($D16:$O16, 2^(COLUMN($O16)-COLUMN($D16:$O16)))</f>
         <v>60</v>
       </c>
-      <c r="Q15" s="187" t="str">
+      <c r="Q15" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P15, 3)</f>
         <v>0x03C</v>
       </c>
-      <c r="R15" s="183"/>
+      <c r="R15" s="178"/>
     </row>
     <row r="16" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="209"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="268"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="226"/>
       <c r="D16" s="59">
         <v>0</v>
       </c>
@@ -11954,18 +11954,18 @@
       <c r="O16" s="90">
         <v>0</v>
       </c>
-      <c r="P16" s="190"/>
-      <c r="Q16" s="188"/>
-      <c r="R16" s="184"/>
+      <c r="P16" s="193"/>
+      <c r="Q16" s="191"/>
+      <c r="R16" s="179"/>
     </row>
     <row r="17" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="228" t="s">
+      <c r="A17" s="182" t="s">
         <v>310</v>
       </c>
-      <c r="B17" s="210" t="s">
+      <c r="B17" s="213" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="267" t="s">
+      <c r="C17" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="41" t="s">
@@ -11977,35 +11977,35 @@
       <c r="F17" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="219" t="s">
+      <c r="G17" s="222" t="s">
         <v>309</v>
       </c>
-      <c r="H17" s="219"/>
-      <c r="I17" s="219"/>
-      <c r="J17" s="219" t="s">
+      <c r="H17" s="222"/>
+      <c r="I17" s="222"/>
+      <c r="J17" s="222" t="s">
         <v>308</v>
       </c>
-      <c r="K17" s="219"/>
-      <c r="L17" s="219"/>
-      <c r="M17" s="219" t="s">
+      <c r="K17" s="222"/>
+      <c r="L17" s="222"/>
+      <c r="M17" s="222" t="s">
         <v>307</v>
       </c>
-      <c r="N17" s="219"/>
-      <c r="O17" s="236"/>
-      <c r="P17" s="189" cm="1">
+      <c r="N17" s="222"/>
+      <c r="O17" s="237"/>
+      <c r="P17" s="192" cm="1">
         <f t="array" ref="P17">SUMPRODUCT($D18:$O18, 2^(COLUMN($O18)-COLUMN($D18:$O18)))</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="191" t="str">
+      <c r="Q17" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P17, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R17" s="183"/>
+      <c r="R17" s="178"/>
     </row>
     <row r="18" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="229"/>
-      <c r="B18" s="211"/>
-      <c r="C18" s="268"/>
+      <c r="A18" s="181"/>
+      <c r="B18" s="214"/>
+      <c r="C18" s="226"/>
       <c r="D18" s="40">
         <v>0</v>
       </c>
@@ -12042,18 +12042,18 @@
       <c r="O18" s="29">
         <v>0</v>
       </c>
-      <c r="P18" s="190"/>
-      <c r="Q18" s="192"/>
-      <c r="R18" s="184"/>
+      <c r="P18" s="193"/>
+      <c r="Q18" s="195"/>
+      <c r="R18" s="179"/>
     </row>
     <row r="19" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="230" t="s">
         <v>306</v>
       </c>
-      <c r="B19" s="210" t="s">
+      <c r="B19" s="213" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="267" t="s">
+      <c r="C19" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="41" t="s">
@@ -12065,35 +12065,35 @@
       <c r="F19" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G19" s="219" t="s">
+      <c r="G19" s="222" t="s">
         <v>305</v>
       </c>
-      <c r="H19" s="219"/>
-      <c r="I19" s="219"/>
-      <c r="J19" s="219" t="s">
+      <c r="H19" s="222"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="222" t="s">
         <v>304</v>
       </c>
-      <c r="K19" s="219"/>
-      <c r="L19" s="219"/>
-      <c r="M19" s="219" t="s">
+      <c r="K19" s="222"/>
+      <c r="L19" s="222"/>
+      <c r="M19" s="222" t="s">
         <v>303</v>
       </c>
-      <c r="N19" s="219"/>
-      <c r="O19" s="236"/>
-      <c r="P19" s="189" cm="1">
+      <c r="N19" s="222"/>
+      <c r="O19" s="237"/>
+      <c r="P19" s="192" cm="1">
         <f t="array" ref="P19">SUMPRODUCT($D20:$O20, 2^(COLUMN($O20)-COLUMN($D20:$O20)))</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="191" t="str">
+      <c r="Q19" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P19, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R19" s="183"/>
+      <c r="R19" s="178"/>
     </row>
     <row r="20" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="229"/>
-      <c r="B20" s="211"/>
-      <c r="C20" s="268"/>
+      <c r="A20" s="181"/>
+      <c r="B20" s="214"/>
+      <c r="C20" s="226"/>
       <c r="D20" s="59">
         <v>0</v>
       </c>
@@ -12130,18 +12130,18 @@
       <c r="O20" s="42">
         <v>0</v>
       </c>
-      <c r="P20" s="190"/>
-      <c r="Q20" s="192"/>
-      <c r="R20" s="184"/>
+      <c r="P20" s="193"/>
+      <c r="Q20" s="195"/>
+      <c r="R20" s="179"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A21" s="208" t="s">
+      <c r="A21" s="211" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="210" t="s">
+      <c r="B21" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="267" t="s">
+      <c r="C21" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="41" t="s">
@@ -12180,20 +12180,20 @@
       <c r="O21" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="P21" s="189" cm="1">
+      <c r="P21" s="192" cm="1">
         <f t="array" ref="P21">SUMPRODUCT($D22:$O22, 2^(COLUMN($O22)-COLUMN($D22:$O22)))</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="191" t="str">
+      <c r="Q21" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P21, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R21" s="183"/>
+      <c r="R21" s="178"/>
     </row>
     <row r="22" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="209"/>
-      <c r="B22" s="211"/>
-      <c r="C22" s="268"/>
+      <c r="A22" s="212"/>
+      <c r="B22" s="214"/>
+      <c r="C22" s="226"/>
       <c r="D22" s="40">
         <v>0</v>
       </c>
@@ -12230,18 +12230,18 @@
       <c r="O22" s="29">
         <v>0</v>
       </c>
-      <c r="P22" s="190"/>
-      <c r="Q22" s="192"/>
-      <c r="R22" s="184"/>
+      <c r="P22" s="193"/>
+      <c r="Q22" s="195"/>
+      <c r="R22" s="179"/>
     </row>
     <row r="23" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A23" s="208" t="s">
+      <c r="A23" s="211" t="s">
         <v>296</v>
       </c>
-      <c r="B23" s="210" t="s">
+      <c r="B23" s="213" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="267" t="s">
+      <c r="C23" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="39" t="s">
@@ -12280,20 +12280,20 @@
       <c r="O23" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="P23" s="189" cm="1">
+      <c r="P23" s="192" cm="1">
         <f t="array" ref="P23">SUMPRODUCT($D24:$O24, 2^(COLUMN($O24)-COLUMN($D24:$O24)))</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="191" t="str">
+      <c r="Q23" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P23, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R23" s="183"/>
+      <c r="R23" s="178"/>
     </row>
     <row r="24" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="209"/>
-      <c r="B24" s="211"/>
-      <c r="C24" s="268"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="214"/>
+      <c r="C24" s="226"/>
       <c r="D24" s="45">
         <v>0</v>
       </c>
@@ -12330,18 +12330,18 @@
       <c r="O24" s="42">
         <v>0</v>
       </c>
-      <c r="P24" s="190"/>
-      <c r="Q24" s="192"/>
-      <c r="R24" s="184"/>
+      <c r="P24" s="193"/>
+      <c r="Q24" s="195"/>
+      <c r="R24" s="179"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A25" s="208" t="s">
+      <c r="A25" s="211" t="s">
         <v>283</v>
       </c>
-      <c r="B25" s="210" t="s">
+      <c r="B25" s="213" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="267" t="s">
+      <c r="C25" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="39" t="s">
@@ -12380,20 +12380,20 @@
       <c r="O25" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="P25" s="189" cm="1">
+      <c r="P25" s="192" cm="1">
         <f t="array" ref="P25">SUMPRODUCT($D26:$O26, 2^(COLUMN($O26)-COLUMN($D26:$O26)))</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="191" t="str">
+      <c r="Q25" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P25, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R25" s="183"/>
+      <c r="R25" s="178"/>
     </row>
     <row r="26" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="209"/>
-      <c r="B26" s="211"/>
-      <c r="C26" s="268"/>
+      <c r="A26" s="212"/>
+      <c r="B26" s="214"/>
+      <c r="C26" s="226"/>
       <c r="D26" s="45">
         <v>0</v>
       </c>
@@ -12430,18 +12430,18 @@
       <c r="O26" s="42">
         <v>0</v>
       </c>
-      <c r="P26" s="190"/>
-      <c r="Q26" s="192"/>
-      <c r="R26" s="184"/>
+      <c r="P26" s="193"/>
+      <c r="Q26" s="195"/>
+      <c r="R26" s="179"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A27" s="208" t="s">
+      <c r="A27" s="211" t="s">
         <v>270</v>
       </c>
-      <c r="B27" s="210" t="s">
+      <c r="B27" s="213" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="267" t="s">
+      <c r="C27" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="39" t="s">
@@ -12480,20 +12480,20 @@
       <c r="O27" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="P27" s="189" cm="1">
+      <c r="P27" s="192" cm="1">
         <f t="array" ref="P27">SUMPRODUCT($D28:$O28, 2^(COLUMN($O28)-COLUMN($D28:$O28)))</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="191" t="str">
+      <c r="Q27" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P27, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R27" s="183"/>
+      <c r="R27" s="178"/>
     </row>
     <row r="28" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="209"/>
-      <c r="B28" s="211"/>
-      <c r="C28" s="268"/>
+      <c r="A28" s="212"/>
+      <c r="B28" s="214"/>
+      <c r="C28" s="226"/>
       <c r="D28" s="36">
         <v>0</v>
       </c>
@@ -12530,54 +12530,54 @@
       <c r="O28" s="29">
         <v>0</v>
       </c>
-      <c r="P28" s="190"/>
-      <c r="Q28" s="192"/>
-      <c r="R28" s="184"/>
+      <c r="P28" s="193"/>
+      <c r="Q28" s="195"/>
+      <c r="R28" s="179"/>
     </row>
     <row r="29" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="208" t="s">
+      <c r="A29" s="211" t="s">
         <v>257</v>
       </c>
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="213" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="267" t="s">
+      <c r="C29" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="212" t="s">
+      <c r="D29" s="215" t="s">
         <v>256</v>
       </c>
-      <c r="E29" s="213"/>
-      <c r="F29" s="213"/>
-      <c r="G29" s="222"/>
-      <c r="H29" s="217" t="s">
+      <c r="E29" s="216"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="231"/>
+      <c r="H29" s="220" t="s">
         <v>255</v>
       </c>
-      <c r="I29" s="213"/>
-      <c r="J29" s="213"/>
-      <c r="K29" s="222"/>
-      <c r="L29" s="217" t="s">
+      <c r="I29" s="216"/>
+      <c r="J29" s="216"/>
+      <c r="K29" s="231"/>
+      <c r="L29" s="220" t="s">
         <v>254</v>
       </c>
-      <c r="M29" s="213"/>
-      <c r="N29" s="213"/>
-      <c r="O29" s="214"/>
-      <c r="P29" s="189" cm="1">
+      <c r="M29" s="216"/>
+      <c r="N29" s="216"/>
+      <c r="O29" s="217"/>
+      <c r="P29" s="192" cm="1">
         <f t="array" ref="P29">SUMPRODUCT($D30:$O30, 2^(COLUMN($O30)-COLUMN($D30:$O30)))</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="191" t="str">
+      <c r="Q29" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P29, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R29" s="228" t="s">
+      <c r="R29" s="182" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="209"/>
-      <c r="B30" s="211"/>
-      <c r="C30" s="268"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="214"/>
+      <c r="C30" s="226"/>
       <c r="D30" s="36">
         <v>0</v>
       </c>
@@ -12614,48 +12614,48 @@
       <c r="O30" s="29">
         <v>0</v>
       </c>
-      <c r="P30" s="190"/>
-      <c r="Q30" s="192"/>
-      <c r="R30" s="229"/>
+      <c r="P30" s="193"/>
+      <c r="Q30" s="195"/>
+      <c r="R30" s="181"/>
     </row>
     <row r="31" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="228" t="s">
+      <c r="A31" s="182" t="s">
         <v>252</v>
       </c>
-      <c r="B31" s="210" t="s">
+      <c r="B31" s="213" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="267" t="s">
+      <c r="C31" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="212" t="s">
+      <c r="D31" s="215" t="s">
         <v>251</v>
       </c>
-      <c r="E31" s="213"/>
-      <c r="F31" s="213"/>
-      <c r="G31" s="213"/>
-      <c r="H31" s="213"/>
-      <c r="I31" s="213"/>
-      <c r="J31" s="213"/>
-      <c r="K31" s="213"/>
-      <c r="L31" s="213"/>
-      <c r="M31" s="213"/>
-      <c r="N31" s="213"/>
-      <c r="O31" s="214"/>
-      <c r="P31" s="189" cm="1">
+      <c r="E31" s="216"/>
+      <c r="F31" s="216"/>
+      <c r="G31" s="216"/>
+      <c r="H31" s="216"/>
+      <c r="I31" s="216"/>
+      <c r="J31" s="216"/>
+      <c r="K31" s="216"/>
+      <c r="L31" s="216"/>
+      <c r="M31" s="216"/>
+      <c r="N31" s="216"/>
+      <c r="O31" s="217"/>
+      <c r="P31" s="192" cm="1">
         <f t="array" ref="P31">SUMPRODUCT($D32:$O32, 2^(COLUMN($O32)-COLUMN($D32:$O32)))</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="191" t="str">
+      <c r="Q31" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P31, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R31" s="183"/>
+      <c r="R31" s="178"/>
     </row>
     <row r="32" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="229"/>
-      <c r="B32" s="211"/>
-      <c r="C32" s="268"/>
+      <c r="A32" s="181"/>
+      <c r="B32" s="214"/>
+      <c r="C32" s="226"/>
       <c r="D32" s="36">
         <v>0</v>
       </c>
@@ -12692,48 +12692,48 @@
       <c r="O32" s="29">
         <v>0</v>
       </c>
-      <c r="P32" s="190"/>
-      <c r="Q32" s="192"/>
-      <c r="R32" s="184"/>
+      <c r="P32" s="193"/>
+      <c r="Q32" s="195"/>
+      <c r="R32" s="179"/>
     </row>
     <row r="33" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="228" t="s">
+      <c r="A33" s="182" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="210" t="s">
+      <c r="B33" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="267" t="s">
+      <c r="C33" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="212" t="s">
+      <c r="D33" s="215" t="s">
         <v>249</v>
       </c>
-      <c r="E33" s="213"/>
-      <c r="F33" s="213"/>
-      <c r="G33" s="213"/>
-      <c r="H33" s="213"/>
-      <c r="I33" s="213"/>
-      <c r="J33" s="213"/>
-      <c r="K33" s="213"/>
-      <c r="L33" s="213"/>
-      <c r="M33" s="213"/>
-      <c r="N33" s="213"/>
-      <c r="O33" s="214"/>
-      <c r="P33" s="189" cm="1">
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="216"/>
+      <c r="I33" s="216"/>
+      <c r="J33" s="216"/>
+      <c r="K33" s="216"/>
+      <c r="L33" s="216"/>
+      <c r="M33" s="216"/>
+      <c r="N33" s="216"/>
+      <c r="O33" s="217"/>
+      <c r="P33" s="192" cm="1">
         <f t="array" ref="P33">SUMPRODUCT($D34:$O34, 2^(COLUMN($O34)-COLUMN($D34:$O34)))</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="191" t="str">
+      <c r="Q33" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P33, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R33" s="183"/>
+      <c r="R33" s="178"/>
     </row>
     <row r="34" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="229"/>
-      <c r="B34" s="211"/>
-      <c r="C34" s="268"/>
+      <c r="A34" s="181"/>
+      <c r="B34" s="214"/>
+      <c r="C34" s="226"/>
       <c r="D34" s="36">
         <v>0</v>
       </c>
@@ -12770,48 +12770,48 @@
       <c r="O34" s="29">
         <v>0</v>
       </c>
-      <c r="P34" s="190"/>
-      <c r="Q34" s="192"/>
-      <c r="R34" s="184"/>
+      <c r="P34" s="193"/>
+      <c r="Q34" s="195"/>
+      <c r="R34" s="179"/>
     </row>
     <row r="35" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="230" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="210" t="s">
+      <c r="B35" s="213" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="267" t="s">
+      <c r="C35" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="212" t="s">
+      <c r="D35" s="215" t="s">
         <v>247</v>
       </c>
-      <c r="E35" s="213"/>
-      <c r="F35" s="213"/>
-      <c r="G35" s="213"/>
-      <c r="H35" s="213"/>
-      <c r="I35" s="213"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="213"/>
-      <c r="M35" s="213"/>
-      <c r="N35" s="213"/>
-      <c r="O35" s="214"/>
-      <c r="P35" s="189" cm="1">
+      <c r="E35" s="216"/>
+      <c r="F35" s="216"/>
+      <c r="G35" s="216"/>
+      <c r="H35" s="216"/>
+      <c r="I35" s="216"/>
+      <c r="J35" s="216"/>
+      <c r="K35" s="216"/>
+      <c r="L35" s="216"/>
+      <c r="M35" s="216"/>
+      <c r="N35" s="216"/>
+      <c r="O35" s="217"/>
+      <c r="P35" s="192" cm="1">
         <f t="array" ref="P35">SUMPRODUCT($D36:$O36, 2^(COLUMN($O36)-COLUMN($D36:$O36)))</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="191" t="str">
+      <c r="Q35" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P35, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R35" s="183"/>
+      <c r="R35" s="178"/>
     </row>
     <row r="36" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="229"/>
-      <c r="B36" s="211"/>
-      <c r="C36" s="268"/>
+      <c r="A36" s="181"/>
+      <c r="B36" s="214"/>
+      <c r="C36" s="226"/>
       <c r="D36" s="45">
         <v>0</v>
       </c>
@@ -12848,18 +12848,18 @@
       <c r="O36" s="42">
         <v>0</v>
       </c>
-      <c r="P36" s="190"/>
-      <c r="Q36" s="192"/>
-      <c r="R36" s="184"/>
+      <c r="P36" s="193"/>
+      <c r="Q36" s="195"/>
+      <c r="R36" s="179"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A37" s="208" t="s">
+      <c r="A37" s="211" t="s">
         <v>246</v>
       </c>
-      <c r="B37" s="210" t="s">
+      <c r="B37" s="213" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="267" t="s">
+      <c r="C37" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="39" t="s">
@@ -12898,20 +12898,20 @@
       <c r="O37" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="P37" s="189" cm="1">
+      <c r="P37" s="192" cm="1">
         <f t="array" ref="P37">SUMPRODUCT($D38:$O38, 2^(COLUMN($O38)-COLUMN($D38:$O38)))</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="191" t="str">
+      <c r="Q37" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P37, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R37" s="183"/>
+      <c r="R37" s="178"/>
     </row>
     <row r="38" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="209"/>
-      <c r="B38" s="211"/>
-      <c r="C38" s="268"/>
+      <c r="A38" s="212"/>
+      <c r="B38" s="214"/>
+      <c r="C38" s="226"/>
       <c r="D38" s="36">
         <v>0</v>
       </c>
@@ -12948,18 +12948,18 @@
       <c r="O38" s="29">
         <v>0</v>
       </c>
-      <c r="P38" s="190"/>
-      <c r="Q38" s="192"/>
-      <c r="R38" s="184"/>
+      <c r="P38" s="193"/>
+      <c r="Q38" s="195"/>
+      <c r="R38" s="179"/>
     </row>
     <row r="39" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="228" t="s">
+      <c r="A39" s="182" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="210" t="s">
+      <c r="B39" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="267" t="s">
+      <c r="C39" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="41" t="s">
@@ -12968,34 +12968,34 @@
       <c r="E39" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F39" s="217" t="s">
+      <c r="F39" s="220" t="s">
         <v>232</v>
       </c>
-      <c r="G39" s="213"/>
-      <c r="H39" s="213"/>
-      <c r="I39" s="213"/>
-      <c r="J39" s="222"/>
-      <c r="K39" s="219" t="s">
+      <c r="G39" s="216"/>
+      <c r="H39" s="216"/>
+      <c r="I39" s="216"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="222" t="s">
         <v>231</v>
       </c>
-      <c r="L39" s="219"/>
-      <c r="M39" s="219"/>
-      <c r="N39" s="219"/>
-      <c r="O39" s="236"/>
-      <c r="P39" s="189" cm="1">
+      <c r="L39" s="222"/>
+      <c r="M39" s="222"/>
+      <c r="N39" s="222"/>
+      <c r="O39" s="237"/>
+      <c r="P39" s="192" cm="1">
         <f t="array" ref="P39">SUMPRODUCT($D40:$O40, 2^(COLUMN($O40)-COLUMN($D40:$O40)))</f>
         <v>0</v>
       </c>
-      <c r="Q39" s="191" t="str">
+      <c r="Q39" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P39, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R39" s="183"/>
+      <c r="R39" s="178"/>
     </row>
     <row r="40" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="229"/>
-      <c r="B40" s="211"/>
-      <c r="C40" s="268"/>
+      <c r="A40" s="181"/>
+      <c r="B40" s="214"/>
+      <c r="C40" s="226"/>
       <c r="D40" s="40">
         <v>0</v>
       </c>
@@ -13032,18 +13032,18 @@
       <c r="O40" s="29">
         <v>0</v>
       </c>
-      <c r="P40" s="190"/>
-      <c r="Q40" s="192"/>
-      <c r="R40" s="184"/>
+      <c r="P40" s="193"/>
+      <c r="Q40" s="195"/>
+      <c r="R40" s="179"/>
     </row>
     <row r="41" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="228" t="s">
+      <c r="A41" s="182" t="s">
         <v>230</v>
       </c>
-      <c r="B41" s="210" t="s">
+      <c r="B41" s="213" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="267" t="s">
+      <c r="C41" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="41" t="s">
@@ -13052,34 +13052,34 @@
       <c r="E41" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F41" s="217" t="s">
+      <c r="F41" s="220" t="s">
         <v>229</v>
       </c>
-      <c r="G41" s="213"/>
-      <c r="H41" s="213"/>
-      <c r="I41" s="213"/>
-      <c r="J41" s="222"/>
-      <c r="K41" s="219" t="s">
+      <c r="G41" s="216"/>
+      <c r="H41" s="216"/>
+      <c r="I41" s="216"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="222" t="s">
         <v>228</v>
       </c>
-      <c r="L41" s="219"/>
-      <c r="M41" s="219"/>
-      <c r="N41" s="219"/>
-      <c r="O41" s="236"/>
-      <c r="P41" s="189" cm="1">
+      <c r="L41" s="222"/>
+      <c r="M41" s="222"/>
+      <c r="N41" s="222"/>
+      <c r="O41" s="237"/>
+      <c r="P41" s="192" cm="1">
         <f t="array" ref="P41">SUMPRODUCT($D42:$O42, 2^(COLUMN($O42)-COLUMN($D42:$O42)))</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="191" t="str">
+      <c r="Q41" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P41, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R41" s="183"/>
+      <c r="R41" s="178"/>
     </row>
     <row r="42" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="229"/>
-      <c r="B42" s="211"/>
-      <c r="C42" s="268"/>
+      <c r="A42" s="181"/>
+      <c r="B42" s="214"/>
+      <c r="C42" s="226"/>
       <c r="D42" s="40">
         <v>0</v>
       </c>
@@ -13116,18 +13116,18 @@
       <c r="O42" s="29">
         <v>0</v>
       </c>
-      <c r="P42" s="190"/>
-      <c r="Q42" s="192"/>
-      <c r="R42" s="184"/>
+      <c r="P42" s="193"/>
+      <c r="Q42" s="195"/>
+      <c r="R42" s="179"/>
     </row>
     <row r="43" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="228" t="s">
+      <c r="A43" s="182" t="s">
         <v>227</v>
       </c>
-      <c r="B43" s="210" t="s">
+      <c r="B43" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="267" t="s">
+      <c r="C43" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="41" t="s">
@@ -13136,34 +13136,34 @@
       <c r="E43" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F43" s="217" t="s">
+      <c r="F43" s="220" t="s">
         <v>226</v>
       </c>
-      <c r="G43" s="213"/>
-      <c r="H43" s="213"/>
-      <c r="I43" s="213"/>
-      <c r="J43" s="222"/>
-      <c r="K43" s="219" t="s">
+      <c r="G43" s="216"/>
+      <c r="H43" s="216"/>
+      <c r="I43" s="216"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="222" t="s">
         <v>225</v>
       </c>
-      <c r="L43" s="219"/>
-      <c r="M43" s="219"/>
-      <c r="N43" s="219"/>
-      <c r="O43" s="236"/>
-      <c r="P43" s="189" cm="1">
+      <c r="L43" s="222"/>
+      <c r="M43" s="222"/>
+      <c r="N43" s="222"/>
+      <c r="O43" s="237"/>
+      <c r="P43" s="192" cm="1">
         <f t="array" ref="P43">SUMPRODUCT($D44:$O44, 2^(COLUMN($O44)-COLUMN($D44:$O44)))</f>
         <v>0</v>
       </c>
-      <c r="Q43" s="191" t="str">
+      <c r="Q43" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P43, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R43" s="183"/>
+      <c r="R43" s="178"/>
     </row>
     <row r="44" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="229"/>
-      <c r="B44" s="211"/>
-      <c r="C44" s="268"/>
+      <c r="A44" s="181"/>
+      <c r="B44" s="214"/>
+      <c r="C44" s="226"/>
       <c r="D44" s="40">
         <v>0</v>
       </c>
@@ -13200,18 +13200,18 @@
       <c r="O44" s="29">
         <v>0</v>
       </c>
-      <c r="P44" s="190"/>
-      <c r="Q44" s="192"/>
-      <c r="R44" s="184"/>
+      <c r="P44" s="193"/>
+      <c r="Q44" s="195"/>
+      <c r="R44" s="179"/>
     </row>
     <row r="45" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="228" t="s">
+      <c r="A45" s="182" t="s">
         <v>224</v>
       </c>
-      <c r="B45" s="210" t="s">
+      <c r="B45" s="213" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="267" t="s">
+      <c r="C45" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="41" t="s">
@@ -13220,34 +13220,34 @@
       <c r="E45" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F45" s="217" t="s">
+      <c r="F45" s="220" t="s">
         <v>223</v>
       </c>
-      <c r="G45" s="213"/>
-      <c r="H45" s="213"/>
-      <c r="I45" s="213"/>
-      <c r="J45" s="222"/>
-      <c r="K45" s="219" t="s">
+      <c r="G45" s="216"/>
+      <c r="H45" s="216"/>
+      <c r="I45" s="216"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="222" t="s">
         <v>222</v>
       </c>
-      <c r="L45" s="219"/>
-      <c r="M45" s="219"/>
-      <c r="N45" s="219"/>
-      <c r="O45" s="236"/>
-      <c r="P45" s="189" cm="1">
+      <c r="L45" s="222"/>
+      <c r="M45" s="222"/>
+      <c r="N45" s="222"/>
+      <c r="O45" s="237"/>
+      <c r="P45" s="192" cm="1">
         <f t="array" ref="P45">SUMPRODUCT($D46:$O46, 2^(COLUMN($O46)-COLUMN($D46:$O46)))</f>
         <v>0</v>
       </c>
-      <c r="Q45" s="191" t="str">
+      <c r="Q45" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P45, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R45" s="183"/>
+      <c r="R45" s="178"/>
     </row>
     <row r="46" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="229"/>
-      <c r="B46" s="211"/>
-      <c r="C46" s="268"/>
+      <c r="A46" s="181"/>
+      <c r="B46" s="214"/>
+      <c r="C46" s="226"/>
       <c r="D46" s="40">
         <v>0</v>
       </c>
@@ -13284,18 +13284,18 @@
       <c r="O46" s="29">
         <v>0</v>
       </c>
-      <c r="P46" s="190"/>
-      <c r="Q46" s="192"/>
-      <c r="R46" s="184"/>
+      <c r="P46" s="193"/>
+      <c r="Q46" s="195"/>
+      <c r="R46" s="179"/>
     </row>
     <row r="47" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="228" t="s">
+      <c r="A47" s="182" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="210" t="s">
+      <c r="B47" s="213" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="267" t="s">
+      <c r="C47" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="41" t="s">
@@ -13304,34 +13304,34 @@
       <c r="E47" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F47" s="217" t="s">
+      <c r="F47" s="220" t="s">
         <v>220</v>
       </c>
-      <c r="G47" s="213"/>
-      <c r="H47" s="213"/>
-      <c r="I47" s="213"/>
-      <c r="J47" s="222"/>
-      <c r="K47" s="219" t="s">
+      <c r="G47" s="216"/>
+      <c r="H47" s="216"/>
+      <c r="I47" s="216"/>
+      <c r="J47" s="231"/>
+      <c r="K47" s="222" t="s">
         <v>219</v>
       </c>
-      <c r="L47" s="219"/>
-      <c r="M47" s="219"/>
-      <c r="N47" s="219"/>
-      <c r="O47" s="236"/>
-      <c r="P47" s="189" cm="1">
+      <c r="L47" s="222"/>
+      <c r="M47" s="222"/>
+      <c r="N47" s="222"/>
+      <c r="O47" s="237"/>
+      <c r="P47" s="192" cm="1">
         <f t="array" ref="P47">SUMPRODUCT($D48:$O48, 2^(COLUMN($O48)-COLUMN($D48:$O48)))</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="191" t="str">
+      <c r="Q47" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P47, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R47" s="183"/>
+      <c r="R47" s="178"/>
     </row>
     <row r="48" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A48" s="229"/>
-      <c r="B48" s="211"/>
-      <c r="C48" s="268"/>
+      <c r="A48" s="181"/>
+      <c r="B48" s="214"/>
+      <c r="C48" s="226"/>
       <c r="D48" s="40">
         <v>0</v>
       </c>
@@ -13368,18 +13368,18 @@
       <c r="O48" s="29">
         <v>0</v>
       </c>
-      <c r="P48" s="190"/>
-      <c r="Q48" s="192"/>
-      <c r="R48" s="184"/>
+      <c r="P48" s="193"/>
+      <c r="Q48" s="195"/>
+      <c r="R48" s="179"/>
     </row>
     <row r="49" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="230" t="s">
         <v>218</v>
       </c>
-      <c r="B49" s="210" t="s">
+      <c r="B49" s="213" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="267" t="s">
+      <c r="C49" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="41" t="s">
@@ -13388,34 +13388,34 @@
       <c r="E49" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="217" t="s">
+      <c r="F49" s="220" t="s">
         <v>217</v>
       </c>
-      <c r="G49" s="213"/>
-      <c r="H49" s="213"/>
-      <c r="I49" s="213"/>
-      <c r="J49" s="222"/>
-      <c r="K49" s="219" t="s">
+      <c r="G49" s="216"/>
+      <c r="H49" s="216"/>
+      <c r="I49" s="216"/>
+      <c r="J49" s="231"/>
+      <c r="K49" s="222" t="s">
         <v>216</v>
       </c>
-      <c r="L49" s="219"/>
-      <c r="M49" s="219"/>
-      <c r="N49" s="219"/>
-      <c r="O49" s="236"/>
-      <c r="P49" s="189" cm="1">
+      <c r="L49" s="222"/>
+      <c r="M49" s="222"/>
+      <c r="N49" s="222"/>
+      <c r="O49" s="237"/>
+      <c r="P49" s="192" cm="1">
         <f t="array" ref="P49">SUMPRODUCT($D50:$O50, 2^(COLUMN($O50)-COLUMN($D50:$O50)))</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="191" t="str">
+      <c r="Q49" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P49, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R49" s="183"/>
+      <c r="R49" s="178"/>
     </row>
     <row r="50" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="229"/>
-      <c r="B50" s="211"/>
-      <c r="C50" s="268"/>
+      <c r="A50" s="181"/>
+      <c r="B50" s="214"/>
+      <c r="C50" s="226"/>
       <c r="D50" s="40">
         <v>0</v>
       </c>
@@ -13452,18 +13452,18 @@
       <c r="O50" s="29">
         <v>0</v>
       </c>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="192"/>
-      <c r="R50" s="184"/>
+      <c r="P50" s="193"/>
+      <c r="Q50" s="195"/>
+      <c r="R50" s="179"/>
     </row>
     <row r="51" spans="1:18" ht="39" x14ac:dyDescent="0.45">
-      <c r="A51" s="208" t="s">
+      <c r="A51" s="211" t="s">
         <v>215</v>
       </c>
-      <c r="B51" s="210" t="s">
+      <c r="B51" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="267" t="s">
+      <c r="C51" s="225" t="s">
         <v>214</v>
       </c>
       <c r="D51" s="39" t="s">
@@ -13472,10 +13472,10 @@
       <c r="E51" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="F51" s="217" t="s">
+      <c r="F51" s="220" t="s">
         <v>211</v>
       </c>
-      <c r="G51" s="222"/>
+      <c r="G51" s="231"/>
       <c r="H51" s="32" t="s">
         <v>210</v>
       </c>
@@ -13500,20 +13500,20 @@
       <c r="O51" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="P51" s="189" cm="1">
+      <c r="P51" s="192" cm="1">
         <f t="array" ref="P51">SUMPRODUCT($D52:$O52, 2^(COLUMN($O52)-COLUMN($D52:$O52)))</f>
         <v>799</v>
       </c>
-      <c r="Q51" s="187" t="str">
+      <c r="Q51" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P51, 3)</f>
         <v>0x31F</v>
       </c>
-      <c r="R51" s="183"/>
+      <c r="R51" s="178"/>
     </row>
     <row r="52" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="209"/>
-      <c r="B52" s="211"/>
-      <c r="C52" s="268"/>
+      <c r="A52" s="212"/>
+      <c r="B52" s="214"/>
+      <c r="C52" s="226"/>
       <c r="D52" s="36">
         <v>0</v>
       </c>
@@ -13550,18 +13550,18 @@
       <c r="O52" s="92">
         <v>1</v>
       </c>
-      <c r="P52" s="190"/>
-      <c r="Q52" s="188"/>
-      <c r="R52" s="184"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="191"/>
+      <c r="R52" s="179"/>
     </row>
     <row r="53" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A53" s="208" t="s">
+      <c r="A53" s="211" t="s">
         <v>202</v>
       </c>
-      <c r="B53" s="210" t="s">
+      <c r="B53" s="213" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="267" t="s">
+      <c r="C53" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D53" s="39" t="s">
@@ -13600,20 +13600,20 @@
       <c r="O53" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="P53" s="189" cm="1">
+      <c r="P53" s="192" cm="1">
         <f t="array" ref="P53">SUMPRODUCT($D54:$O54, 2^(COLUMN($O54)-COLUMN($D54:$O54)))</f>
         <v>0</v>
       </c>
-      <c r="Q53" s="191" t="str">
+      <c r="Q53" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P53, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R53" s="183"/>
+      <c r="R53" s="178"/>
     </row>
     <row r="54" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A54" s="209"/>
-      <c r="B54" s="211"/>
-      <c r="C54" s="268"/>
+      <c r="A54" s="212"/>
+      <c r="B54" s="214"/>
+      <c r="C54" s="226"/>
       <c r="D54" s="36">
         <v>0</v>
       </c>
@@ -13650,18 +13650,18 @@
       <c r="O54" s="29">
         <v>0</v>
       </c>
-      <c r="P54" s="190"/>
-      <c r="Q54" s="192"/>
-      <c r="R54" s="184"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="195"/>
+      <c r="R54" s="179"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A55" s="208" t="s">
+      <c r="A55" s="211" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="210" t="s">
+      <c r="B55" s="213" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="267" t="s">
+      <c r="C55" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D55" s="57" t="s">
@@ -13685,27 +13685,27 @@
       <c r="J55" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="K55" s="225" t="s">
+      <c r="K55" s="227" t="s">
         <v>196</v>
       </c>
-      <c r="L55" s="226"/>
-      <c r="M55" s="226"/>
-      <c r="N55" s="226"/>
-      <c r="O55" s="227"/>
-      <c r="P55" s="189" cm="1">
+      <c r="L55" s="228"/>
+      <c r="M55" s="228"/>
+      <c r="N55" s="228"/>
+      <c r="O55" s="229"/>
+      <c r="P55" s="192" cm="1">
         <f t="array" ref="P55">SUMPRODUCT($D56:$O56, 2^(COLUMN($O56)-COLUMN($D56:$O56)))</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="191" t="str">
+      <c r="Q55" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P55, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R55" s="183"/>
+      <c r="R55" s="178"/>
     </row>
     <row r="56" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A56" s="209"/>
-      <c r="B56" s="211"/>
-      <c r="C56" s="268"/>
+      <c r="A56" s="212"/>
+      <c r="B56" s="214"/>
+      <c r="C56" s="226"/>
       <c r="D56" s="56">
         <v>0</v>
       </c>
@@ -13742,18 +13742,18 @@
       <c r="O56" s="21">
         <v>0</v>
       </c>
-      <c r="P56" s="190"/>
-      <c r="Q56" s="192"/>
-      <c r="R56" s="184"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="195"/>
+      <c r="R56" s="179"/>
     </row>
     <row r="57" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A57" s="208" t="s">
+      <c r="A57" s="211" t="s">
         <v>195</v>
       </c>
-      <c r="B57" s="210" t="s">
+      <c r="B57" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="267" t="s">
+      <c r="C57" s="225" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="50" t="s">
@@ -13792,20 +13792,20 @@
       <c r="O57" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="P57" s="189" cm="1">
+      <c r="P57" s="192" cm="1">
         <f t="array" ref="P57">SUMPRODUCT($D58:$O58, 2^(COLUMN($O58)-COLUMN($D58:$O58)))</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="191" t="str">
+      <c r="Q57" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P57, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R57" s="183"/>
+      <c r="R57" s="178"/>
     </row>
     <row r="58" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A58" s="209"/>
-      <c r="B58" s="211"/>
-      <c r="C58" s="268"/>
+      <c r="A58" s="212"/>
+      <c r="B58" s="214"/>
+      <c r="C58" s="226"/>
       <c r="D58" s="49">
         <v>0</v>
       </c>
@@ -13842,50 +13842,50 @@
       <c r="O58" s="21">
         <v>0</v>
       </c>
-      <c r="P58" s="190"/>
-      <c r="Q58" s="192"/>
-      <c r="R58" s="184"/>
+      <c r="P58" s="193"/>
+      <c r="Q58" s="195"/>
+      <c r="R58" s="179"/>
     </row>
     <row r="59" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="208" t="s">
+      <c r="A59" s="211" t="s">
         <v>192</v>
       </c>
-      <c r="B59" s="210" t="s">
+      <c r="B59" s="213" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="180" t="s">
+      <c r="C59" s="185" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="212" t="s">
+      <c r="D59" s="215" t="s">
         <v>190</v>
       </c>
-      <c r="E59" s="213"/>
-      <c r="F59" s="213"/>
-      <c r="G59" s="213"/>
-      <c r="H59" s="213"/>
-      <c r="I59" s="222"/>
-      <c r="J59" s="217" t="s">
+      <c r="E59" s="216"/>
+      <c r="F59" s="216"/>
+      <c r="G59" s="216"/>
+      <c r="H59" s="216"/>
+      <c r="I59" s="231"/>
+      <c r="J59" s="220" t="s">
         <v>189</v>
       </c>
-      <c r="K59" s="213"/>
-      <c r="L59" s="213"/>
-      <c r="M59" s="213"/>
-      <c r="N59" s="213"/>
-      <c r="O59" s="214"/>
-      <c r="P59" s="215" cm="1">
+      <c r="K59" s="216"/>
+      <c r="L59" s="216"/>
+      <c r="M59" s="216"/>
+      <c r="N59" s="216"/>
+      <c r="O59" s="217"/>
+      <c r="P59" s="218" cm="1">
         <f t="array" ref="P59">SUMPRODUCT($D60:$O60, 2^(COLUMN($O60)-COLUMN($D60:$O60)))</f>
         <v>792</v>
       </c>
-      <c r="Q59" s="187" t="str">
+      <c r="Q59" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P59, 3)</f>
         <v>0x318</v>
       </c>
-      <c r="R59" s="183"/>
+      <c r="R59" s="178"/>
     </row>
     <row r="60" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A60" s="209"/>
-      <c r="B60" s="211"/>
-      <c r="C60" s="181"/>
+      <c r="A60" s="212"/>
+      <c r="B60" s="214"/>
+      <c r="C60" s="186"/>
       <c r="D60" s="54">
         <v>0</v>
       </c>
@@ -13922,18 +13922,18 @@
       <c r="O60" s="53">
         <v>0</v>
       </c>
-      <c r="P60" s="216"/>
-      <c r="Q60" s="188"/>
-      <c r="R60" s="184"/>
+      <c r="P60" s="219"/>
+      <c r="Q60" s="191"/>
+      <c r="R60" s="179"/>
     </row>
     <row r="61" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="228" t="s">
+      <c r="A61" s="182" t="s">
         <v>188</v>
       </c>
-      <c r="B61" s="215" t="s">
+      <c r="B61" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="180" t="s">
+      <c r="C61" s="185" t="s">
         <v>187</v>
       </c>
       <c r="D61" s="41" t="s">
@@ -13945,31 +13945,31 @@
       <c r="F61" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="G61" s="217" t="s">
+      <c r="G61" s="220" t="s">
         <v>186</v>
       </c>
-      <c r="H61" s="213"/>
-      <c r="I61" s="213"/>
-      <c r="J61" s="213"/>
-      <c r="K61" s="213"/>
-      <c r="L61" s="213"/>
-      <c r="M61" s="213"/>
-      <c r="N61" s="213"/>
-      <c r="O61" s="214"/>
-      <c r="P61" s="215" cm="1">
+      <c r="H61" s="216"/>
+      <c r="I61" s="216"/>
+      <c r="J61" s="216"/>
+      <c r="K61" s="216"/>
+      <c r="L61" s="216"/>
+      <c r="M61" s="216"/>
+      <c r="N61" s="216"/>
+      <c r="O61" s="217"/>
+      <c r="P61" s="218" cm="1">
         <f t="array" ref="P61">SUMPRODUCT($D62:$O62, 2^(COLUMN($O62)-COLUMN($D62:$O62)))</f>
         <v>128</v>
       </c>
-      <c r="Q61" s="187" t="str">
+      <c r="Q61" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P61, 3)</f>
         <v>0x080</v>
       </c>
-      <c r="R61" s="183"/>
+      <c r="R61" s="178"/>
     </row>
     <row r="62" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="229"/>
-      <c r="B62" s="216"/>
-      <c r="C62" s="181"/>
+      <c r="A62" s="181"/>
+      <c r="B62" s="219"/>
+      <c r="C62" s="186"/>
       <c r="D62" s="40">
         <v>0</v>
       </c>
@@ -14006,18 +14006,18 @@
       <c r="O62" s="29">
         <v>0</v>
       </c>
-      <c r="P62" s="216"/>
-      <c r="Q62" s="188"/>
-      <c r="R62" s="184"/>
+      <c r="P62" s="219"/>
+      <c r="Q62" s="191"/>
+      <c r="R62" s="179"/>
     </row>
     <row r="63" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="208" t="s">
+      <c r="A63" s="211" t="s">
         <v>185</v>
       </c>
-      <c r="B63" s="210" t="s">
+      <c r="B63" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="180" t="s">
+      <c r="C63" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D63" s="52" t="s">
@@ -14026,32 +14026,32 @@
       <c r="E63" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="237" t="s">
+      <c r="F63" s="238" t="s">
         <v>184</v>
       </c>
-      <c r="G63" s="238"/>
-      <c r="H63" s="238"/>
-      <c r="I63" s="238"/>
-      <c r="J63" s="238"/>
-      <c r="K63" s="238"/>
-      <c r="L63" s="238"/>
-      <c r="M63" s="238"/>
-      <c r="N63" s="238"/>
-      <c r="O63" s="239"/>
-      <c r="P63" s="189" cm="1">
+      <c r="G63" s="239"/>
+      <c r="H63" s="239"/>
+      <c r="I63" s="239"/>
+      <c r="J63" s="239"/>
+      <c r="K63" s="239"/>
+      <c r="L63" s="239"/>
+      <c r="M63" s="239"/>
+      <c r="N63" s="239"/>
+      <c r="O63" s="240"/>
+      <c r="P63" s="192" cm="1">
         <f t="array" ref="P63">SUMPRODUCT($D64:$O64, 2^(COLUMN($O64)-COLUMN($D64:$O64)))</f>
         <v>0</v>
       </c>
-      <c r="Q63" s="191" t="str">
+      <c r="Q63" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P63, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R63" s="183"/>
+      <c r="R63" s="178"/>
     </row>
     <row r="64" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A64" s="209"/>
-      <c r="B64" s="211"/>
-      <c r="C64" s="181"/>
+      <c r="A64" s="212"/>
+      <c r="B64" s="214"/>
+      <c r="C64" s="186"/>
       <c r="D64" s="40">
         <v>0</v>
       </c>
@@ -14088,18 +14088,18 @@
       <c r="O64" s="29">
         <v>0</v>
       </c>
-      <c r="P64" s="190"/>
-      <c r="Q64" s="192"/>
-      <c r="R64" s="184"/>
+      <c r="P64" s="193"/>
+      <c r="Q64" s="195"/>
+      <c r="R64" s="179"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A65" s="208" t="s">
+      <c r="A65" s="211" t="s">
         <v>183</v>
       </c>
-      <c r="B65" s="210" t="s">
+      <c r="B65" s="213" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="180" t="s">
+      <c r="C65" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D65" s="50" t="s">
@@ -14108,32 +14108,32 @@
       <c r="E65" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F65" s="217" t="s">
+      <c r="F65" s="220" t="s">
         <v>180</v>
       </c>
-      <c r="G65" s="213"/>
-      <c r="H65" s="213"/>
-      <c r="I65" s="213"/>
-      <c r="J65" s="213"/>
-      <c r="K65" s="213"/>
-      <c r="L65" s="213"/>
-      <c r="M65" s="213"/>
-      <c r="N65" s="213"/>
-      <c r="O65" s="214"/>
-      <c r="P65" s="189" cm="1">
+      <c r="G65" s="216"/>
+      <c r="H65" s="216"/>
+      <c r="I65" s="216"/>
+      <c r="J65" s="216"/>
+      <c r="K65" s="216"/>
+      <c r="L65" s="216"/>
+      <c r="M65" s="216"/>
+      <c r="N65" s="216"/>
+      <c r="O65" s="217"/>
+      <c r="P65" s="192" cm="1">
         <f t="array" ref="P65">SUMPRODUCT($D66:$O66, 2^(COLUMN($O66)-COLUMN($D66:$O66)))</f>
         <v>0</v>
       </c>
-      <c r="Q65" s="220" t="str">
+      <c r="Q65" s="223" t="str">
         <f>"0x"&amp;DEC2HEX($P65, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R65" s="183"/>
+      <c r="R65" s="178"/>
     </row>
     <row r="66" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="209"/>
-      <c r="B66" s="211"/>
-      <c r="C66" s="181"/>
+      <c r="A66" s="212"/>
+      <c r="B66" s="214"/>
+      <c r="C66" s="186"/>
       <c r="D66" s="49">
         <v>0</v>
       </c>
@@ -14170,18 +14170,18 @@
       <c r="O66" s="29">
         <v>0</v>
       </c>
-      <c r="P66" s="190"/>
-      <c r="Q66" s="221"/>
-      <c r="R66" s="184"/>
+      <c r="P66" s="193"/>
+      <c r="Q66" s="224"/>
+      <c r="R66" s="179"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A67" s="208" t="s">
+      <c r="A67" s="211" t="s">
         <v>179</v>
       </c>
-      <c r="B67" s="210" t="s">
+      <c r="B67" s="213" t="s">
         <v>178</v>
       </c>
-      <c r="C67" s="180" t="s">
+      <c r="C67" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D67" s="41" t="s">
@@ -14190,32 +14190,32 @@
       <c r="E67" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F67" s="217" t="s">
+      <c r="F67" s="220" t="s">
         <v>177</v>
       </c>
-      <c r="G67" s="213"/>
-      <c r="H67" s="213"/>
-      <c r="I67" s="213"/>
-      <c r="J67" s="213"/>
-      <c r="K67" s="213"/>
-      <c r="L67" s="213"/>
-      <c r="M67" s="213"/>
-      <c r="N67" s="213"/>
-      <c r="O67" s="214"/>
-      <c r="P67" s="189" cm="1">
+      <c r="G67" s="216"/>
+      <c r="H67" s="216"/>
+      <c r="I67" s="216"/>
+      <c r="J67" s="216"/>
+      <c r="K67" s="216"/>
+      <c r="L67" s="216"/>
+      <c r="M67" s="216"/>
+      <c r="N67" s="216"/>
+      <c r="O67" s="217"/>
+      <c r="P67" s="192" cm="1">
         <f t="array" ref="P67">SUMPRODUCT($D68:$O68, 2^(COLUMN($O68)-COLUMN($D68:$O68)))</f>
         <v>0</v>
       </c>
-      <c r="Q67" s="191" t="str">
+      <c r="Q67" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P67, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R67" s="183"/>
+      <c r="R67" s="178"/>
     </row>
     <row r="68" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A68" s="209"/>
-      <c r="B68" s="211"/>
-      <c r="C68" s="181"/>
+      <c r="A68" s="212"/>
+      <c r="B68" s="214"/>
+      <c r="C68" s="186"/>
       <c r="D68" s="40">
         <v>0</v>
       </c>
@@ -14252,50 +14252,50 @@
       <c r="O68" s="29">
         <v>0</v>
       </c>
-      <c r="P68" s="190"/>
-      <c r="Q68" s="192"/>
-      <c r="R68" s="184"/>
+      <c r="P68" s="193"/>
+      <c r="Q68" s="195"/>
+      <c r="R68" s="179"/>
     </row>
     <row r="69" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="208" t="s">
+      <c r="A69" s="211" t="s">
         <v>176</v>
       </c>
-      <c r="B69" s="210" t="s">
+      <c r="B69" s="213" t="s">
         <v>175</v>
       </c>
-      <c r="C69" s="180" t="s">
+      <c r="C69" s="185" t="s">
         <v>88</v>
       </c>
       <c r="D69" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E69" s="217" t="s">
+      <c r="E69" s="220" t="s">
         <v>174</v>
       </c>
-      <c r="F69" s="213"/>
-      <c r="G69" s="213"/>
-      <c r="H69" s="213"/>
-      <c r="I69" s="213"/>
-      <c r="J69" s="213"/>
-      <c r="K69" s="213"/>
-      <c r="L69" s="213"/>
-      <c r="M69" s="213"/>
-      <c r="N69" s="213"/>
-      <c r="O69" s="214"/>
-      <c r="P69" s="189" cm="1">
+      <c r="F69" s="216"/>
+      <c r="G69" s="216"/>
+      <c r="H69" s="216"/>
+      <c r="I69" s="216"/>
+      <c r="J69" s="216"/>
+      <c r="K69" s="216"/>
+      <c r="L69" s="216"/>
+      <c r="M69" s="216"/>
+      <c r="N69" s="216"/>
+      <c r="O69" s="217"/>
+      <c r="P69" s="192" cm="1">
         <f t="array" ref="P69">SUMPRODUCT($D70:$O70, 2^(COLUMN($O70)-COLUMN($D70:$O70)))</f>
         <v>1023</v>
       </c>
-      <c r="Q69" s="187" t="str">
+      <c r="Q69" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P69, 3)</f>
         <v>0x3FF</v>
       </c>
-      <c r="R69" s="183"/>
+      <c r="R69" s="178"/>
     </row>
     <row r="70" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A70" s="209"/>
-      <c r="B70" s="211"/>
-      <c r="C70" s="181"/>
+      <c r="A70" s="212"/>
+      <c r="B70" s="214"/>
+      <c r="C70" s="186"/>
       <c r="D70" s="40">
         <v>0</v>
       </c>
@@ -14332,48 +14332,48 @@
       <c r="O70" s="92">
         <v>1</v>
       </c>
-      <c r="P70" s="190"/>
-      <c r="Q70" s="188"/>
-      <c r="R70" s="184"/>
+      <c r="P70" s="193"/>
+      <c r="Q70" s="191"/>
+      <c r="R70" s="179"/>
     </row>
     <row r="71" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="228" t="s">
+      <c r="A71" s="182" t="s">
         <v>173</v>
       </c>
-      <c r="B71" s="210" t="s">
+      <c r="B71" s="213" t="s">
         <v>172</v>
       </c>
-      <c r="C71" s="180" t="s">
+      <c r="C71" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="212" t="s">
+      <c r="D71" s="215" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="213"/>
-      <c r="F71" s="213"/>
-      <c r="G71" s="213"/>
-      <c r="H71" s="213"/>
-      <c r="I71" s="213"/>
-      <c r="J71" s="213"/>
-      <c r="K71" s="213"/>
-      <c r="L71" s="213"/>
-      <c r="M71" s="213"/>
-      <c r="N71" s="213"/>
-      <c r="O71" s="214"/>
-      <c r="P71" s="189" cm="1">
+      <c r="E71" s="216"/>
+      <c r="F71" s="216"/>
+      <c r="G71" s="216"/>
+      <c r="H71" s="216"/>
+      <c r="I71" s="216"/>
+      <c r="J71" s="216"/>
+      <c r="K71" s="216"/>
+      <c r="L71" s="216"/>
+      <c r="M71" s="216"/>
+      <c r="N71" s="216"/>
+      <c r="O71" s="217"/>
+      <c r="P71" s="192" cm="1">
         <f t="array" ref="P71">SUMPRODUCT($D72:$O72, 2^(COLUMN($O72)-COLUMN($D72:$O72)))</f>
         <v>0</v>
       </c>
-      <c r="Q71" s="191" t="str">
+      <c r="Q71" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P71, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R71" s="183"/>
+      <c r="R71" s="178"/>
     </row>
     <row r="72" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A72" s="229"/>
-      <c r="B72" s="211"/>
-      <c r="C72" s="181"/>
+      <c r="A72" s="181"/>
+      <c r="B72" s="214"/>
+      <c r="C72" s="186"/>
       <c r="D72" s="45">
         <v>0</v>
       </c>
@@ -14410,54 +14410,54 @@
       <c r="O72" s="42">
         <v>0</v>
       </c>
-      <c r="P72" s="190"/>
-      <c r="Q72" s="192"/>
-      <c r="R72" s="184"/>
+      <c r="P72" s="193"/>
+      <c r="Q72" s="195"/>
+      <c r="R72" s="179"/>
     </row>
     <row r="73" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="230" t="s">
         <v>170</v>
       </c>
-      <c r="B73" s="210" t="s">
+      <c r="B73" s="213" t="s">
         <v>169</v>
       </c>
-      <c r="C73" s="180" t="s">
+      <c r="C73" s="185" t="s">
         <v>168</v>
       </c>
       <c r="D73" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="E73" s="219" t="s">
+      <c r="E73" s="222" t="s">
         <v>166</v>
       </c>
-      <c r="F73" s="219"/>
+      <c r="F73" s="222"/>
       <c r="G73" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H73" s="219" t="s">
+      <c r="H73" s="222" t="s">
         <v>165</v>
       </c>
-      <c r="I73" s="219"/>
-      <c r="J73" s="219"/>
-      <c r="K73" s="219"/>
-      <c r="L73" s="219"/>
-      <c r="M73" s="219"/>
-      <c r="N73" s="219"/>
-      <c r="O73" s="236"/>
-      <c r="P73" s="189" cm="1">
+      <c r="I73" s="222"/>
+      <c r="J73" s="222"/>
+      <c r="K73" s="222"/>
+      <c r="L73" s="222"/>
+      <c r="M73" s="222"/>
+      <c r="N73" s="222"/>
+      <c r="O73" s="237"/>
+      <c r="P73" s="192" cm="1">
         <f t="array" ref="P73">SUMPRODUCT($D74:$O74, 2^(COLUMN($O74)-COLUMN($D74:$O74)))</f>
         <v>3122</v>
       </c>
-      <c r="Q73" s="187" t="str">
+      <c r="Q73" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P73, 3)</f>
         <v>0xC32</v>
       </c>
-      <c r="R73" s="183"/>
+      <c r="R73" s="178"/>
     </row>
     <row r="74" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="229"/>
-      <c r="B74" s="211"/>
-      <c r="C74" s="181"/>
+      <c r="A74" s="181"/>
+      <c r="B74" s="214"/>
+      <c r="C74" s="186"/>
       <c r="D74" s="93">
         <v>1</v>
       </c>
@@ -14494,48 +14494,48 @@
       <c r="O74" s="29">
         <v>0</v>
       </c>
-      <c r="P74" s="190"/>
-      <c r="Q74" s="188"/>
-      <c r="R74" s="184"/>
+      <c r="P74" s="193"/>
+      <c r="Q74" s="191"/>
+      <c r="R74" s="179"/>
     </row>
     <row r="75" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="208" t="s">
+      <c r="A75" s="211" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="210" t="s">
+      <c r="B75" s="213" t="s">
         <v>163</v>
       </c>
-      <c r="C75" s="180" t="s">
+      <c r="C75" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="212" t="s">
+      <c r="D75" s="215" t="s">
         <v>162</v>
       </c>
-      <c r="E75" s="213"/>
-      <c r="F75" s="213"/>
-      <c r="G75" s="213"/>
-      <c r="H75" s="213"/>
-      <c r="I75" s="213"/>
-      <c r="J75" s="213"/>
-      <c r="K75" s="213"/>
-      <c r="L75" s="213"/>
-      <c r="M75" s="213"/>
-      <c r="N75" s="213"/>
-      <c r="O75" s="214"/>
-      <c r="P75" s="189" cm="1">
+      <c r="E75" s="216"/>
+      <c r="F75" s="216"/>
+      <c r="G75" s="216"/>
+      <c r="H75" s="216"/>
+      <c r="I75" s="216"/>
+      <c r="J75" s="216"/>
+      <c r="K75" s="216"/>
+      <c r="L75" s="216"/>
+      <c r="M75" s="216"/>
+      <c r="N75" s="216"/>
+      <c r="O75" s="217"/>
+      <c r="P75" s="192" cm="1">
         <f t="array" ref="P75">SUMPRODUCT($D76:$O76, 2^(COLUMN($O76)-COLUMN($D76:$O76)))</f>
         <v>1365</v>
       </c>
-      <c r="Q75" s="187" t="str">
+      <c r="Q75" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P75, 3)</f>
         <v>0x555</v>
       </c>
-      <c r="R75" s="183"/>
+      <c r="R75" s="178"/>
     </row>
     <row r="76" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A76" s="209"/>
-      <c r="B76" s="211"/>
-      <c r="C76" s="181"/>
+      <c r="A76" s="212"/>
+      <c r="B76" s="214"/>
+      <c r="C76" s="186"/>
       <c r="D76" s="36">
         <v>0</v>
       </c>
@@ -14572,28 +14572,28 @@
       <c r="O76" s="92">
         <v>1</v>
       </c>
-      <c r="P76" s="190"/>
-      <c r="Q76" s="188"/>
-      <c r="R76" s="184"/>
+      <c r="P76" s="193"/>
+      <c r="Q76" s="191"/>
+      <c r="R76" s="179"/>
     </row>
     <row r="77" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="208" t="s">
+      <c r="A77" s="211" t="s">
         <v>161</v>
       </c>
-      <c r="B77" s="210" t="s">
+      <c r="B77" s="213" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="180" t="s">
+      <c r="C77" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D77" s="212" t="s">
+      <c r="D77" s="215" t="s">
         <v>159</v>
       </c>
-      <c r="E77" s="213"/>
-      <c r="F77" s="213"/>
-      <c r="G77" s="213"/>
-      <c r="H77" s="213"/>
-      <c r="I77" s="222"/>
+      <c r="E77" s="216"/>
+      <c r="F77" s="216"/>
+      <c r="G77" s="216"/>
+      <c r="H77" s="216"/>
+      <c r="I77" s="231"/>
       <c r="J77" s="32" t="s">
         <v>158</v>
       </c>
@@ -14612,20 +14612,20 @@
       <c r="O77" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="P77" s="189" cm="1">
+      <c r="P77" s="192" cm="1">
         <f t="array" ref="P77">SUMPRODUCT($D78:$O78, 2^(COLUMN($O78)-COLUMN($D78:$O78)))</f>
         <v>0</v>
       </c>
-      <c r="Q77" s="191" t="str">
+      <c r="Q77" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P77, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R77" s="183"/>
+      <c r="R77" s="178"/>
     </row>
     <row r="78" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A78" s="209"/>
-      <c r="B78" s="211"/>
-      <c r="C78" s="181"/>
+      <c r="A78" s="212"/>
+      <c r="B78" s="214"/>
+      <c r="C78" s="186"/>
       <c r="D78" s="36">
         <v>0</v>
       </c>
@@ -14662,18 +14662,18 @@
       <c r="O78" s="29">
         <v>0</v>
       </c>
-      <c r="P78" s="190"/>
-      <c r="Q78" s="192"/>
-      <c r="R78" s="184"/>
+      <c r="P78" s="193"/>
+      <c r="Q78" s="195"/>
+      <c r="R78" s="179"/>
     </row>
     <row r="79" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A79" s="208" t="s">
+      <c r="A79" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="B79" s="210" t="s">
+      <c r="B79" s="213" t="s">
         <v>152</v>
       </c>
-      <c r="C79" s="180" t="s">
+      <c r="C79" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D79" s="46" t="s">
@@ -14712,20 +14712,20 @@
       <c r="O79" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="P79" s="189" cm="1">
+      <c r="P79" s="192" cm="1">
         <f t="array" ref="P79">SUMPRODUCT($D80:$O80, 2^(COLUMN($O80)-COLUMN($D80:$O80)))</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="220" t="str">
+      <c r="Q79" s="223" t="str">
         <f>"0x"&amp;DEC2HEX($P79, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R79" s="183"/>
+      <c r="R79" s="178"/>
     </row>
     <row r="80" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A80" s="209"/>
-      <c r="B80" s="211"/>
-      <c r="C80" s="181"/>
+      <c r="A80" s="212"/>
+      <c r="B80" s="214"/>
+      <c r="C80" s="186"/>
       <c r="D80" s="47">
         <v>0</v>
       </c>
@@ -14762,18 +14762,18 @@
       <c r="O80" s="42">
         <v>0</v>
       </c>
-      <c r="P80" s="190"/>
-      <c r="Q80" s="221"/>
-      <c r="R80" s="184"/>
+      <c r="P80" s="193"/>
+      <c r="Q80" s="224"/>
+      <c r="R80" s="179"/>
     </row>
     <row r="81" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="208" t="s">
+      <c r="A81" s="211" t="s">
         <v>144</v>
       </c>
-      <c r="B81" s="210" t="s">
+      <c r="B81" s="213" t="s">
         <v>143</v>
       </c>
-      <c r="C81" s="180" t="s">
+      <c r="C81" s="185" t="s">
         <v>142</v>
       </c>
       <c r="D81" s="41" t="s">
@@ -14794,32 +14794,32 @@
       <c r="I81" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="J81" s="217" t="s">
+      <c r="J81" s="220" t="s">
         <v>139</v>
       </c>
-      <c r="K81" s="222"/>
-      <c r="L81" s="217" t="s">
+      <c r="K81" s="231"/>
+      <c r="L81" s="220" t="s">
         <v>138</v>
       </c>
-      <c r="M81" s="222"/>
-      <c r="N81" s="217" t="s">
+      <c r="M81" s="231"/>
+      <c r="N81" s="220" t="s">
         <v>137</v>
       </c>
-      <c r="O81" s="214"/>
-      <c r="P81" s="189" cm="1">
+      <c r="O81" s="217"/>
+      <c r="P81" s="192" cm="1">
         <f t="array" ref="P81">SUMPRODUCT($D82:$O82, 2^(COLUMN($O82)-COLUMN($D82:$O82)))</f>
         <v>41</v>
       </c>
-      <c r="Q81" s="187" t="str">
+      <c r="Q81" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P81, 3)</f>
         <v>0x029</v>
       </c>
-      <c r="R81" s="183"/>
+      <c r="R81" s="178"/>
     </row>
     <row r="82" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A82" s="209"/>
-      <c r="B82" s="211"/>
-      <c r="C82" s="181"/>
+      <c r="A82" s="212"/>
+      <c r="B82" s="214"/>
+      <c r="C82" s="186"/>
       <c r="D82" s="40">
         <v>0</v>
       </c>
@@ -14856,48 +14856,48 @@
       <c r="O82" s="92">
         <v>1</v>
       </c>
-      <c r="P82" s="190"/>
-      <c r="Q82" s="188"/>
-      <c r="R82" s="184"/>
+      <c r="P82" s="193"/>
+      <c r="Q82" s="191"/>
+      <c r="R82" s="179"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A83" s="228" t="s">
+      <c r="A83" s="182" t="s">
         <v>136</v>
       </c>
-      <c r="B83" s="210" t="s">
+      <c r="B83" s="213" t="s">
         <v>135</v>
       </c>
-      <c r="C83" s="180" t="s">
+      <c r="C83" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D83" s="212" t="s">
+      <c r="D83" s="215" t="s">
         <v>134</v>
       </c>
-      <c r="E83" s="213"/>
-      <c r="F83" s="213"/>
-      <c r="G83" s="213"/>
-      <c r="H83" s="213"/>
-      <c r="I83" s="213"/>
-      <c r="J83" s="213"/>
-      <c r="K83" s="213"/>
-      <c r="L83" s="213"/>
-      <c r="M83" s="213"/>
-      <c r="N83" s="213"/>
-      <c r="O83" s="214"/>
-      <c r="P83" s="189" cm="1">
+      <c r="E83" s="216"/>
+      <c r="F83" s="216"/>
+      <c r="G83" s="216"/>
+      <c r="H83" s="216"/>
+      <c r="I83" s="216"/>
+      <c r="J83" s="216"/>
+      <c r="K83" s="216"/>
+      <c r="L83" s="216"/>
+      <c r="M83" s="216"/>
+      <c r="N83" s="216"/>
+      <c r="O83" s="217"/>
+      <c r="P83" s="192" cm="1">
         <f t="array" ref="P83">SUMPRODUCT($D84:$O84, 2^(COLUMN($O84)-COLUMN($D84:$O84)))</f>
         <v>0</v>
       </c>
-      <c r="Q83" s="191" t="str">
+      <c r="Q83" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P83, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R83" s="183"/>
+      <c r="R83" s="178"/>
     </row>
     <row r="84" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A84" s="229"/>
-      <c r="B84" s="211"/>
-      <c r="C84" s="181"/>
+      <c r="A84" s="181"/>
+      <c r="B84" s="214"/>
+      <c r="C84" s="186"/>
       <c r="D84" s="45">
         <v>0</v>
       </c>
@@ -14934,18 +14934,18 @@
       <c r="O84" s="42">
         <v>0</v>
       </c>
-      <c r="P84" s="190"/>
-      <c r="Q84" s="192"/>
-      <c r="R84" s="184"/>
+      <c r="P84" s="193"/>
+      <c r="Q84" s="195"/>
+      <c r="R84" s="179"/>
     </row>
     <row r="85" spans="1:18" ht="26" x14ac:dyDescent="0.45">
       <c r="A85" s="230" t="s">
         <v>133</v>
       </c>
-      <c r="B85" s="210" t="s">
+      <c r="B85" s="213" t="s">
         <v>132</v>
       </c>
-      <c r="C85" s="180" t="s">
+      <c r="C85" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D85" s="46" t="s">
@@ -14966,30 +14966,30 @@
       <c r="I85" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="J85" s="225" t="s">
+      <c r="J85" s="227" t="s">
         <v>130</v>
       </c>
-      <c r="K85" s="235"/>
-      <c r="L85" s="225" t="s">
+      <c r="K85" s="236"/>
+      <c r="L85" s="227" t="s">
         <v>129</v>
       </c>
-      <c r="M85" s="226"/>
-      <c r="N85" s="226"/>
-      <c r="O85" s="227"/>
-      <c r="P85" s="231" cm="1">
+      <c r="M85" s="228"/>
+      <c r="N85" s="228"/>
+      <c r="O85" s="229"/>
+      <c r="P85" s="232" cm="1">
         <f t="array" ref="P85">SUMPRODUCT($D86:$O86, 2^(COLUMN($O86)-COLUMN($D86:$O86)))</f>
         <v>2056</v>
       </c>
-      <c r="Q85" s="233" t="str">
+      <c r="Q85" s="234" t="str">
         <f>"0x"&amp;DEC2HEX($P85, 3)</f>
         <v>0x808</v>
       </c>
-      <c r="R85" s="245"/>
+      <c r="R85" s="180"/>
     </row>
     <row r="86" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A86" s="229"/>
-      <c r="B86" s="211"/>
-      <c r="C86" s="181"/>
+      <c r="A86" s="181"/>
+      <c r="B86" s="214"/>
+      <c r="C86" s="186"/>
       <c r="D86" s="95">
         <v>1</v>
       </c>
@@ -15026,18 +15026,18 @@
       <c r="O86" s="21">
         <v>0</v>
       </c>
-      <c r="P86" s="232"/>
-      <c r="Q86" s="234"/>
-      <c r="R86" s="229"/>
+      <c r="P86" s="233"/>
+      <c r="Q86" s="235"/>
+      <c r="R86" s="181"/>
     </row>
     <row r="87" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="208" t="s">
+      <c r="A87" s="211" t="s">
         <v>128</v>
       </c>
-      <c r="B87" s="210" t="s">
+      <c r="B87" s="213" t="s">
         <v>127</v>
       </c>
-      <c r="C87" s="180" t="s">
+      <c r="C87" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="39" t="s">
@@ -15055,33 +15055,33 @@
       <c r="H87" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I87" s="217" t="s">
+      <c r="I87" s="220" t="s">
         <v>125</v>
       </c>
-      <c r="J87" s="213"/>
-      <c r="K87" s="222"/>
+      <c r="J87" s="216"/>
+      <c r="K87" s="231"/>
       <c r="L87" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="M87" s="217" t="s">
+      <c r="M87" s="220" t="s">
         <v>124</v>
       </c>
-      <c r="N87" s="213"/>
-      <c r="O87" s="214"/>
-      <c r="P87" s="189" cm="1">
+      <c r="N87" s="216"/>
+      <c r="O87" s="217"/>
+      <c r="P87" s="192" cm="1">
         <f t="array" ref="P87">SUMPRODUCT($D88:$O88, 2^(COLUMN($O88)-COLUMN($D88:$O88)))</f>
         <v>0</v>
       </c>
-      <c r="Q87" s="191" t="str">
+      <c r="Q87" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P87, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R87" s="183"/>
+      <c r="R87" s="178"/>
     </row>
     <row r="88" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A88" s="209"/>
-      <c r="B88" s="211"/>
-      <c r="C88" s="181"/>
+      <c r="A88" s="212"/>
+      <c r="B88" s="214"/>
+      <c r="C88" s="186"/>
       <c r="D88" s="45">
         <v>0</v>
       </c>
@@ -15118,18 +15118,18 @@
       <c r="O88" s="42">
         <v>0</v>
       </c>
-      <c r="P88" s="190"/>
-      <c r="Q88" s="192"/>
-      <c r="R88" s="184"/>
+      <c r="P88" s="193"/>
+      <c r="Q88" s="195"/>
+      <c r="R88" s="179"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A89" s="208" t="s">
+      <c r="A89" s="211" t="s">
         <v>123</v>
       </c>
-      <c r="B89" s="210" t="s">
+      <c r="B89" s="213" t="s">
         <v>122</v>
       </c>
-      <c r="C89" s="180" t="s">
+      <c r="C89" s="185" t="s">
         <v>121</v>
       </c>
       <c r="D89" s="41" t="s">
@@ -15168,20 +15168,20 @@
       <c r="O89" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="P89" s="189" cm="1">
+      <c r="P89" s="192" cm="1">
         <f t="array" ref="P89">SUMPRODUCT($D90:$O90, 2^(COLUMN($O90)-COLUMN($D90:$O90)))</f>
         <v>23</v>
       </c>
-      <c r="Q89" s="187" t="str">
+      <c r="Q89" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P89, 3)</f>
         <v>0x017</v>
       </c>
-      <c r="R89" s="183"/>
+      <c r="R89" s="178"/>
     </row>
     <row r="90" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A90" s="209"/>
-      <c r="B90" s="211"/>
-      <c r="C90" s="181"/>
+      <c r="A90" s="212"/>
+      <c r="B90" s="214"/>
+      <c r="C90" s="186"/>
       <c r="D90" s="40">
         <v>0</v>
       </c>
@@ -15218,48 +15218,48 @@
       <c r="O90" s="92">
         <v>1</v>
       </c>
-      <c r="P90" s="190"/>
-      <c r="Q90" s="188"/>
-      <c r="R90" s="184"/>
+      <c r="P90" s="193"/>
+      <c r="Q90" s="191"/>
+      <c r="R90" s="179"/>
     </row>
     <row r="91" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="208" t="s">
+      <c r="A91" s="211" t="s">
         <v>116</v>
       </c>
-      <c r="B91" s="210" t="s">
+      <c r="B91" s="213" t="s">
         <v>115</v>
       </c>
-      <c r="C91" s="180" t="s">
+      <c r="C91" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D91" s="212" t="s">
+      <c r="D91" s="215" t="s">
         <v>114</v>
       </c>
-      <c r="E91" s="213"/>
-      <c r="F91" s="213"/>
-      <c r="G91" s="213"/>
-      <c r="H91" s="213"/>
-      <c r="I91" s="213"/>
-      <c r="J91" s="213"/>
-      <c r="K91" s="213"/>
-      <c r="L91" s="213"/>
-      <c r="M91" s="213"/>
-      <c r="N91" s="213"/>
-      <c r="O91" s="214"/>
-      <c r="P91" s="189" cm="1">
+      <c r="E91" s="216"/>
+      <c r="F91" s="216"/>
+      <c r="G91" s="216"/>
+      <c r="H91" s="216"/>
+      <c r="I91" s="216"/>
+      <c r="J91" s="216"/>
+      <c r="K91" s="216"/>
+      <c r="L91" s="216"/>
+      <c r="M91" s="216"/>
+      <c r="N91" s="216"/>
+      <c r="O91" s="217"/>
+      <c r="P91" s="192" cm="1">
         <f t="array" ref="P91">SUMPRODUCT($D92:$O92, 2^(COLUMN($O92)-COLUMN($D92:$O92)))</f>
         <v>0</v>
       </c>
-      <c r="Q91" s="191" t="str">
+      <c r="Q91" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P91, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R91" s="183"/>
+      <c r="R91" s="178"/>
     </row>
     <row r="92" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A92" s="209"/>
-      <c r="B92" s="211"/>
-      <c r="C92" s="181"/>
+      <c r="A92" s="212"/>
+      <c r="B92" s="214"/>
+      <c r="C92" s="186"/>
       <c r="D92" s="36">
         <v>0</v>
       </c>
@@ -15296,48 +15296,48 @@
       <c r="O92" s="29">
         <v>0</v>
       </c>
-      <c r="P92" s="190"/>
-      <c r="Q92" s="192"/>
-      <c r="R92" s="184"/>
+      <c r="P92" s="193"/>
+      <c r="Q92" s="195"/>
+      <c r="R92" s="179"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A93" s="208" t="s">
+      <c r="A93" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="210" t="s">
+      <c r="B93" s="213" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="180" t="s">
+      <c r="C93" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D93" s="212" t="s">
+      <c r="D93" s="215" t="s">
         <v>111</v>
       </c>
-      <c r="E93" s="213"/>
-      <c r="F93" s="213"/>
-      <c r="G93" s="213"/>
-      <c r="H93" s="213"/>
-      <c r="I93" s="213"/>
-      <c r="J93" s="213"/>
-      <c r="K93" s="213"/>
-      <c r="L93" s="213"/>
-      <c r="M93" s="213"/>
-      <c r="N93" s="213"/>
-      <c r="O93" s="214"/>
-      <c r="P93" s="189" cm="1">
+      <c r="E93" s="216"/>
+      <c r="F93" s="216"/>
+      <c r="G93" s="216"/>
+      <c r="H93" s="216"/>
+      <c r="I93" s="216"/>
+      <c r="J93" s="216"/>
+      <c r="K93" s="216"/>
+      <c r="L93" s="216"/>
+      <c r="M93" s="216"/>
+      <c r="N93" s="216"/>
+      <c r="O93" s="217"/>
+      <c r="P93" s="192" cm="1">
         <f t="array" ref="P93">SUMPRODUCT($D94:$O94, 2^(COLUMN($O94)-COLUMN($D94:$O94)))</f>
         <v>0</v>
       </c>
-      <c r="Q93" s="191" t="str">
+      <c r="Q93" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P93, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R93" s="183"/>
+      <c r="R93" s="178"/>
     </row>
     <row r="94" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A94" s="209"/>
-      <c r="B94" s="211"/>
-      <c r="C94" s="181"/>
+      <c r="A94" s="212"/>
+      <c r="B94" s="214"/>
+      <c r="C94" s="186"/>
       <c r="D94" s="36">
         <v>0</v>
       </c>
@@ -15374,48 +15374,48 @@
       <c r="O94" s="29">
         <v>0</v>
       </c>
-      <c r="P94" s="190"/>
-      <c r="Q94" s="192"/>
-      <c r="R94" s="184"/>
+      <c r="P94" s="193"/>
+      <c r="Q94" s="195"/>
+      <c r="R94" s="179"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A95" s="208" t="s">
+      <c r="A95" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="B95" s="210" t="s">
+      <c r="B95" s="213" t="s">
         <v>109</v>
       </c>
-      <c r="C95" s="180" t="s">
+      <c r="C95" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D95" s="212" t="s">
+      <c r="D95" s="215" t="s">
         <v>108</v>
       </c>
-      <c r="E95" s="213"/>
-      <c r="F95" s="213"/>
-      <c r="G95" s="213"/>
-      <c r="H95" s="213"/>
-      <c r="I95" s="213"/>
-      <c r="J95" s="213"/>
-      <c r="K95" s="213"/>
-      <c r="L95" s="213"/>
-      <c r="M95" s="213"/>
-      <c r="N95" s="213"/>
-      <c r="O95" s="214"/>
-      <c r="P95" s="189" cm="1">
+      <c r="E95" s="216"/>
+      <c r="F95" s="216"/>
+      <c r="G95" s="216"/>
+      <c r="H95" s="216"/>
+      <c r="I95" s="216"/>
+      <c r="J95" s="216"/>
+      <c r="K95" s="216"/>
+      <c r="L95" s="216"/>
+      <c r="M95" s="216"/>
+      <c r="N95" s="216"/>
+      <c r="O95" s="217"/>
+      <c r="P95" s="192" cm="1">
         <f t="array" ref="P95">SUMPRODUCT($D96:$O96, 2^(COLUMN($O96)-COLUMN($D96:$O96)))</f>
         <v>0</v>
       </c>
-      <c r="Q95" s="191" t="str">
+      <c r="Q95" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P95, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R95" s="183"/>
+      <c r="R95" s="178"/>
     </row>
     <row r="96" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A96" s="209"/>
-      <c r="B96" s="211"/>
-      <c r="C96" s="181"/>
+      <c r="A96" s="212"/>
+      <c r="B96" s="214"/>
+      <c r="C96" s="186"/>
       <c r="D96" s="36">
         <v>0</v>
       </c>
@@ -15452,40 +15452,40 @@
       <c r="O96" s="29">
         <v>0</v>
       </c>
-      <c r="P96" s="190"/>
-      <c r="Q96" s="192"/>
-      <c r="R96" s="184"/>
+      <c r="P96" s="193"/>
+      <c r="Q96" s="195"/>
+      <c r="R96" s="179"/>
     </row>
     <row r="97" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A97" s="242" t="s">
+      <c r="A97" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="B97" s="243"/>
-      <c r="C97" s="243"/>
-      <c r="D97" s="243"/>
-      <c r="E97" s="243"/>
-      <c r="F97" s="243"/>
-      <c r="G97" s="243"/>
-      <c r="H97" s="243"/>
-      <c r="I97" s="243"/>
-      <c r="J97" s="243"/>
-      <c r="K97" s="243"/>
-      <c r="L97" s="243"/>
-      <c r="M97" s="243"/>
-      <c r="N97" s="243"/>
-      <c r="O97" s="243"/>
-      <c r="P97" s="243"/>
-      <c r="Q97" s="243"/>
-      <c r="R97" s="244"/>
+      <c r="B97" s="244"/>
+      <c r="C97" s="244"/>
+      <c r="D97" s="244"/>
+      <c r="E97" s="244"/>
+      <c r="F97" s="244"/>
+      <c r="G97" s="244"/>
+      <c r="H97" s="244"/>
+      <c r="I97" s="244"/>
+      <c r="J97" s="244"/>
+      <c r="K97" s="244"/>
+      <c r="L97" s="244"/>
+      <c r="M97" s="244"/>
+      <c r="N97" s="244"/>
+      <c r="O97" s="244"/>
+      <c r="P97" s="244"/>
+      <c r="Q97" s="244"/>
+      <c r="R97" s="245"/>
     </row>
     <row r="98" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A98" s="223" t="s">
+      <c r="A98" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="224" t="s">
+      <c r="B98" s="247" t="s">
         <v>105</v>
       </c>
-      <c r="C98" s="180" t="s">
+      <c r="C98" s="185" t="s">
         <v>84</v>
       </c>
       <c r="D98" s="39" t="s">
@@ -15500,10 +15500,10 @@
       <c r="G98" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H98" s="217" t="s">
+      <c r="H98" s="220" t="s">
         <v>103</v>
       </c>
-      <c r="I98" s="222"/>
+      <c r="I98" s="231"/>
       <c r="J98" s="32" t="s">
         <v>102</v>
       </c>
@@ -15522,20 +15522,20 @@
       <c r="O98" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="P98" s="189" cm="1">
+      <c r="P98" s="192" cm="1">
         <f t="array" ref="P98">SUMPRODUCT($D99:$O99, 2^(COLUMN($O99)-COLUMN($D99:$O99)))</f>
         <v>2084</v>
       </c>
-      <c r="Q98" s="187" t="str">
+      <c r="Q98" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P98, 3)</f>
         <v>0x824</v>
       </c>
-      <c r="R98" s="183"/>
+      <c r="R98" s="178"/>
     </row>
     <row r="99" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A99" s="209"/>
-      <c r="B99" s="211"/>
-      <c r="C99" s="181"/>
+      <c r="A99" s="212"/>
+      <c r="B99" s="214"/>
+      <c r="C99" s="186"/>
       <c r="D99" s="36">
         <v>1</v>
       </c>
@@ -15572,18 +15572,18 @@
       <c r="O99" s="29">
         <v>0</v>
       </c>
-      <c r="P99" s="190"/>
-      <c r="Q99" s="188"/>
-      <c r="R99" s="184"/>
+      <c r="P99" s="193"/>
+      <c r="Q99" s="191"/>
+      <c r="R99" s="179"/>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A100" s="208" t="s">
+      <c r="A100" s="211" t="s">
         <v>96</v>
       </c>
-      <c r="B100" s="210" t="s">
+      <c r="B100" s="213" t="s">
         <v>95</v>
       </c>
-      <c r="C100" s="180" t="s">
+      <c r="C100" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D100" s="34" t="s">
@@ -15607,27 +15607,27 @@
       <c r="J100" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K100" s="219" t="s">
+      <c r="K100" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="L100" s="219"/>
-      <c r="M100" s="219"/>
-      <c r="N100" s="219"/>
-      <c r="O100" s="236"/>
-      <c r="P100" s="215" cm="1">
+      <c r="L100" s="222"/>
+      <c r="M100" s="222"/>
+      <c r="N100" s="222"/>
+      <c r="O100" s="237"/>
+      <c r="P100" s="218" cm="1">
         <f t="array" ref="P100">SUMPRODUCT($D101:$O101, 2^(COLUMN($O101)-COLUMN($D101:$O101)))</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="191" t="str">
+      <c r="Q100" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P100, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R100" s="183"/>
+      <c r="R100" s="178"/>
     </row>
     <row r="101" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A101" s="209"/>
-      <c r="B101" s="211"/>
-      <c r="C101" s="181"/>
+      <c r="A101" s="212"/>
+      <c r="B101" s="214"/>
+      <c r="C101" s="186"/>
       <c r="D101" s="30">
         <v>0</v>
       </c>
@@ -15664,18 +15664,18 @@
       <c r="O101" s="29">
         <v>0</v>
       </c>
-      <c r="P101" s="216"/>
-      <c r="Q101" s="192"/>
-      <c r="R101" s="184"/>
+      <c r="P101" s="219"/>
+      <c r="Q101" s="195"/>
+      <c r="R101" s="179"/>
     </row>
     <row r="102" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="208" t="s">
+      <c r="A102" s="211" t="s">
         <v>93</v>
       </c>
-      <c r="B102" s="210" t="s">
+      <c r="B102" s="213" t="s">
         <v>92</v>
       </c>
-      <c r="C102" s="180" t="s">
+      <c r="C102" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="34" t="s">
@@ -15702,26 +15702,26 @@
       <c r="K102" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="L102" s="217" t="s">
+      <c r="L102" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="M102" s="213"/>
-      <c r="N102" s="213"/>
-      <c r="O102" s="214"/>
-      <c r="P102" s="215" cm="1">
+      <c r="M102" s="216"/>
+      <c r="N102" s="216"/>
+      <c r="O102" s="217"/>
+      <c r="P102" s="218" cm="1">
         <f t="array" ref="P102">SUMPRODUCT($D103:$O103, 2^(COLUMN($O103)-COLUMN($D103:$O103)))</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="191" t="str">
+      <c r="Q102" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P102, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R102" s="183"/>
+      <c r="R102" s="178"/>
     </row>
     <row r="103" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A103" s="209"/>
-      <c r="B103" s="211"/>
-      <c r="C103" s="181"/>
+      <c r="A103" s="212"/>
+      <c r="B103" s="214"/>
+      <c r="C103" s="186"/>
       <c r="D103" s="30">
         <v>0</v>
       </c>
@@ -15758,48 +15758,48 @@
       <c r="O103" s="29">
         <v>0</v>
       </c>
-      <c r="P103" s="216"/>
-      <c r="Q103" s="192"/>
-      <c r="R103" s="184"/>
+      <c r="P103" s="219"/>
+      <c r="Q103" s="195"/>
+      <c r="R103" s="179"/>
     </row>
     <row r="104" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A104" s="208" t="s">
+      <c r="A104" s="211" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="210" t="s">
+      <c r="B104" s="213" t="s">
         <v>89</v>
       </c>
-      <c r="C104" s="180" t="s">
+      <c r="C104" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="D104" s="212" t="s">
+      <c r="D104" s="215" t="s">
         <v>87</v>
       </c>
-      <c r="E104" s="213"/>
-      <c r="F104" s="213"/>
-      <c r="G104" s="213"/>
-      <c r="H104" s="213"/>
-      <c r="I104" s="213"/>
-      <c r="J104" s="213"/>
-      <c r="K104" s="213"/>
-      <c r="L104" s="213"/>
-      <c r="M104" s="213"/>
-      <c r="N104" s="213"/>
-      <c r="O104" s="214"/>
-      <c r="P104" s="215" cm="1">
+      <c r="E104" s="216"/>
+      <c r="F104" s="216"/>
+      <c r="G104" s="216"/>
+      <c r="H104" s="216"/>
+      <c r="I104" s="216"/>
+      <c r="J104" s="216"/>
+      <c r="K104" s="216"/>
+      <c r="L104" s="216"/>
+      <c r="M104" s="216"/>
+      <c r="N104" s="216"/>
+      <c r="O104" s="217"/>
+      <c r="P104" s="218" cm="1">
         <f t="array" ref="P104">SUMPRODUCT($D105:$O105, 2^(COLUMN($O105)-COLUMN($D105:$O105)))</f>
         <v>1023</v>
       </c>
-      <c r="Q104" s="187" t="str">
+      <c r="Q104" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P104, 3)</f>
         <v>0x3FF</v>
       </c>
-      <c r="R104" s="183"/>
+      <c r="R104" s="178"/>
     </row>
     <row r="105" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A105" s="209"/>
-      <c r="B105" s="211"/>
-      <c r="C105" s="181"/>
+      <c r="A105" s="212"/>
+      <c r="B105" s="214"/>
+      <c r="C105" s="186"/>
       <c r="D105" s="20">
         <v>0</v>
       </c>
@@ -15836,18 +15836,18 @@
       <c r="O105" s="92">
         <v>1</v>
       </c>
-      <c r="P105" s="216"/>
-      <c r="Q105" s="188"/>
-      <c r="R105" s="184"/>
+      <c r="P105" s="219"/>
+      <c r="Q105" s="191"/>
+      <c r="R105" s="179"/>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A106" s="208" t="s">
+      <c r="A106" s="211" t="s">
         <v>86</v>
       </c>
-      <c r="B106" s="210" t="s">
+      <c r="B106" s="213" t="s">
         <v>85</v>
       </c>
-      <c r="C106" s="180" t="s">
+      <c r="C106" s="185" t="s">
         <v>84</v>
       </c>
       <c r="D106" s="33" t="s">
@@ -15868,30 +15868,30 @@
       <c r="I106" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="J106" s="219" t="s">
+      <c r="J106" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="K106" s="219"/>
-      <c r="L106" s="217" t="s">
+      <c r="K106" s="222"/>
+      <c r="L106" s="220" t="s">
         <v>82</v>
       </c>
-      <c r="M106" s="213"/>
-      <c r="N106" s="213"/>
-      <c r="O106" s="214"/>
-      <c r="P106" s="215" cm="1">
+      <c r="M106" s="216"/>
+      <c r="N106" s="216"/>
+      <c r="O106" s="217"/>
+      <c r="P106" s="218" cm="1">
         <f t="array" ref="P106">SUMPRODUCT($D107:$O107, 2^(COLUMN($O107)-COLUMN($D107:$O107)))</f>
         <v>4</v>
       </c>
-      <c r="Q106" s="187" t="str">
+      <c r="Q106" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P106, 3)</f>
         <v>0x004</v>
       </c>
-      <c r="R106" s="183"/>
+      <c r="R106" s="178"/>
     </row>
     <row r="107" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="209"/>
-      <c r="B107" s="211"/>
-      <c r="C107" s="181"/>
+      <c r="A107" s="212"/>
+      <c r="B107" s="214"/>
+      <c r="C107" s="186"/>
       <c r="D107" s="30">
         <v>0</v>
       </c>
@@ -15928,18 +15928,18 @@
       <c r="O107" s="29">
         <v>0</v>
       </c>
-      <c r="P107" s="216"/>
-      <c r="Q107" s="188"/>
-      <c r="R107" s="184"/>
+      <c r="P107" s="219"/>
+      <c r="Q107" s="191"/>
+      <c r="R107" s="179"/>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A108" s="208" t="s">
+      <c r="A108" s="211" t="s">
         <v>81</v>
       </c>
-      <c r="B108" s="210" t="s">
+      <c r="B108" s="213" t="s">
         <v>80</v>
       </c>
-      <c r="C108" s="180" t="s">
+      <c r="C108" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="28" t="s">
@@ -15978,20 +15978,20 @@
       <c r="O108" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="P108" s="215" cm="1">
+      <c r="P108" s="218" cm="1">
         <f t="array" ref="P108">SUMPRODUCT($D109:$O109, 2^(COLUMN($O109)-COLUMN($D109:$O109)))</f>
         <v>0</v>
       </c>
-      <c r="Q108" s="220" t="str">
+      <c r="Q108" s="223" t="str">
         <f>"0x"&amp;DEC2HEX($P108, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R108" s="183"/>
+      <c r="R108" s="178"/>
     </row>
     <row r="109" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A109" s="209"/>
-      <c r="B109" s="211"/>
-      <c r="C109" s="181"/>
+      <c r="A109" s="212"/>
+      <c r="B109" s="214"/>
+      <c r="C109" s="186"/>
       <c r="D109" s="20">
         <v>0</v>
       </c>
@@ -16028,48 +16028,48 @@
       <c r="O109" s="21">
         <v>0</v>
       </c>
-      <c r="P109" s="216"/>
-      <c r="Q109" s="221"/>
-      <c r="R109" s="184"/>
+      <c r="P109" s="219"/>
+      <c r="Q109" s="224"/>
+      <c r="R109" s="179"/>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A110" s="208" t="s">
+      <c r="A110" s="211" t="s">
         <v>76</v>
       </c>
-      <c r="B110" s="210" t="s">
+      <c r="B110" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="C110" s="180" t="s">
+      <c r="C110" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="D110" s="212" t="s">
+      <c r="D110" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="E110" s="213"/>
-      <c r="F110" s="213"/>
-      <c r="G110" s="213"/>
-      <c r="H110" s="213"/>
-      <c r="I110" s="213"/>
-      <c r="J110" s="213"/>
-      <c r="K110" s="213"/>
-      <c r="L110" s="213"/>
-      <c r="M110" s="213"/>
-      <c r="N110" s="213"/>
-      <c r="O110" s="214"/>
-      <c r="P110" s="215" cm="1">
+      <c r="E110" s="216"/>
+      <c r="F110" s="216"/>
+      <c r="G110" s="216"/>
+      <c r="H110" s="216"/>
+      <c r="I110" s="216"/>
+      <c r="J110" s="216"/>
+      <c r="K110" s="216"/>
+      <c r="L110" s="216"/>
+      <c r="M110" s="216"/>
+      <c r="N110" s="216"/>
+      <c r="O110" s="217"/>
+      <c r="P110" s="218" cm="1">
         <f t="array" ref="P110">SUMPRODUCT($D111:$O111, 2^(COLUMN($O111)-COLUMN($D111:$O111)))</f>
         <v>1445</v>
       </c>
-      <c r="Q110" s="187" t="str">
+      <c r="Q110" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P110, 3)</f>
         <v>0x5A5</v>
       </c>
-      <c r="R110" s="183"/>
+      <c r="R110" s="178"/>
     </row>
     <row r="111" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A111" s="209"/>
-      <c r="B111" s="211"/>
-      <c r="C111" s="181"/>
+      <c r="A111" s="212"/>
+      <c r="B111" s="214"/>
+      <c r="C111" s="186"/>
       <c r="D111" s="20">
         <v>0</v>
       </c>
@@ -16106,38 +16106,38 @@
       <c r="O111" s="92">
         <v>1</v>
       </c>
-      <c r="P111" s="216"/>
-      <c r="Q111" s="188"/>
-      <c r="R111" s="184"/>
+      <c r="P111" s="219"/>
+      <c r="Q111" s="191"/>
+      <c r="R111" s="179"/>
     </row>
     <row r="112" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A112" s="246" t="s">
+      <c r="A112" s="251" t="s">
         <v>72</v>
       </c>
-      <c r="B112" s="247"/>
-      <c r="C112" s="247"/>
-      <c r="D112" s="247"/>
-      <c r="E112" s="247"/>
-      <c r="F112" s="247"/>
-      <c r="G112" s="247"/>
-      <c r="H112" s="247"/>
-      <c r="I112" s="247"/>
-      <c r="J112" s="247"/>
-      <c r="K112" s="247"/>
-      <c r="L112" s="247"/>
-      <c r="M112" s="247"/>
-      <c r="N112" s="247"/>
-      <c r="O112" s="247"/>
-      <c r="P112" s="247"/>
-      <c r="Q112" s="247"/>
-      <c r="R112" s="248"/>
+      <c r="B112" s="252"/>
+      <c r="C112" s="252"/>
+      <c r="D112" s="252"/>
+      <c r="E112" s="252"/>
+      <c r="F112" s="252"/>
+      <c r="G112" s="252"/>
+      <c r="H112" s="252"/>
+      <c r="I112" s="252"/>
+      <c r="J112" s="252"/>
+      <c r="K112" s="252"/>
+      <c r="L112" s="252"/>
+      <c r="M112" s="252"/>
+      <c r="N112" s="252"/>
+      <c r="O112" s="252"/>
+      <c r="P112" s="252"/>
+      <c r="Q112" s="252"/>
+      <c r="R112" s="253"/>
     </row>
     <row r="113" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="18"/>
-      <c r="B113" s="178" t="s">
+      <c r="B113" s="183" t="s">
         <v>71</v>
       </c>
-      <c r="C113" s="180" t="s">
+      <c r="C113" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D113" s="14" t="s">
@@ -16152,30 +16152,30 @@
       <c r="G113" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H113" s="185" t="s">
+      <c r="H113" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="I113" s="185"/>
-      <c r="J113" s="185"/>
-      <c r="K113" s="185"/>
-      <c r="L113" s="185"/>
-      <c r="M113" s="185"/>
-      <c r="N113" s="185"/>
-      <c r="O113" s="185"/>
-      <c r="P113" s="189" cm="1">
+      <c r="I113" s="188"/>
+      <c r="J113" s="188"/>
+      <c r="K113" s="188"/>
+      <c r="L113" s="188"/>
+      <c r="M113" s="188"/>
+      <c r="N113" s="188"/>
+      <c r="O113" s="188"/>
+      <c r="P113" s="192" cm="1">
         <f t="array" ref="P113">SUMPRODUCT($D114:$O114, 2^(COLUMN($O114)-COLUMN($D114:$O114)))</f>
         <v>0</v>
       </c>
-      <c r="Q113" s="191" t="str">
+      <c r="Q113" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P113, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R113" s="183"/>
+      <c r="R113" s="178"/>
     </row>
     <row r="114" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A114" s="13"/>
-      <c r="B114" s="182"/>
-      <c r="C114" s="181"/>
+      <c r="B114" s="187"/>
+      <c r="C114" s="186"/>
       <c r="D114" s="17">
         <v>0</v>
       </c>
@@ -16212,16 +16212,16 @@
       <c r="O114" s="16">
         <v>0</v>
       </c>
-      <c r="P114" s="202"/>
-      <c r="Q114" s="207"/>
-      <c r="R114" s="184"/>
+      <c r="P114" s="205"/>
+      <c r="Q114" s="210"/>
+      <c r="R114" s="179"/>
     </row>
     <row r="115" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="13"/>
-      <c r="B115" s="178" t="s">
+      <c r="B115" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="C115" s="180" t="s">
+      <c r="C115" s="185" t="s">
         <v>65</v>
       </c>
       <c r="D115" s="14" t="s">
@@ -16230,34 +16230,34 @@
       <c r="E115" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F115" s="185" t="s">
+      <c r="F115" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="G115" s="185"/>
-      <c r="H115" s="185"/>
-      <c r="I115" s="185"/>
-      <c r="J115" s="185"/>
-      <c r="K115" s="185" t="s">
+      <c r="G115" s="188"/>
+      <c r="H115" s="188"/>
+      <c r="I115" s="188"/>
+      <c r="J115" s="188"/>
+      <c r="K115" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="L115" s="185"/>
-      <c r="M115" s="185"/>
-      <c r="N115" s="185"/>
-      <c r="O115" s="185"/>
-      <c r="P115" s="189" cm="1">
+      <c r="L115" s="188"/>
+      <c r="M115" s="188"/>
+      <c r="N115" s="188"/>
+      <c r="O115" s="188"/>
+      <c r="P115" s="192" cm="1">
         <f t="array" ref="P115">SUMPRODUCT($D116:$O116, 2^(COLUMN($O116)-COLUMN($D116:$O116)))</f>
         <v>528</v>
       </c>
-      <c r="Q115" s="187" t="str">
+      <c r="Q115" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P115, 3)</f>
         <v>0x210</v>
       </c>
-      <c r="R115" s="183"/>
+      <c r="R115" s="178"/>
     </row>
     <row r="116" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A116" s="13"/>
-      <c r="B116" s="179"/>
-      <c r="C116" s="181"/>
+      <c r="B116" s="184"/>
+      <c r="C116" s="186"/>
       <c r="D116" s="11">
         <v>0</v>
       </c>
@@ -16294,16 +16294,16 @@
       <c r="O116" s="10">
         <v>0</v>
       </c>
-      <c r="P116" s="190"/>
-      <c r="Q116" s="188"/>
-      <c r="R116" s="184"/>
+      <c r="P116" s="193"/>
+      <c r="Q116" s="191"/>
+      <c r="R116" s="179"/>
     </row>
     <row r="117" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="13"/>
-      <c r="B117" s="178" t="s">
+      <c r="B117" s="183" t="s">
         <v>66</v>
       </c>
-      <c r="C117" s="180" t="s">
+      <c r="C117" s="185" t="s">
         <v>65</v>
       </c>
       <c r="D117" s="14" t="s">
@@ -16312,34 +16312,34 @@
       <c r="E117" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F117" s="185" t="s">
+      <c r="F117" s="188" t="s">
         <v>64</v>
       </c>
-      <c r="G117" s="185"/>
-      <c r="H117" s="185"/>
-      <c r="I117" s="185"/>
-      <c r="J117" s="185"/>
-      <c r="K117" s="185" t="s">
+      <c r="G117" s="188"/>
+      <c r="H117" s="188"/>
+      <c r="I117" s="188"/>
+      <c r="J117" s="188"/>
+      <c r="K117" s="188" t="s">
         <v>63</v>
       </c>
-      <c r="L117" s="185"/>
-      <c r="M117" s="185"/>
-      <c r="N117" s="185"/>
-      <c r="O117" s="185"/>
-      <c r="P117" s="189" cm="1">
+      <c r="L117" s="188"/>
+      <c r="M117" s="188"/>
+      <c r="N117" s="188"/>
+      <c r="O117" s="188"/>
+      <c r="P117" s="192" cm="1">
         <f t="array" ref="P117">SUMPRODUCT($D118:$O118, 2^(COLUMN($O118)-COLUMN($D118:$O118)))</f>
         <v>528</v>
       </c>
-      <c r="Q117" s="187" t="str">
+      <c r="Q117" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P117, 3)</f>
         <v>0x210</v>
       </c>
-      <c r="R117" s="183"/>
+      <c r="R117" s="178"/>
     </row>
     <row r="118" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A118" s="13"/>
-      <c r="B118" s="179"/>
-      <c r="C118" s="181"/>
+      <c r="B118" s="184"/>
+      <c r="C118" s="186"/>
       <c r="D118" s="11">
         <v>0</v>
       </c>
@@ -16376,24 +16376,24 @@
       <c r="O118" s="10">
         <v>0</v>
       </c>
-      <c r="P118" s="190"/>
-      <c r="Q118" s="188"/>
-      <c r="R118" s="184"/>
+      <c r="P118" s="193"/>
+      <c r="Q118" s="191"/>
+      <c r="R118" s="179"/>
     </row>
     <row r="119" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="13"/>
-      <c r="B119" s="178" t="s">
+      <c r="B119" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="C119" s="180" t="s">
+      <c r="C119" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="D119" s="196" t="s">
+      <c r="D119" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="E119" s="197"/>
-      <c r="F119" s="197"/>
-      <c r="G119" s="198"/>
+      <c r="E119" s="200"/>
+      <c r="F119" s="200"/>
+      <c r="G119" s="201"/>
       <c r="H119" s="14" t="s">
         <v>1</v>
       </c>
@@ -16403,27 +16403,27 @@
       <c r="J119" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K119" s="218" t="s">
+      <c r="K119" s="221" t="s">
         <v>60</v>
       </c>
-      <c r="L119" s="218"/>
-      <c r="M119" s="218"/>
-      <c r="N119" s="218"/>
-      <c r="O119" s="218"/>
-      <c r="P119" s="202" cm="1">
+      <c r="L119" s="221"/>
+      <c r="M119" s="221"/>
+      <c r="N119" s="221"/>
+      <c r="O119" s="221"/>
+      <c r="P119" s="205" cm="1">
         <f t="array" ref="P119">SUMPRODUCT($D120:$O120, 2^(COLUMN($O120)-COLUMN($D120:$O120)))</f>
         <v>2064</v>
       </c>
-      <c r="Q119" s="203" t="str">
+      <c r="Q119" s="206" t="str">
         <f>"0x"&amp;DEC2HEX($P119, 3)</f>
         <v>0x810</v>
       </c>
-      <c r="R119" s="183"/>
+      <c r="R119" s="178"/>
     </row>
     <row r="120" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A120" s="13"/>
-      <c r="B120" s="179"/>
-      <c r="C120" s="181"/>
+      <c r="B120" s="184"/>
+      <c r="C120" s="186"/>
       <c r="D120" s="96">
         <v>1</v>
       </c>
@@ -16460,52 +16460,52 @@
       <c r="O120" s="10">
         <v>0</v>
       </c>
-      <c r="P120" s="190"/>
-      <c r="Q120" s="188"/>
-      <c r="R120" s="184"/>
+      <c r="P120" s="193"/>
+      <c r="Q120" s="191"/>
+      <c r="R120" s="179"/>
     </row>
     <row r="121" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="13"/>
-      <c r="B121" s="178" t="s">
+      <c r="B121" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="C121" s="180" t="s">
+      <c r="C121" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="D121" s="193" t="s">
+      <c r="D121" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="E121" s="194"/>
-      <c r="F121" s="194"/>
-      <c r="G121" s="194"/>
-      <c r="H121" s="195"/>
+      <c r="E121" s="197"/>
+      <c r="F121" s="197"/>
+      <c r="G121" s="197"/>
+      <c r="H121" s="198"/>
       <c r="I121" s="14" t="s">
         <v>1</v>
       </c>
       <c r="J121" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K121" s="193" t="s">
+      <c r="K121" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="L121" s="194"/>
-      <c r="M121" s="194"/>
-      <c r="N121" s="194"/>
-      <c r="O121" s="195"/>
-      <c r="P121" s="189" cm="1">
+      <c r="L121" s="197"/>
+      <c r="M121" s="197"/>
+      <c r="N121" s="197"/>
+      <c r="O121" s="198"/>
+      <c r="P121" s="192" cm="1">
         <f t="array" ref="P121">SUMPRODUCT($D122:$O122, 2^(COLUMN($O122)-COLUMN($D122:$O122)))</f>
         <v>2064</v>
       </c>
-      <c r="Q121" s="187" t="str">
+      <c r="Q121" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P121, 3)</f>
         <v>0x810</v>
       </c>
-      <c r="R121" s="183"/>
+      <c r="R121" s="178"/>
     </row>
     <row r="122" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A122" s="13"/>
-      <c r="B122" s="179"/>
-      <c r="C122" s="181"/>
+      <c r="B122" s="184"/>
+      <c r="C122" s="186"/>
       <c r="D122" s="96">
         <v>1</v>
       </c>
@@ -16542,16 +16542,16 @@
       <c r="O122" s="10">
         <v>0</v>
       </c>
-      <c r="P122" s="190"/>
-      <c r="Q122" s="188"/>
-      <c r="R122" s="184"/>
+      <c r="P122" s="193"/>
+      <c r="Q122" s="191"/>
+      <c r="R122" s="179"/>
     </row>
     <row r="123" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="13"/>
-      <c r="B123" s="178" t="s">
+      <c r="B123" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="C123" s="180" t="s">
+      <c r="C123" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D123" s="14" t="s">
@@ -16566,32 +16566,32 @@
       <c r="G123" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H123" s="186" t="s">
+      <c r="H123" s="189" t="s">
         <v>54</v>
       </c>
-      <c r="I123" s="186"/>
-      <c r="J123" s="186"/>
-      <c r="K123" s="186"/>
-      <c r="L123" s="186" t="s">
+      <c r="I123" s="189"/>
+      <c r="J123" s="189"/>
+      <c r="K123" s="189"/>
+      <c r="L123" s="189" t="s">
         <v>53</v>
       </c>
-      <c r="M123" s="186"/>
-      <c r="N123" s="186"/>
-      <c r="O123" s="186"/>
-      <c r="P123" s="189" cm="1">
+      <c r="M123" s="189"/>
+      <c r="N123" s="189"/>
+      <c r="O123" s="189"/>
+      <c r="P123" s="192" cm="1">
         <f t="array" ref="P123">SUMPRODUCT($D124:$O124, 2^(COLUMN($O124)-COLUMN($D124:$O124)))</f>
         <v>128</v>
       </c>
-      <c r="Q123" s="187" t="str">
+      <c r="Q123" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P123, 3)</f>
         <v>0x080</v>
       </c>
-      <c r="R123" s="183"/>
+      <c r="R123" s="178"/>
     </row>
     <row r="124" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A124" s="13"/>
-      <c r="B124" s="179"/>
-      <c r="C124" s="181"/>
+      <c r="B124" s="184"/>
+      <c r="C124" s="186"/>
       <c r="D124" s="17">
         <v>0</v>
       </c>
@@ -16628,16 +16628,16 @@
       <c r="O124" s="16">
         <v>0</v>
       </c>
-      <c r="P124" s="202"/>
-      <c r="Q124" s="203"/>
-      <c r="R124" s="184"/>
+      <c r="P124" s="205"/>
+      <c r="Q124" s="206"/>
+      <c r="R124" s="179"/>
     </row>
     <row r="125" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="13"/>
-      <c r="B125" s="178" t="s">
+      <c r="B125" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="C125" s="180" t="s">
+      <c r="C125" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D125" s="15" t="s">
@@ -16649,31 +16649,31 @@
       <c r="F125" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G125" s="199" t="s">
+      <c r="G125" s="202" t="s">
         <v>51</v>
       </c>
-      <c r="H125" s="200"/>
-      <c r="I125" s="200"/>
-      <c r="J125" s="200"/>
-      <c r="K125" s="200"/>
-      <c r="L125" s="200"/>
-      <c r="M125" s="200"/>
-      <c r="N125" s="200"/>
-      <c r="O125" s="201"/>
-      <c r="P125" s="189" cm="1">
+      <c r="H125" s="203"/>
+      <c r="I125" s="203"/>
+      <c r="J125" s="203"/>
+      <c r="K125" s="203"/>
+      <c r="L125" s="203"/>
+      <c r="M125" s="203"/>
+      <c r="N125" s="203"/>
+      <c r="O125" s="204"/>
+      <c r="P125" s="192" cm="1">
         <f t="array" ref="P125">SUMPRODUCT($D126:$O126, 2^(COLUMN($O126)-COLUMN($D126:$O126)))</f>
         <v>0</v>
       </c>
-      <c r="Q125" s="191" t="str">
+      <c r="Q125" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P125, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R125" s="183"/>
+      <c r="R125" s="178"/>
     </row>
     <row r="126" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A126" s="13"/>
-      <c r="B126" s="179"/>
-      <c r="C126" s="181"/>
+      <c r="B126" s="184"/>
+      <c r="C126" s="186"/>
       <c r="D126" s="12">
         <v>0</v>
       </c>
@@ -16710,16 +16710,16 @@
       <c r="O126" s="10">
         <v>0</v>
       </c>
-      <c r="P126" s="190"/>
-      <c r="Q126" s="192"/>
-      <c r="R126" s="184"/>
+      <c r="P126" s="193"/>
+      <c r="Q126" s="195"/>
+      <c r="R126" s="179"/>
     </row>
     <row r="127" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="13"/>
-      <c r="B127" s="178" t="s">
+      <c r="B127" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="C127" s="180" t="s">
+      <c r="C127" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D127" s="15" t="s">
@@ -16731,31 +16731,31 @@
       <c r="F127" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G127" s="199" t="s">
+      <c r="G127" s="202" t="s">
         <v>49</v>
       </c>
-      <c r="H127" s="200"/>
-      <c r="I127" s="200"/>
-      <c r="J127" s="200"/>
-      <c r="K127" s="200"/>
-      <c r="L127" s="200"/>
-      <c r="M127" s="200"/>
-      <c r="N127" s="200"/>
-      <c r="O127" s="201"/>
-      <c r="P127" s="189" cm="1">
+      <c r="H127" s="203"/>
+      <c r="I127" s="203"/>
+      <c r="J127" s="203"/>
+      <c r="K127" s="203"/>
+      <c r="L127" s="203"/>
+      <c r="M127" s="203"/>
+      <c r="N127" s="203"/>
+      <c r="O127" s="204"/>
+      <c r="P127" s="192" cm="1">
         <f t="array" ref="P127">SUMPRODUCT($D128:$O128, 2^(COLUMN($O128)-COLUMN($D128:$O128)))</f>
         <v>0</v>
       </c>
-      <c r="Q127" s="191" t="str">
+      <c r="Q127" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P127, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R127" s="183"/>
+      <c r="R127" s="178"/>
     </row>
     <row r="128" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A128" s="13"/>
-      <c r="B128" s="179"/>
-      <c r="C128" s="181"/>
+      <c r="B128" s="184"/>
+      <c r="C128" s="186"/>
       <c r="D128" s="12">
         <v>0</v>
       </c>
@@ -16792,16 +16792,16 @@
       <c r="O128" s="10">
         <v>0</v>
       </c>
-      <c r="P128" s="190"/>
-      <c r="Q128" s="192"/>
-      <c r="R128" s="184"/>
+      <c r="P128" s="193"/>
+      <c r="Q128" s="195"/>
+      <c r="R128" s="179"/>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A129" s="13"/>
-      <c r="B129" s="178" t="s">
+      <c r="B129" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="C129" s="180" t="s">
+      <c r="C129" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D129" s="15" t="s">
@@ -16813,31 +16813,31 @@
       <c r="F129" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G129" s="199" t="s">
+      <c r="G129" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="H129" s="200"/>
-      <c r="I129" s="200"/>
-      <c r="J129" s="200"/>
-      <c r="K129" s="200"/>
-      <c r="L129" s="200"/>
-      <c r="M129" s="200"/>
-      <c r="N129" s="200"/>
-      <c r="O129" s="201"/>
-      <c r="P129" s="189" cm="1">
+      <c r="H129" s="203"/>
+      <c r="I129" s="203"/>
+      <c r="J129" s="203"/>
+      <c r="K129" s="203"/>
+      <c r="L129" s="203"/>
+      <c r="M129" s="203"/>
+      <c r="N129" s="203"/>
+      <c r="O129" s="204"/>
+      <c r="P129" s="192" cm="1">
         <f t="array" ref="P129">SUMPRODUCT($D130:$O130, 2^(COLUMN($O130)-COLUMN($D130:$O130)))</f>
         <v>0</v>
       </c>
-      <c r="Q129" s="191" t="str">
+      <c r="Q129" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P129, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R129" s="183"/>
+      <c r="R129" s="178"/>
     </row>
     <row r="130" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A130" s="13"/>
-      <c r="B130" s="179"/>
-      <c r="C130" s="181"/>
+      <c r="B130" s="184"/>
+      <c r="C130" s="186"/>
       <c r="D130" s="12">
         <v>0</v>
       </c>
@@ -16874,16 +16874,16 @@
       <c r="O130" s="10">
         <v>0</v>
       </c>
-      <c r="P130" s="190"/>
-      <c r="Q130" s="192"/>
-      <c r="R130" s="184"/>
+      <c r="P130" s="193"/>
+      <c r="Q130" s="195"/>
+      <c r="R130" s="179"/>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A131" s="13"/>
-      <c r="B131" s="178" t="s">
+      <c r="B131" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="C131" s="180" t="s">
+      <c r="C131" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="15" t="s">
@@ -16895,31 +16895,31 @@
       <c r="F131" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G131" s="199" t="s">
+      <c r="G131" s="202" t="s">
         <v>45</v>
       </c>
-      <c r="H131" s="200"/>
-      <c r="I131" s="200"/>
-      <c r="J131" s="200"/>
-      <c r="K131" s="200"/>
-      <c r="L131" s="200"/>
-      <c r="M131" s="200"/>
-      <c r="N131" s="200"/>
-      <c r="O131" s="201"/>
-      <c r="P131" s="189" cm="1">
+      <c r="H131" s="203"/>
+      <c r="I131" s="203"/>
+      <c r="J131" s="203"/>
+      <c r="K131" s="203"/>
+      <c r="L131" s="203"/>
+      <c r="M131" s="203"/>
+      <c r="N131" s="203"/>
+      <c r="O131" s="204"/>
+      <c r="P131" s="192" cm="1">
         <f t="array" ref="P131">SUMPRODUCT($D132:$O132, 2^(COLUMN($O132)-COLUMN($D132:$O132)))</f>
         <v>0</v>
       </c>
-      <c r="Q131" s="191" t="str">
+      <c r="Q131" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P131, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R131" s="183"/>
+      <c r="R131" s="178"/>
     </row>
     <row r="132" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A132" s="13"/>
-      <c r="B132" s="179"/>
-      <c r="C132" s="181"/>
+      <c r="B132" s="184"/>
+      <c r="C132" s="186"/>
       <c r="D132" s="12">
         <v>0</v>
       </c>
@@ -16956,16 +16956,16 @@
       <c r="O132" s="10">
         <v>0</v>
       </c>
-      <c r="P132" s="190"/>
-      <c r="Q132" s="192"/>
-      <c r="R132" s="184"/>
+      <c r="P132" s="193"/>
+      <c r="Q132" s="195"/>
+      <c r="R132" s="179"/>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A133" s="13"/>
-      <c r="B133" s="178" t="s">
+      <c r="B133" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="C133" s="180" t="s">
+      <c r="C133" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D133" s="15" t="s">
@@ -16977,31 +16977,31 @@
       <c r="F133" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G133" s="199" t="s">
+      <c r="G133" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="H133" s="200"/>
-      <c r="I133" s="200"/>
-      <c r="J133" s="200"/>
-      <c r="K133" s="200"/>
-      <c r="L133" s="200"/>
-      <c r="M133" s="200"/>
-      <c r="N133" s="200"/>
-      <c r="O133" s="201"/>
-      <c r="P133" s="189" cm="1">
+      <c r="H133" s="203"/>
+      <c r="I133" s="203"/>
+      <c r="J133" s="203"/>
+      <c r="K133" s="203"/>
+      <c r="L133" s="203"/>
+      <c r="M133" s="203"/>
+      <c r="N133" s="203"/>
+      <c r="O133" s="204"/>
+      <c r="P133" s="192" cm="1">
         <f t="array" ref="P133">SUMPRODUCT($D134:$O134, 2^(COLUMN($O134)-COLUMN($D134:$O134)))</f>
         <v>0</v>
       </c>
-      <c r="Q133" s="191" t="str">
+      <c r="Q133" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P133, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R133" s="183"/>
+      <c r="R133" s="178"/>
     </row>
     <row r="134" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A134" s="13"/>
-      <c r="B134" s="179"/>
-      <c r="C134" s="181"/>
+      <c r="B134" s="184"/>
+      <c r="C134" s="186"/>
       <c r="D134" s="12">
         <v>0</v>
       </c>
@@ -17038,16 +17038,16 @@
       <c r="O134" s="10">
         <v>0</v>
       </c>
-      <c r="P134" s="190"/>
-      <c r="Q134" s="192"/>
-      <c r="R134" s="184"/>
+      <c r="P134" s="193"/>
+      <c r="Q134" s="195"/>
+      <c r="R134" s="179"/>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A135" s="13"/>
-      <c r="B135" s="178" t="s">
+      <c r="B135" s="183" t="s">
         <v>42</v>
       </c>
-      <c r="C135" s="180" t="s">
+      <c r="C135" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D135" s="15" t="s">
@@ -17059,31 +17059,31 @@
       <c r="F135" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G135" s="199" t="s">
+      <c r="G135" s="202" t="s">
         <v>41</v>
       </c>
-      <c r="H135" s="200"/>
-      <c r="I135" s="200"/>
-      <c r="J135" s="200"/>
-      <c r="K135" s="200"/>
-      <c r="L135" s="200"/>
-      <c r="M135" s="200"/>
-      <c r="N135" s="200"/>
-      <c r="O135" s="201"/>
-      <c r="P135" s="189" cm="1">
+      <c r="H135" s="203"/>
+      <c r="I135" s="203"/>
+      <c r="J135" s="203"/>
+      <c r="K135" s="203"/>
+      <c r="L135" s="203"/>
+      <c r="M135" s="203"/>
+      <c r="N135" s="203"/>
+      <c r="O135" s="204"/>
+      <c r="P135" s="192" cm="1">
         <f t="array" ref="P135">SUMPRODUCT($D136:$O136, 2^(COLUMN($O136)-COLUMN($D136:$O136)))</f>
         <v>0</v>
       </c>
-      <c r="Q135" s="191" t="str">
+      <c r="Q135" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P135, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R135" s="183"/>
+      <c r="R135" s="178"/>
     </row>
     <row r="136" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A136" s="13"/>
-      <c r="B136" s="179"/>
-      <c r="C136" s="181"/>
+      <c r="B136" s="184"/>
+      <c r="C136" s="186"/>
       <c r="D136" s="12">
         <v>0</v>
       </c>
@@ -17120,16 +17120,16 @@
       <c r="O136" s="10">
         <v>0</v>
       </c>
-      <c r="P136" s="190"/>
-      <c r="Q136" s="192"/>
-      <c r="R136" s="184"/>
+      <c r="P136" s="193"/>
+      <c r="Q136" s="195"/>
+      <c r="R136" s="179"/>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A137" s="13"/>
-      <c r="B137" s="178" t="s">
+      <c r="B137" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="C137" s="180" t="s">
+      <c r="C137" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D137" s="15" t="s">
@@ -17141,31 +17141,31 @@
       <c r="F137" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G137" s="199" t="s">
+      <c r="G137" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="H137" s="200"/>
-      <c r="I137" s="200"/>
-      <c r="J137" s="200"/>
-      <c r="K137" s="200"/>
-      <c r="L137" s="200"/>
-      <c r="M137" s="200"/>
-      <c r="N137" s="200"/>
-      <c r="O137" s="201"/>
-      <c r="P137" s="189" cm="1">
+      <c r="H137" s="203"/>
+      <c r="I137" s="203"/>
+      <c r="J137" s="203"/>
+      <c r="K137" s="203"/>
+      <c r="L137" s="203"/>
+      <c r="M137" s="203"/>
+      <c r="N137" s="203"/>
+      <c r="O137" s="204"/>
+      <c r="P137" s="192" cm="1">
         <f t="array" ref="P137">SUMPRODUCT($D138:$O138, 2^(COLUMN($O138)-COLUMN($D138:$O138)))</f>
         <v>0</v>
       </c>
-      <c r="Q137" s="191" t="str">
+      <c r="Q137" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P137, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R137" s="183"/>
+      <c r="R137" s="178"/>
     </row>
     <row r="138" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A138" s="13"/>
-      <c r="B138" s="179"/>
-      <c r="C138" s="181"/>
+      <c r="B138" s="184"/>
+      <c r="C138" s="186"/>
       <c r="D138" s="12">
         <v>0</v>
       </c>
@@ -17202,16 +17202,16 @@
       <c r="O138" s="10">
         <v>0</v>
       </c>
-      <c r="P138" s="190"/>
-      <c r="Q138" s="192"/>
-      <c r="R138" s="184"/>
+      <c r="P138" s="193"/>
+      <c r="Q138" s="195"/>
+      <c r="R138" s="179"/>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A139" s="13"/>
-      <c r="B139" s="178" t="s">
+      <c r="B139" s="183" t="s">
         <v>38</v>
       </c>
-      <c r="C139" s="180" t="s">
+      <c r="C139" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D139" s="15" t="s">
@@ -17223,31 +17223,31 @@
       <c r="F139" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G139" s="199" t="s">
+      <c r="G139" s="202" t="s">
         <v>37</v>
       </c>
-      <c r="H139" s="200"/>
-      <c r="I139" s="200"/>
-      <c r="J139" s="200"/>
-      <c r="K139" s="200"/>
-      <c r="L139" s="200"/>
-      <c r="M139" s="200"/>
-      <c r="N139" s="200"/>
-      <c r="O139" s="201"/>
-      <c r="P139" s="189" cm="1">
+      <c r="H139" s="203"/>
+      <c r="I139" s="203"/>
+      <c r="J139" s="203"/>
+      <c r="K139" s="203"/>
+      <c r="L139" s="203"/>
+      <c r="M139" s="203"/>
+      <c r="N139" s="203"/>
+      <c r="O139" s="204"/>
+      <c r="P139" s="192" cm="1">
         <f t="array" ref="P139">SUMPRODUCT($D140:$O140, 2^(COLUMN($O140)-COLUMN($D140:$O140)))</f>
         <v>0</v>
       </c>
-      <c r="Q139" s="191" t="str">
+      <c r="Q139" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P139, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R139" s="183"/>
+      <c r="R139" s="178"/>
     </row>
     <row r="140" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A140" s="13"/>
-      <c r="B140" s="179"/>
-      <c r="C140" s="181"/>
+      <c r="B140" s="184"/>
+      <c r="C140" s="186"/>
       <c r="D140" s="12">
         <v>0</v>
       </c>
@@ -17284,16 +17284,16 @@
       <c r="O140" s="10">
         <v>0</v>
       </c>
-      <c r="P140" s="190"/>
-      <c r="Q140" s="192"/>
-      <c r="R140" s="184"/>
+      <c r="P140" s="193"/>
+      <c r="Q140" s="195"/>
+      <c r="R140" s="179"/>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A141" s="13"/>
-      <c r="B141" s="178" t="s">
+      <c r="B141" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="C141" s="180" t="s">
+      <c r="C141" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D141" s="15" t="s">
@@ -17305,31 +17305,31 @@
       <c r="F141" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G141" s="199" t="s">
+      <c r="G141" s="202" t="s">
         <v>35</v>
       </c>
-      <c r="H141" s="200"/>
-      <c r="I141" s="200"/>
-      <c r="J141" s="200"/>
-      <c r="K141" s="200"/>
-      <c r="L141" s="200"/>
-      <c r="M141" s="200"/>
-      <c r="N141" s="200"/>
-      <c r="O141" s="201"/>
-      <c r="P141" s="189" cm="1">
+      <c r="H141" s="203"/>
+      <c r="I141" s="203"/>
+      <c r="J141" s="203"/>
+      <c r="K141" s="203"/>
+      <c r="L141" s="203"/>
+      <c r="M141" s="203"/>
+      <c r="N141" s="203"/>
+      <c r="O141" s="204"/>
+      <c r="P141" s="192" cm="1">
         <f t="array" ref="P141">SUMPRODUCT($D142:$O142, 2^(COLUMN($O142)-COLUMN($D142:$O142)))</f>
         <v>0</v>
       </c>
-      <c r="Q141" s="191" t="str">
+      <c r="Q141" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P141, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R141" s="183"/>
+      <c r="R141" s="178"/>
     </row>
     <row r="142" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A142" s="13"/>
-      <c r="B142" s="179"/>
-      <c r="C142" s="181"/>
+      <c r="B142" s="184"/>
+      <c r="C142" s="186"/>
       <c r="D142" s="12">
         <v>0</v>
       </c>
@@ -17366,16 +17366,16 @@
       <c r="O142" s="10">
         <v>0</v>
       </c>
-      <c r="P142" s="190"/>
-      <c r="Q142" s="192"/>
-      <c r="R142" s="184"/>
+      <c r="P142" s="193"/>
+      <c r="Q142" s="195"/>
+      <c r="R142" s="179"/>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A143" s="13"/>
-      <c r="B143" s="178" t="s">
+      <c r="B143" s="183" t="s">
         <v>34</v>
       </c>
-      <c r="C143" s="180" t="s">
+      <c r="C143" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D143" s="15" t="s">
@@ -17387,31 +17387,31 @@
       <c r="F143" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G143" s="199" t="s">
+      <c r="G143" s="202" t="s">
         <v>33</v>
       </c>
-      <c r="H143" s="200"/>
-      <c r="I143" s="200"/>
-      <c r="J143" s="200"/>
-      <c r="K143" s="200"/>
-      <c r="L143" s="200"/>
-      <c r="M143" s="200"/>
-      <c r="N143" s="200"/>
-      <c r="O143" s="201"/>
-      <c r="P143" s="189" cm="1">
+      <c r="H143" s="203"/>
+      <c r="I143" s="203"/>
+      <c r="J143" s="203"/>
+      <c r="K143" s="203"/>
+      <c r="L143" s="203"/>
+      <c r="M143" s="203"/>
+      <c r="N143" s="203"/>
+      <c r="O143" s="204"/>
+      <c r="P143" s="192" cm="1">
         <f t="array" ref="P143">SUMPRODUCT($D144:$O144, 2^(COLUMN($O144)-COLUMN($D144:$O144)))</f>
         <v>0</v>
       </c>
-      <c r="Q143" s="191" t="str">
+      <c r="Q143" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P143, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R143" s="183"/>
+      <c r="R143" s="178"/>
     </row>
     <row r="144" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A144" s="13"/>
-      <c r="B144" s="179"/>
-      <c r="C144" s="181"/>
+      <c r="B144" s="184"/>
+      <c r="C144" s="186"/>
       <c r="D144" s="12">
         <v>0</v>
       </c>
@@ -17448,16 +17448,16 @@
       <c r="O144" s="10">
         <v>0</v>
       </c>
-      <c r="P144" s="190"/>
-      <c r="Q144" s="192"/>
-      <c r="R144" s="184"/>
+      <c r="P144" s="193"/>
+      <c r="Q144" s="195"/>
+      <c r="R144" s="179"/>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A145" s="13"/>
-      <c r="B145" s="178" t="s">
+      <c r="B145" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="C145" s="180" t="s">
+      <c r="C145" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D145" s="15" t="s">
@@ -17469,31 +17469,31 @@
       <c r="F145" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G145" s="199" t="s">
+      <c r="G145" s="202" t="s">
         <v>31</v>
       </c>
-      <c r="H145" s="200"/>
-      <c r="I145" s="200"/>
-      <c r="J145" s="200"/>
-      <c r="K145" s="200"/>
-      <c r="L145" s="200"/>
-      <c r="M145" s="200"/>
-      <c r="N145" s="200"/>
-      <c r="O145" s="201"/>
-      <c r="P145" s="189" cm="1">
+      <c r="H145" s="203"/>
+      <c r="I145" s="203"/>
+      <c r="J145" s="203"/>
+      <c r="K145" s="203"/>
+      <c r="L145" s="203"/>
+      <c r="M145" s="203"/>
+      <c r="N145" s="203"/>
+      <c r="O145" s="204"/>
+      <c r="P145" s="192" cm="1">
         <f t="array" ref="P145">SUMPRODUCT($D146:$O146, 2^(COLUMN($O146)-COLUMN($D146:$O146)))</f>
         <v>0</v>
       </c>
-      <c r="Q145" s="191" t="str">
+      <c r="Q145" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P145, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R145" s="183"/>
+      <c r="R145" s="178"/>
     </row>
     <row r="146" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A146" s="13"/>
-      <c r="B146" s="179"/>
-      <c r="C146" s="181"/>
+      <c r="B146" s="184"/>
+      <c r="C146" s="186"/>
       <c r="D146" s="12">
         <v>0</v>
       </c>
@@ -17530,16 +17530,16 @@
       <c r="O146" s="10">
         <v>0</v>
       </c>
-      <c r="P146" s="190"/>
-      <c r="Q146" s="192"/>
-      <c r="R146" s="184"/>
+      <c r="P146" s="193"/>
+      <c r="Q146" s="195"/>
+      <c r="R146" s="179"/>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A147" s="13"/>
-      <c r="B147" s="178" t="s">
+      <c r="B147" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="C147" s="180" t="s">
+      <c r="C147" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D147" s="15" t="s">
@@ -17551,31 +17551,31 @@
       <c r="F147" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G147" s="199" t="s">
+      <c r="G147" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="H147" s="200"/>
-      <c r="I147" s="200"/>
-      <c r="J147" s="200"/>
-      <c r="K147" s="200"/>
-      <c r="L147" s="200"/>
-      <c r="M147" s="200"/>
-      <c r="N147" s="200"/>
-      <c r="O147" s="201"/>
-      <c r="P147" s="189" cm="1">
+      <c r="H147" s="203"/>
+      <c r="I147" s="203"/>
+      <c r="J147" s="203"/>
+      <c r="K147" s="203"/>
+      <c r="L147" s="203"/>
+      <c r="M147" s="203"/>
+      <c r="N147" s="203"/>
+      <c r="O147" s="204"/>
+      <c r="P147" s="192" cm="1">
         <f t="array" ref="P147">SUMPRODUCT($D148:$O148, 2^(COLUMN($O148)-COLUMN($D148:$O148)))</f>
         <v>0</v>
       </c>
-      <c r="Q147" s="191" t="str">
+      <c r="Q147" s="194" t="str">
         <f>"0x"&amp;DEC2HEX($P147, 3)</f>
         <v>0x000</v>
       </c>
-      <c r="R147" s="183"/>
+      <c r="R147" s="178"/>
     </row>
     <row r="148" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A148" s="13"/>
-      <c r="B148" s="179"/>
-      <c r="C148" s="181"/>
+      <c r="B148" s="184"/>
+      <c r="C148" s="186"/>
       <c r="D148" s="12">
         <v>0</v>
       </c>
@@ -17612,16 +17612,16 @@
       <c r="O148" s="10">
         <v>0</v>
       </c>
-      <c r="P148" s="190"/>
-      <c r="Q148" s="192"/>
-      <c r="R148" s="184"/>
+      <c r="P148" s="193"/>
+      <c r="Q148" s="195"/>
+      <c r="R148" s="179"/>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A149" s="13"/>
-      <c r="B149" s="178" t="s">
+      <c r="B149" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="C149" s="180" t="s">
+      <c r="C149" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D149" s="15" t="s">
@@ -17639,29 +17639,29 @@
       <c r="H149" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I149" s="199" t="s">
+      <c r="I149" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="J149" s="200"/>
-      <c r="K149" s="200"/>
-      <c r="L149" s="200"/>
-      <c r="M149" s="200"/>
-      <c r="N149" s="200"/>
-      <c r="O149" s="201"/>
-      <c r="P149" s="189" cm="1">
+      <c r="J149" s="203"/>
+      <c r="K149" s="203"/>
+      <c r="L149" s="203"/>
+      <c r="M149" s="203"/>
+      <c r="N149" s="203"/>
+      <c r="O149" s="204"/>
+      <c r="P149" s="192" cm="1">
         <f t="array" ref="P149">SUMPRODUCT($D150:$O150, 2^(COLUMN($O150)-COLUMN($D150:$O150)))</f>
         <v>64</v>
       </c>
-      <c r="Q149" s="187" t="str">
+      <c r="Q149" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P149, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R149" s="183"/>
+      <c r="R149" s="178"/>
     </row>
     <row r="150" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A150" s="13"/>
-      <c r="B150" s="179"/>
-      <c r="C150" s="181"/>
+      <c r="B150" s="184"/>
+      <c r="C150" s="186"/>
       <c r="D150" s="12">
         <v>0</v>
       </c>
@@ -17698,16 +17698,16 @@
       <c r="O150" s="10">
         <v>0</v>
       </c>
-      <c r="P150" s="190"/>
-      <c r="Q150" s="188"/>
-      <c r="R150" s="184"/>
+      <c r="P150" s="193"/>
+      <c r="Q150" s="191"/>
+      <c r="R150" s="179"/>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A151" s="13"/>
-      <c r="B151" s="178" t="s">
+      <c r="B151" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="C151" s="180" t="s">
+      <c r="C151" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D151" s="15" t="s">
@@ -17725,29 +17725,29 @@
       <c r="H151" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I151" s="199" t="s">
+      <c r="I151" s="202" t="s">
         <v>25</v>
       </c>
-      <c r="J151" s="200"/>
-      <c r="K151" s="200"/>
-      <c r="L151" s="200"/>
-      <c r="M151" s="200"/>
-      <c r="N151" s="200"/>
-      <c r="O151" s="201"/>
-      <c r="P151" s="189" cm="1">
+      <c r="J151" s="203"/>
+      <c r="K151" s="203"/>
+      <c r="L151" s="203"/>
+      <c r="M151" s="203"/>
+      <c r="N151" s="203"/>
+      <c r="O151" s="204"/>
+      <c r="P151" s="192" cm="1">
         <f t="array" ref="P151">SUMPRODUCT($D152:$O152, 2^(COLUMN($O152)-COLUMN($D152:$O152)))</f>
         <v>64</v>
       </c>
-      <c r="Q151" s="187" t="str">
+      <c r="Q151" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P151, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R151" s="183"/>
+      <c r="R151" s="178"/>
     </row>
     <row r="152" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A152" s="13"/>
-      <c r="B152" s="179"/>
-      <c r="C152" s="181"/>
+      <c r="B152" s="184"/>
+      <c r="C152" s="186"/>
       <c r="D152" s="12">
         <v>0</v>
       </c>
@@ -17784,16 +17784,16 @@
       <c r="O152" s="10">
         <v>0</v>
       </c>
-      <c r="P152" s="190"/>
-      <c r="Q152" s="188"/>
-      <c r="R152" s="184"/>
+      <c r="P152" s="193"/>
+      <c r="Q152" s="191"/>
+      <c r="R152" s="179"/>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A153" s="13"/>
-      <c r="B153" s="178" t="s">
+      <c r="B153" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="C153" s="180" t="s">
+      <c r="C153" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D153" s="15" t="s">
@@ -17811,29 +17811,29 @@
       <c r="H153" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I153" s="199" t="s">
+      <c r="I153" s="202" t="s">
         <v>23</v>
       </c>
-      <c r="J153" s="200"/>
-      <c r="K153" s="200"/>
-      <c r="L153" s="200"/>
-      <c r="M153" s="200"/>
-      <c r="N153" s="200"/>
-      <c r="O153" s="201"/>
-      <c r="P153" s="189" cm="1">
+      <c r="J153" s="203"/>
+      <c r="K153" s="203"/>
+      <c r="L153" s="203"/>
+      <c r="M153" s="203"/>
+      <c r="N153" s="203"/>
+      <c r="O153" s="204"/>
+      <c r="P153" s="192" cm="1">
         <f t="array" ref="P153">SUMPRODUCT($D154:$O154, 2^(COLUMN($O154)-COLUMN($D154:$O154)))</f>
         <v>64</v>
       </c>
-      <c r="Q153" s="187" t="str">
+      <c r="Q153" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P153, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R153" s="183"/>
+      <c r="R153" s="178"/>
     </row>
     <row r="154" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A154" s="13"/>
-      <c r="B154" s="179"/>
-      <c r="C154" s="181"/>
+      <c r="B154" s="184"/>
+      <c r="C154" s="186"/>
       <c r="D154" s="12">
         <v>0</v>
       </c>
@@ -17870,16 +17870,16 @@
       <c r="O154" s="10">
         <v>0</v>
       </c>
-      <c r="P154" s="190"/>
-      <c r="Q154" s="188"/>
-      <c r="R154" s="184"/>
+      <c r="P154" s="193"/>
+      <c r="Q154" s="191"/>
+      <c r="R154" s="179"/>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A155" s="13"/>
-      <c r="B155" s="178" t="s">
+      <c r="B155" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="180" t="s">
+      <c r="C155" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D155" s="15" t="s">
@@ -17897,29 +17897,29 @@
       <c r="H155" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I155" s="199" t="s">
+      <c r="I155" s="202" t="s">
         <v>21</v>
       </c>
-      <c r="J155" s="200"/>
-      <c r="K155" s="200"/>
-      <c r="L155" s="200"/>
-      <c r="M155" s="200"/>
-      <c r="N155" s="200"/>
-      <c r="O155" s="201"/>
-      <c r="P155" s="189" cm="1">
+      <c r="J155" s="203"/>
+      <c r="K155" s="203"/>
+      <c r="L155" s="203"/>
+      <c r="M155" s="203"/>
+      <c r="N155" s="203"/>
+      <c r="O155" s="204"/>
+      <c r="P155" s="192" cm="1">
         <f t="array" ref="P155">SUMPRODUCT($D156:$O156, 2^(COLUMN($O156)-COLUMN($D156:$O156)))</f>
         <v>64</v>
       </c>
-      <c r="Q155" s="187" t="str">
+      <c r="Q155" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P155, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R155" s="183"/>
+      <c r="R155" s="178"/>
     </row>
     <row r="156" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A156" s="13"/>
-      <c r="B156" s="179"/>
-      <c r="C156" s="181"/>
+      <c r="B156" s="184"/>
+      <c r="C156" s="186"/>
       <c r="D156" s="12">
         <v>0</v>
       </c>
@@ -17956,16 +17956,16 @@
       <c r="O156" s="10">
         <v>0</v>
       </c>
-      <c r="P156" s="190"/>
-      <c r="Q156" s="188"/>
-      <c r="R156" s="184"/>
+      <c r="P156" s="193"/>
+      <c r="Q156" s="191"/>
+      <c r="R156" s="179"/>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A157" s="13"/>
-      <c r="B157" s="178" t="s">
+      <c r="B157" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="C157" s="180" t="s">
+      <c r="C157" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D157" s="15" t="s">
@@ -17983,29 +17983,29 @@
       <c r="H157" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I157" s="199" t="s">
+      <c r="I157" s="202" t="s">
         <v>19</v>
       </c>
-      <c r="J157" s="200"/>
-      <c r="K157" s="200"/>
-      <c r="L157" s="200"/>
-      <c r="M157" s="200"/>
-      <c r="N157" s="200"/>
-      <c r="O157" s="201"/>
-      <c r="P157" s="189" cm="1">
+      <c r="J157" s="203"/>
+      <c r="K157" s="203"/>
+      <c r="L157" s="203"/>
+      <c r="M157" s="203"/>
+      <c r="N157" s="203"/>
+      <c r="O157" s="204"/>
+      <c r="P157" s="192" cm="1">
         <f t="array" ref="P157">SUMPRODUCT($D158:$O158, 2^(COLUMN($O158)-COLUMN($D158:$O158)))</f>
         <v>64</v>
       </c>
-      <c r="Q157" s="187" t="str">
+      <c r="Q157" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P157, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R157" s="183"/>
+      <c r="R157" s="178"/>
     </row>
     <row r="158" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A158" s="13"/>
-      <c r="B158" s="179"/>
-      <c r="C158" s="181"/>
+      <c r="B158" s="184"/>
+      <c r="C158" s="186"/>
       <c r="D158" s="12">
         <v>0</v>
       </c>
@@ -18042,16 +18042,16 @@
       <c r="O158" s="10">
         <v>0</v>
       </c>
-      <c r="P158" s="190"/>
-      <c r="Q158" s="188"/>
-      <c r="R158" s="184"/>
+      <c r="P158" s="193"/>
+      <c r="Q158" s="191"/>
+      <c r="R158" s="179"/>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A159" s="13"/>
-      <c r="B159" s="178" t="s">
+      <c r="B159" s="183" t="s">
         <v>18</v>
       </c>
-      <c r="C159" s="180" t="s">
+      <c r="C159" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D159" s="15" t="s">
@@ -18069,29 +18069,29 @@
       <c r="H159" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I159" s="199" t="s">
+      <c r="I159" s="202" t="s">
         <v>17</v>
       </c>
-      <c r="J159" s="200"/>
-      <c r="K159" s="200"/>
-      <c r="L159" s="200"/>
-      <c r="M159" s="200"/>
-      <c r="N159" s="200"/>
-      <c r="O159" s="201"/>
-      <c r="P159" s="189" cm="1">
+      <c r="J159" s="203"/>
+      <c r="K159" s="203"/>
+      <c r="L159" s="203"/>
+      <c r="M159" s="203"/>
+      <c r="N159" s="203"/>
+      <c r="O159" s="204"/>
+      <c r="P159" s="192" cm="1">
         <f t="array" ref="P159">SUMPRODUCT($D160:$O160, 2^(COLUMN($O160)-COLUMN($D160:$O160)))</f>
         <v>64</v>
       </c>
-      <c r="Q159" s="187" t="str">
+      <c r="Q159" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P159, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R159" s="183"/>
+      <c r="R159" s="178"/>
     </row>
     <row r="160" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A160" s="13"/>
-      <c r="B160" s="179"/>
-      <c r="C160" s="181"/>
+      <c r="B160" s="184"/>
+      <c r="C160" s="186"/>
       <c r="D160" s="12">
         <v>0</v>
       </c>
@@ -18128,16 +18128,16 @@
       <c r="O160" s="10">
         <v>0</v>
       </c>
-      <c r="P160" s="190"/>
-      <c r="Q160" s="188"/>
-      <c r="R160" s="184"/>
+      <c r="P160" s="193"/>
+      <c r="Q160" s="191"/>
+      <c r="R160" s="179"/>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A161" s="13"/>
-      <c r="B161" s="178" t="s">
+      <c r="B161" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="C161" s="180" t="s">
+      <c r="C161" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D161" s="15" t="s">
@@ -18155,29 +18155,29 @@
       <c r="H161" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I161" s="199" t="s">
+      <c r="I161" s="202" t="s">
         <v>15</v>
       </c>
-      <c r="J161" s="200"/>
-      <c r="K161" s="200"/>
-      <c r="L161" s="200"/>
-      <c r="M161" s="200"/>
-      <c r="N161" s="200"/>
-      <c r="O161" s="201"/>
-      <c r="P161" s="189" cm="1">
+      <c r="J161" s="203"/>
+      <c r="K161" s="203"/>
+      <c r="L161" s="203"/>
+      <c r="M161" s="203"/>
+      <c r="N161" s="203"/>
+      <c r="O161" s="204"/>
+      <c r="P161" s="192" cm="1">
         <f t="array" ref="P161">SUMPRODUCT($D162:$O162, 2^(COLUMN($O162)-COLUMN($D162:$O162)))</f>
         <v>64</v>
       </c>
-      <c r="Q161" s="187" t="str">
+      <c r="Q161" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P161, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R161" s="183"/>
+      <c r="R161" s="178"/>
     </row>
     <row r="162" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A162" s="13"/>
-      <c r="B162" s="179"/>
-      <c r="C162" s="181"/>
+      <c r="B162" s="184"/>
+      <c r="C162" s="186"/>
       <c r="D162" s="12">
         <v>0</v>
       </c>
@@ -18214,16 +18214,16 @@
       <c r="O162" s="10">
         <v>0</v>
       </c>
-      <c r="P162" s="190"/>
-      <c r="Q162" s="188"/>
-      <c r="R162" s="184"/>
+      <c r="P162" s="193"/>
+      <c r="Q162" s="191"/>
+      <c r="R162" s="179"/>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A163" s="13"/>
-      <c r="B163" s="178" t="s">
+      <c r="B163" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="C163" s="180" t="s">
+      <c r="C163" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D163" s="15" t="s">
@@ -18241,29 +18241,29 @@
       <c r="H163" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I163" s="199" t="s">
+      <c r="I163" s="202" t="s">
         <v>13</v>
       </c>
-      <c r="J163" s="200"/>
-      <c r="K163" s="200"/>
-      <c r="L163" s="200"/>
-      <c r="M163" s="200"/>
-      <c r="N163" s="200"/>
-      <c r="O163" s="201"/>
-      <c r="P163" s="189" cm="1">
+      <c r="J163" s="203"/>
+      <c r="K163" s="203"/>
+      <c r="L163" s="203"/>
+      <c r="M163" s="203"/>
+      <c r="N163" s="203"/>
+      <c r="O163" s="204"/>
+      <c r="P163" s="192" cm="1">
         <f t="array" ref="P163">SUMPRODUCT($D164:$O164, 2^(COLUMN($O164)-COLUMN($D164:$O164)))</f>
         <v>64</v>
       </c>
-      <c r="Q163" s="187" t="str">
+      <c r="Q163" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P163, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R163" s="183"/>
+      <c r="R163" s="178"/>
     </row>
     <row r="164" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A164" s="13"/>
-      <c r="B164" s="179"/>
-      <c r="C164" s="181"/>
+      <c r="B164" s="184"/>
+      <c r="C164" s="186"/>
       <c r="D164" s="12">
         <v>0</v>
       </c>
@@ -18300,16 +18300,16 @@
       <c r="O164" s="10">
         <v>0</v>
       </c>
-      <c r="P164" s="190"/>
-      <c r="Q164" s="188"/>
-      <c r="R164" s="184"/>
+      <c r="P164" s="193"/>
+      <c r="Q164" s="191"/>
+      <c r="R164" s="179"/>
     </row>
     <row r="165" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A165" s="13"/>
-      <c r="B165" s="178" t="s">
+      <c r="B165" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="180" t="s">
+      <c r="C165" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D165" s="15" t="s">
@@ -18327,29 +18327,29 @@
       <c r="H165" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I165" s="199" t="s">
+      <c r="I165" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="J165" s="200"/>
-      <c r="K165" s="200"/>
-      <c r="L165" s="200"/>
-      <c r="M165" s="200"/>
-      <c r="N165" s="200"/>
-      <c r="O165" s="201"/>
-      <c r="P165" s="189" cm="1">
+      <c r="J165" s="203"/>
+      <c r="K165" s="203"/>
+      <c r="L165" s="203"/>
+      <c r="M165" s="203"/>
+      <c r="N165" s="203"/>
+      <c r="O165" s="204"/>
+      <c r="P165" s="192" cm="1">
         <f t="array" ref="P165">SUMPRODUCT($D166:$O166, 2^(COLUMN($O166)-COLUMN($D166:$O166)))</f>
         <v>64</v>
       </c>
-      <c r="Q165" s="187" t="str">
+      <c r="Q165" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P165, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R165" s="183"/>
+      <c r="R165" s="178"/>
     </row>
     <row r="166" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A166" s="13"/>
-      <c r="B166" s="179"/>
-      <c r="C166" s="181"/>
+      <c r="B166" s="184"/>
+      <c r="C166" s="186"/>
       <c r="D166" s="12">
         <v>0</v>
       </c>
@@ -18386,16 +18386,16 @@
       <c r="O166" s="10">
         <v>0</v>
       </c>
-      <c r="P166" s="190"/>
-      <c r="Q166" s="188"/>
-      <c r="R166" s="184"/>
+      <c r="P166" s="193"/>
+      <c r="Q166" s="191"/>
+      <c r="R166" s="179"/>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A167" s="13"/>
-      <c r="B167" s="178" t="s">
+      <c r="B167" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="C167" s="180" t="s">
+      <c r="C167" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D167" s="15" t="s">
@@ -18413,29 +18413,29 @@
       <c r="H167" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I167" s="199" t="s">
+      <c r="I167" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="J167" s="200"/>
-      <c r="K167" s="200"/>
-      <c r="L167" s="200"/>
-      <c r="M167" s="200"/>
-      <c r="N167" s="200"/>
-      <c r="O167" s="201"/>
-      <c r="P167" s="189" cm="1">
+      <c r="J167" s="203"/>
+      <c r="K167" s="203"/>
+      <c r="L167" s="203"/>
+      <c r="M167" s="203"/>
+      <c r="N167" s="203"/>
+      <c r="O167" s="204"/>
+      <c r="P167" s="192" cm="1">
         <f t="array" ref="P167">SUMPRODUCT($D168:$O168, 2^(COLUMN($O168)-COLUMN($D168:$O168)))</f>
         <v>64</v>
       </c>
-      <c r="Q167" s="187" t="str">
+      <c r="Q167" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P167, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R167" s="183"/>
+      <c r="R167" s="178"/>
     </row>
     <row r="168" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A168" s="13"/>
-      <c r="B168" s="179"/>
-      <c r="C168" s="181"/>
+      <c r="B168" s="184"/>
+      <c r="C168" s="186"/>
       <c r="D168" s="12">
         <v>0</v>
       </c>
@@ -18472,16 +18472,16 @@
       <c r="O168" s="10">
         <v>0</v>
       </c>
-      <c r="P168" s="190"/>
-      <c r="Q168" s="188"/>
-      <c r="R168" s="184"/>
+      <c r="P168" s="193"/>
+      <c r="Q168" s="191"/>
+      <c r="R168" s="179"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A169" s="13"/>
-      <c r="B169" s="178" t="s">
+      <c r="B169" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="C169" s="180" t="s">
+      <c r="C169" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D169" s="15" t="s">
@@ -18499,29 +18499,29 @@
       <c r="H169" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I169" s="199" t="s">
+      <c r="I169" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="J169" s="200"/>
-      <c r="K169" s="200"/>
-      <c r="L169" s="200"/>
-      <c r="M169" s="200"/>
-      <c r="N169" s="200"/>
-      <c r="O169" s="201"/>
-      <c r="P169" s="189" cm="1">
+      <c r="J169" s="203"/>
+      <c r="K169" s="203"/>
+      <c r="L169" s="203"/>
+      <c r="M169" s="203"/>
+      <c r="N169" s="203"/>
+      <c r="O169" s="204"/>
+      <c r="P169" s="192" cm="1">
         <f t="array" ref="P169">SUMPRODUCT($D170:$O170, 2^(COLUMN($O170)-COLUMN($D170:$O170)))</f>
         <v>64</v>
       </c>
-      <c r="Q169" s="187" t="str">
+      <c r="Q169" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P169, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R169" s="183"/>
+      <c r="R169" s="178"/>
     </row>
     <row r="170" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A170" s="13"/>
-      <c r="B170" s="179"/>
-      <c r="C170" s="181"/>
+      <c r="B170" s="184"/>
+      <c r="C170" s="186"/>
       <c r="D170" s="12">
         <v>0</v>
       </c>
@@ -18558,16 +18558,16 @@
       <c r="O170" s="10">
         <v>0</v>
       </c>
-      <c r="P170" s="190"/>
-      <c r="Q170" s="188"/>
-      <c r="R170" s="184"/>
+      <c r="P170" s="193"/>
+      <c r="Q170" s="191"/>
+      <c r="R170" s="179"/>
     </row>
     <row r="171" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A171" s="13"/>
-      <c r="B171" s="178" t="s">
+      <c r="B171" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C171" s="180" t="s">
+      <c r="C171" s="185" t="s">
         <v>5</v>
       </c>
       <c r="D171" s="15" t="s">
@@ -18585,29 +18585,29 @@
       <c r="H171" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I171" s="199" t="s">
+      <c r="I171" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="J171" s="200"/>
-      <c r="K171" s="200"/>
-      <c r="L171" s="200"/>
-      <c r="M171" s="200"/>
-      <c r="N171" s="200"/>
-      <c r="O171" s="201"/>
-      <c r="P171" s="189" cm="1">
+      <c r="J171" s="203"/>
+      <c r="K171" s="203"/>
+      <c r="L171" s="203"/>
+      <c r="M171" s="203"/>
+      <c r="N171" s="203"/>
+      <c r="O171" s="204"/>
+      <c r="P171" s="192" cm="1">
         <f t="array" ref="P171">SUMPRODUCT($D172:$O172, 2^(COLUMN($O172)-COLUMN($D172:$O172)))</f>
         <v>64</v>
       </c>
-      <c r="Q171" s="187" t="str">
+      <c r="Q171" s="190" t="str">
         <f>"0x"&amp;DEC2HEX($P171, 3)</f>
         <v>0x040</v>
       </c>
-      <c r="R171" s="183"/>
+      <c r="R171" s="178"/>
     </row>
     <row r="172" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A172" s="13"/>
-      <c r="B172" s="182"/>
-      <c r="C172" s="181"/>
+      <c r="B172" s="187"/>
+      <c r="C172" s="186"/>
       <c r="D172" s="12">
         <v>0</v>
       </c>
@@ -18644,9 +18644,9 @@
       <c r="O172" s="10">
         <v>0</v>
       </c>
-      <c r="P172" s="190"/>
-      <c r="Q172" s="188"/>
-      <c r="R172" s="184"/>
+      <c r="P172" s="193"/>
+      <c r="Q172" s="191"/>
+      <c r="R172" s="179"/>
     </row>
     <row r="173" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" s="9"/>
@@ -18668,24 +18668,22 @@
       <c r="G173" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H173" s="204" t="s">
-        <v>0</v>
-      </c>
-      <c r="I173" s="205"/>
-      <c r="J173" s="205"/>
-      <c r="K173" s="205"/>
-      <c r="L173" s="205"/>
-      <c r="M173" s="205"/>
-      <c r="N173" s="205"/>
-      <c r="O173" s="206"/>
+      <c r="H173" s="207" t="s">
+        <v>0</v>
+      </c>
+      <c r="I173" s="208"/>
+      <c r="J173" s="208"/>
+      <c r="K173" s="208"/>
+      <c r="L173" s="208"/>
+      <c r="M173" s="208"/>
+      <c r="N173" s="208"/>
+      <c r="O173" s="209"/>
       <c r="P173" s="4"/>
       <c r="Q173" s="3"/>
       <c r="R173" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="577">
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="D11:K11"/>
     <mergeCell ref="R165:R166"/>
     <mergeCell ref="R167:R168"/>
     <mergeCell ref="R169:R170"/>
@@ -18708,6 +18706,7 @@
     <mergeCell ref="R139:R140"/>
     <mergeCell ref="R141:R142"/>
     <mergeCell ref="R143:R144"/>
+    <mergeCell ref="A93:A94"/>
     <mergeCell ref="R145:R146"/>
     <mergeCell ref="R115:R116"/>
     <mergeCell ref="R75:R76"/>
@@ -18731,7 +18730,7 @@
     <mergeCell ref="R89:R90"/>
     <mergeCell ref="R91:R92"/>
     <mergeCell ref="R93:R94"/>
-    <mergeCell ref="R95:R96"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="R98:R99"/>
     <mergeCell ref="A97:R97"/>
     <mergeCell ref="Q93:Q94"/>
@@ -18741,8 +18740,20 @@
     <mergeCell ref="Q87:Q88"/>
     <mergeCell ref="I87:K87"/>
     <mergeCell ref="M87:O87"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="P98:P99"/>
+    <mergeCell ref="Q98:Q99"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:O95"/>
+    <mergeCell ref="P95:P96"/>
+    <mergeCell ref="Q95:Q96"/>
     <mergeCell ref="C100:C101"/>
     <mergeCell ref="K100:O100"/>
     <mergeCell ref="P100:P101"/>
@@ -18764,6 +18775,7 @@
     <mergeCell ref="R67:R68"/>
     <mergeCell ref="R69:R70"/>
     <mergeCell ref="R71:R72"/>
+    <mergeCell ref="R95:R96"/>
     <mergeCell ref="R33:R34"/>
     <mergeCell ref="R35:R36"/>
     <mergeCell ref="R37:R38"/>
@@ -18782,10 +18794,6 @@
     <mergeCell ref="R31:R32"/>
     <mergeCell ref="R17:R18"/>
     <mergeCell ref="R19:R20"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="Q9:Q10"/>
     <mergeCell ref="Q19:Q20"/>
@@ -18806,7 +18814,8 @@
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="D11:K11"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -18829,8 +18838,8 @@
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="Q15:Q16"/>
     <mergeCell ref="P13:P14"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
@@ -18839,6 +18848,9 @@
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="P21:P22"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q21:Q22"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
@@ -18855,6 +18867,10 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="P23:P24"/>
     <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="Q43:Q44"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:C28"/>
@@ -18874,6 +18890,13 @@
     <mergeCell ref="H29:K29"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="C31:C32"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="F49:J49"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="B45:B46"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="C33:C34"/>
@@ -18891,11 +18914,6 @@
     <mergeCell ref="Q37:Q38"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C39:C40"/>
@@ -18910,14 +18928,6 @@
     <mergeCell ref="K41:O41"/>
     <mergeCell ref="P41:P42"/>
     <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="P43:P44"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="F49:J49"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="B45:B46"/>
     <mergeCell ref="C45:C46"/>
     <mergeCell ref="F45:J45"/>
     <mergeCell ref="K45:O45"/>
@@ -18939,6 +18949,9 @@
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="Q49:Q50"/>
     <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="K43:O43"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="B63:B64"/>
     <mergeCell ref="C63:C64"/>
@@ -19051,21 +19064,6 @@
     <mergeCell ref="A91:A92"/>
     <mergeCell ref="B91:B92"/>
     <mergeCell ref="C91:C92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="P98:P99"/>
-    <mergeCell ref="Q98:Q99"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:O95"/>
-    <mergeCell ref="P95:P96"/>
-    <mergeCell ref="Q95:Q96"/>
-    <mergeCell ref="A93:A94"/>
     <mergeCell ref="B93:B94"/>
     <mergeCell ref="C93:C94"/>
     <mergeCell ref="C102:C103"/>
@@ -19088,6 +19086,8 @@
     <mergeCell ref="D104:O104"/>
     <mergeCell ref="A102:A103"/>
     <mergeCell ref="B102:B103"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
     <mergeCell ref="Q110:Q111"/>
     <mergeCell ref="A110:A111"/>
     <mergeCell ref="B110:B111"/>
@@ -19340,35 +19340,35 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="254" t="s">
+      <c r="A3" s="259" t="s">
         <v>376</v>
       </c>
-      <c r="B3" s="255"/>
-      <c r="C3" s="255"/>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="255"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
-      <c r="M3" s="255"/>
-      <c r="N3" s="255"/>
-      <c r="O3" s="255"/>
-      <c r="P3" s="255"/>
-      <c r="Q3" s="255"/>
-      <c r="R3" s="256"/>
+      <c r="B3" s="260"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="260"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="260"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="260"/>
+      <c r="L3" s="260"/>
+      <c r="M3" s="260"/>
+      <c r="N3" s="260"/>
+      <c r="O3" s="260"/>
+      <c r="P3" s="260"/>
+      <c r="Q3" s="260"/>
+      <c r="R3" s="261"/>
     </row>
     <row r="4" spans="1:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="242" t="s">
         <v>355</v>
       </c>
       <c r="D4" s="38" t="s">
@@ -19392,27 +19392,27 @@
       <c r="J4" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="219" t="s">
+      <c r="K4" s="222" t="s">
         <v>350</v>
       </c>
-      <c r="L4" s="219"/>
-      <c r="M4" s="219"/>
-      <c r="N4" s="219"/>
-      <c r="O4" s="217"/>
-      <c r="P4" s="215" cm="1">
+      <c r="L4" s="222"/>
+      <c r="M4" s="222"/>
+      <c r="N4" s="222"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="218" cm="1">
         <f t="array" ref="P4">SUMPRODUCT($D5:$O5, 2^(COLUMN($O5)-COLUMN($D5:$O5)))</f>
         <v>2048</v>
       </c>
-      <c r="Q4" s="249" t="str">
+      <c r="Q4" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P4, 3)</f>
         <v>0x800</v>
       </c>
-      <c r="R4" s="183"/>
+      <c r="R4" s="178"/>
     </row>
     <row r="5" spans="1:18" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="240"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="181"/>
+      <c r="A5" s="241"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="186"/>
       <c r="D5" s="75">
         <v>1</v>
       </c>
@@ -19449,31 +19449,31 @@
       <c r="O5" s="53">
         <v>0</v>
       </c>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="250"/>
-      <c r="R5" s="184"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="255"/>
+      <c r="R5" s="179"/>
     </row>
     <row r="6" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="208" t="s">
+      <c r="A6" s="211" t="s">
         <v>321</v>
       </c>
-      <c r="B6" s="210" t="s">
+      <c r="B6" s="213" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="180" t="s">
+      <c r="C6" s="185" t="s">
         <v>320</v>
       </c>
       <c r="D6" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="217" t="s">
+      <c r="E6" s="220" t="s">
         <v>319</v>
       </c>
-      <c r="F6" s="222"/>
-      <c r="G6" s="217" t="s">
+      <c r="F6" s="231"/>
+      <c r="G6" s="220" t="s">
         <v>318</v>
       </c>
-      <c r="H6" s="222"/>
+      <c r="H6" s="231"/>
       <c r="I6" s="32" t="s">
         <v>317</v>
       </c>
@@ -19495,20 +19495,20 @@
       <c r="O6" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="P6" s="189" cm="1">
+      <c r="P6" s="192" cm="1">
         <f t="array" ref="P6">SUMPRODUCT($D7:$O7, 2^(COLUMN($O7)-COLUMN($D7:$O7)))</f>
         <v>255</v>
       </c>
-      <c r="Q6" s="257" t="str">
+      <c r="Q6" s="262" t="str">
         <f>"0x"&amp;DEC2HEX($P6, 3)</f>
         <v>0x0FF</v>
       </c>
-      <c r="R6" s="183"/>
+      <c r="R6" s="178"/>
     </row>
     <row r="7" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="209"/>
-      <c r="B7" s="211"/>
-      <c r="C7" s="181"/>
+      <c r="A7" s="212"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="186"/>
       <c r="D7" s="59">
         <v>0</v>
       </c>
@@ -19545,18 +19545,18 @@
       <c r="O7" s="90">
         <v>1</v>
       </c>
-      <c r="P7" s="190"/>
-      <c r="Q7" s="258"/>
-      <c r="R7" s="184"/>
+      <c r="P7" s="193"/>
+      <c r="Q7" s="263"/>
+      <c r="R7" s="179"/>
     </row>
     <row r="8" spans="1:18" ht="39" x14ac:dyDescent="0.45">
-      <c r="A8" s="208" t="s">
+      <c r="A8" s="211" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="210" t="s">
+      <c r="B8" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="256" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="39" t="s">
@@ -19565,10 +19565,10 @@
       <c r="E8" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="F8" s="217" t="s">
+      <c r="F8" s="220" t="s">
         <v>211</v>
       </c>
-      <c r="G8" s="222"/>
+      <c r="G8" s="231"/>
       <c r="H8" s="32" t="s">
         <v>210</v>
       </c>
@@ -19593,20 +19593,20 @@
       <c r="O8" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="P8" s="189" cm="1">
+      <c r="P8" s="192" cm="1">
         <f t="array" ref="P8">SUMPRODUCT($D9:$O9, 2^(COLUMN($O9)-COLUMN($D9:$O9)))</f>
         <v>4095</v>
       </c>
-      <c r="Q8" s="259" t="str">
+      <c r="Q8" s="264" t="str">
         <f>"0x"&amp;DEC2HEX($P8, 3)</f>
         <v>0xFFF</v>
       </c>
-      <c r="R8" s="183"/>
+      <c r="R8" s="178"/>
     </row>
     <row r="9" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="209"/>
-      <c r="B9" s="211"/>
-      <c r="C9" s="252"/>
+      <c r="A9" s="212"/>
+      <c r="B9" s="214"/>
+      <c r="C9" s="257"/>
       <c r="D9" s="68">
         <v>1</v>
       </c>
@@ -19643,48 +19643,48 @@
       <c r="O9" s="92">
         <v>1</v>
       </c>
-      <c r="P9" s="190"/>
-      <c r="Q9" s="260"/>
-      <c r="R9" s="184"/>
+      <c r="P9" s="193"/>
+      <c r="Q9" s="265"/>
+      <c r="R9" s="179"/>
     </row>
     <row r="10" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="228" t="s">
+      <c r="A10" s="182" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="210" t="s">
+      <c r="B10" s="213" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="180" t="s">
+      <c r="C10" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="212" t="s">
+      <c r="D10" s="215" t="s">
         <v>171</v>
       </c>
-      <c r="E10" s="213"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="213"/>
-      <c r="I10" s="213"/>
-      <c r="J10" s="213"/>
-      <c r="K10" s="213"/>
-      <c r="L10" s="213"/>
-      <c r="M10" s="213"/>
-      <c r="N10" s="213"/>
-      <c r="O10" s="214"/>
-      <c r="P10" s="189" cm="1">
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="216"/>
+      <c r="I10" s="216"/>
+      <c r="J10" s="216"/>
+      <c r="K10" s="216"/>
+      <c r="L10" s="216"/>
+      <c r="M10" s="216"/>
+      <c r="N10" s="216"/>
+      <c r="O10" s="217"/>
+      <c r="P10" s="192" cm="1">
         <f t="array" ref="P10">SUMPRODUCT($D11:$O11, 2^(COLUMN($O11)-COLUMN($D11:$O11)))</f>
         <v>3533</v>
       </c>
-      <c r="Q10" s="249" t="str">
+      <c r="Q10" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P10, 3)</f>
         <v>0xDCD</v>
       </c>
-      <c r="R10" s="183"/>
+      <c r="R10" s="178"/>
     </row>
     <row r="11" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="229"/>
-      <c r="B11" s="211"/>
-      <c r="C11" s="181"/>
+      <c r="A11" s="181"/>
+      <c r="B11" s="214"/>
+      <c r="C11" s="186"/>
       <c r="D11" s="74">
         <v>1</v>
       </c>
@@ -19721,18 +19721,18 @@
       <c r="O11" s="72">
         <v>1</v>
       </c>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="250"/>
-      <c r="R11" s="184"/>
+      <c r="P11" s="193"/>
+      <c r="Q11" s="255"/>
+      <c r="R11" s="179"/>
     </row>
     <row r="12" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A12" s="208" t="s">
+      <c r="A12" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="210" t="s">
+      <c r="B12" s="213" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="180" t="s">
+      <c r="C12" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="41" t="s">
@@ -19771,20 +19771,20 @@
       <c r="O12" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="P12" s="189" cm="1">
+      <c r="P12" s="192" cm="1">
         <f t="array" ref="P12">SUMPRODUCT($D13:$O13, 2^(COLUMN($O13)-COLUMN($D13:$O13)))</f>
         <v>63</v>
       </c>
-      <c r="Q12" s="249" t="str">
+      <c r="Q12" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P12, 3)</f>
         <v>0x03F</v>
       </c>
-      <c r="R12" s="183"/>
+      <c r="R12" s="178"/>
     </row>
     <row r="13" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="209"/>
-      <c r="B13" s="211"/>
-      <c r="C13" s="181"/>
+      <c r="A13" s="212"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="186"/>
       <c r="D13" s="59">
         <v>0</v>
       </c>
@@ -19821,18 +19821,18 @@
       <c r="O13" s="72">
         <v>1</v>
       </c>
-      <c r="P13" s="190"/>
-      <c r="Q13" s="250"/>
-      <c r="R13" s="184"/>
+      <c r="P13" s="193"/>
+      <c r="Q13" s="255"/>
+      <c r="R13" s="179"/>
     </row>
     <row r="14" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A14" s="223" t="s">
+      <c r="A14" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="224" t="s">
+      <c r="B14" s="247" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="253" t="s">
+      <c r="C14" s="258" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="39" t="s">
@@ -19847,10 +19847,10 @@
       <c r="G14" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="217" t="s">
+      <c r="H14" s="220" t="s">
         <v>103</v>
       </c>
-      <c r="I14" s="222"/>
+      <c r="I14" s="231"/>
       <c r="J14" s="32" t="s">
         <v>102</v>
       </c>
@@ -19869,20 +19869,20 @@
       <c r="O14" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="P14" s="189" cm="1">
+      <c r="P14" s="192" cm="1">
         <f t="array" ref="P14">SUMPRODUCT($D15:$O15, 2^(COLUMN($O15)-COLUMN($D15:$O15)))</f>
         <v>2148</v>
       </c>
-      <c r="Q14" s="249" t="str">
+      <c r="Q14" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P14, 3)</f>
         <v>0x864</v>
       </c>
-      <c r="R14" s="183"/>
+      <c r="R14" s="178"/>
     </row>
     <row r="15" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="209"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="252"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="257"/>
       <c r="D15" s="68">
         <v>1</v>
       </c>
@@ -19919,48 +19919,48 @@
       <c r="O15" s="29">
         <v>0</v>
       </c>
-      <c r="P15" s="190"/>
-      <c r="Q15" s="250"/>
-      <c r="R15" s="184"/>
+      <c r="P15" s="193"/>
+      <c r="Q15" s="255"/>
+      <c r="R15" s="179"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A16" s="208" t="s">
+      <c r="A16" s="211" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="210" t="s">
+      <c r="B16" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="180" t="s">
+      <c r="C16" s="185" t="s">
         <v>506</v>
       </c>
-      <c r="D16" s="212" t="s">
+      <c r="D16" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="213"/>
-      <c r="F16" s="213"/>
-      <c r="G16" s="213"/>
-      <c r="H16" s="213"/>
-      <c r="I16" s="213"/>
-      <c r="J16" s="213"/>
-      <c r="K16" s="213"/>
-      <c r="L16" s="213"/>
-      <c r="M16" s="213"/>
-      <c r="N16" s="213"/>
-      <c r="O16" s="214"/>
-      <c r="P16" s="215" cm="1">
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="216"/>
+      <c r="J16" s="216"/>
+      <c r="K16" s="216"/>
+      <c r="L16" s="216"/>
+      <c r="M16" s="216"/>
+      <c r="N16" s="216"/>
+      <c r="O16" s="217"/>
+      <c r="P16" s="218" cm="1">
         <f t="array" ref="P16">SUMPRODUCT($D17:$O17, 2^(COLUMN($O17)-COLUMN($D17:$O17)))</f>
         <v>2650</v>
       </c>
-      <c r="Q16" s="257" t="str">
+      <c r="Q16" s="262" t="str">
         <f>"0x"&amp;DEC2HEX($P16, 3)</f>
         <v>0xA5A</v>
       </c>
-      <c r="R16" s="183"/>
+      <c r="R16" s="178"/>
     </row>
     <row r="17" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="209"/>
-      <c r="B17" s="211"/>
-      <c r="C17" s="181"/>
+      <c r="A17" s="212"/>
+      <c r="B17" s="214"/>
+      <c r="C17" s="186"/>
       <c r="D17" s="20">
         <v>1</v>
       </c>
@@ -19997,41 +19997,41 @@
       <c r="O17" s="29">
         <v>0</v>
       </c>
-      <c r="P17" s="216"/>
-      <c r="Q17" s="258"/>
-      <c r="R17" s="184"/>
+      <c r="P17" s="219"/>
+      <c r="Q17" s="263"/>
+      <c r="R17" s="179"/>
     </row>
     <row r="19" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="20" spans="1:18" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="254" t="s">
+      <c r="A20" s="259" t="s">
         <v>459</v>
       </c>
-      <c r="B20" s="255"/>
-      <c r="C20" s="255"/>
-      <c r="D20" s="255"/>
-      <c r="E20" s="255"/>
-      <c r="F20" s="255"/>
-      <c r="G20" s="255"/>
-      <c r="H20" s="255"/>
-      <c r="I20" s="255"/>
-      <c r="J20" s="255"/>
-      <c r="K20" s="255"/>
-      <c r="L20" s="255"/>
-      <c r="M20" s="255"/>
-      <c r="N20" s="255"/>
-      <c r="O20" s="255"/>
-      <c r="P20" s="255"/>
-      <c r="Q20" s="255"/>
-      <c r="R20" s="256"/>
+      <c r="B20" s="260"/>
+      <c r="C20" s="260"/>
+      <c r="D20" s="260"/>
+      <c r="E20" s="260"/>
+      <c r="F20" s="260"/>
+      <c r="G20" s="260"/>
+      <c r="H20" s="260"/>
+      <c r="I20" s="260"/>
+      <c r="J20" s="260"/>
+      <c r="K20" s="260"/>
+      <c r="L20" s="260"/>
+      <c r="M20" s="260"/>
+      <c r="N20" s="260"/>
+      <c r="O20" s="260"/>
+      <c r="P20" s="260"/>
+      <c r="Q20" s="260"/>
+      <c r="R20" s="261"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A21" s="208" t="s">
+      <c r="A21" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="B21" s="210" t="s">
+      <c r="B21" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="241" t="s">
+      <c r="C21" s="242" t="s">
         <v>355</v>
       </c>
       <c r="D21" s="38" t="s">
@@ -20055,27 +20055,27 @@
       <c r="J21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K21" s="219" t="s">
+      <c r="K21" s="222" t="s">
         <v>350</v>
       </c>
-      <c r="L21" s="219"/>
-      <c r="M21" s="219"/>
-      <c r="N21" s="219"/>
-      <c r="O21" s="217"/>
-      <c r="P21" s="215" cm="1">
+      <c r="L21" s="222"/>
+      <c r="M21" s="222"/>
+      <c r="N21" s="222"/>
+      <c r="O21" s="220"/>
+      <c r="P21" s="218" cm="1">
         <f t="array" ref="P21">SUMPRODUCT($D22:$O22, 2^(COLUMN($O22)-COLUMN($D22:$O22)))</f>
         <v>2048</v>
       </c>
-      <c r="Q21" s="249" t="str">
+      <c r="Q21" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P21, 3)</f>
         <v>0x800</v>
       </c>
-      <c r="R21" s="183"/>
+      <c r="R21" s="178"/>
     </row>
     <row r="22" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="240"/>
-      <c r="B22" s="211"/>
-      <c r="C22" s="181"/>
+      <c r="A22" s="241"/>
+      <c r="B22" s="214"/>
+      <c r="C22" s="186"/>
       <c r="D22" s="75">
         <v>1</v>
       </c>
@@ -20112,18 +20112,18 @@
       <c r="O22" s="53">
         <v>0</v>
       </c>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="250"/>
-      <c r="R22" s="184"/>
+      <c r="P22" s="219"/>
+      <c r="Q22" s="255"/>
+      <c r="R22" s="179"/>
     </row>
     <row r="23" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A23" s="208" t="s">
+      <c r="A23" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="210" t="s">
+      <c r="B23" s="213" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="180" t="s">
+      <c r="C23" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -20162,20 +20162,20 @@
       <c r="O23" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="P23" s="189" cm="1">
+      <c r="P23" s="192" cm="1">
         <f t="array" ref="P23">SUMPRODUCT($D24:$O24, 2^(COLUMN($O24)-COLUMN($D24:$O24)))</f>
         <v>63</v>
       </c>
-      <c r="Q23" s="249" t="str">
+      <c r="Q23" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P23, 3)</f>
         <v>0x03F</v>
       </c>
-      <c r="R23" s="183"/>
+      <c r="R23" s="178"/>
     </row>
     <row r="24" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="209"/>
-      <c r="B24" s="211"/>
-      <c r="C24" s="181"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="214"/>
+      <c r="C24" s="186"/>
       <c r="D24" s="40">
         <v>0</v>
       </c>
@@ -20212,18 +20212,18 @@
       <c r="O24" s="70">
         <v>1</v>
       </c>
-      <c r="P24" s="190"/>
-      <c r="Q24" s="250"/>
-      <c r="R24" s="184"/>
+      <c r="P24" s="193"/>
+      <c r="Q24" s="255"/>
+      <c r="R24" s="179"/>
     </row>
     <row r="25" spans="1:18" ht="26" x14ac:dyDescent="0.45">
       <c r="A25" s="230" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="210" t="s">
+      <c r="B25" s="213" t="s">
         <v>132</v>
       </c>
-      <c r="C25" s="251" t="s">
+      <c r="C25" s="256" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="69" t="s">
@@ -20244,30 +20244,30 @@
       <c r="I25" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J25" s="217" t="s">
+      <c r="J25" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="K25" s="222"/>
-      <c r="L25" s="217" t="s">
+      <c r="K25" s="231"/>
+      <c r="L25" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="M25" s="213"/>
-      <c r="N25" s="213"/>
-      <c r="O25" s="214"/>
-      <c r="P25" s="189" cm="1">
+      <c r="M25" s="216"/>
+      <c r="N25" s="216"/>
+      <c r="O25" s="217"/>
+      <c r="P25" s="192" cm="1">
         <f t="array" ref="P25">SUMPRODUCT($D26:$O26, 2^(COLUMN($O26)-COLUMN($D26:$O26)))</f>
         <v>8</v>
       </c>
-      <c r="Q25" s="249" t="str">
+      <c r="Q25" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P25, 3)</f>
         <v>0x008</v>
       </c>
-      <c r="R25" s="183"/>
+      <c r="R25" s="178"/>
     </row>
     <row r="26" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="229"/>
-      <c r="B26" s="211"/>
-      <c r="C26" s="252"/>
+      <c r="A26" s="181"/>
+      <c r="B26" s="214"/>
+      <c r="C26" s="257"/>
       <c r="D26" s="68">
         <v>0</v>
       </c>
@@ -20304,18 +20304,18 @@
       <c r="O26" s="29">
         <v>0</v>
       </c>
-      <c r="P26" s="190"/>
-      <c r="Q26" s="250"/>
-      <c r="R26" s="184"/>
+      <c r="P26" s="193"/>
+      <c r="Q26" s="255"/>
+      <c r="R26" s="179"/>
     </row>
     <row r="27" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A27" s="223" t="s">
+      <c r="A27" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="224" t="s">
+      <c r="B27" s="247" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="253" t="s">
+      <c r="C27" s="258" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="39" t="s">
@@ -20330,10 +20330,10 @@
       <c r="G27" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H27" s="217" t="s">
+      <c r="H27" s="220" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="222"/>
+      <c r="I27" s="231"/>
       <c r="J27" s="32" t="s">
         <v>102</v>
       </c>
@@ -20352,20 +20352,20 @@
       <c r="O27" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="P27" s="189" cm="1">
+      <c r="P27" s="192" cm="1">
         <f t="array" ref="P27">SUMPRODUCT($D28:$O28, 2^(COLUMN($O28)-COLUMN($D28:$O28)))</f>
         <v>2164</v>
       </c>
-      <c r="Q27" s="249" t="str">
+      <c r="Q27" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P27, 3)</f>
         <v>0x874</v>
       </c>
-      <c r="R27" s="183"/>
+      <c r="R27" s="178"/>
     </row>
     <row r="28" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="209"/>
-      <c r="B28" s="211"/>
-      <c r="C28" s="252"/>
+      <c r="A28" s="212"/>
+      <c r="B28" s="214"/>
+      <c r="C28" s="257"/>
       <c r="D28" s="68">
         <v>1</v>
       </c>
@@ -20402,48 +20402,48 @@
       <c r="O28" s="29">
         <v>0</v>
       </c>
-      <c r="P28" s="190"/>
-      <c r="Q28" s="250"/>
-      <c r="R28" s="184"/>
+      <c r="P28" s="193"/>
+      <c r="Q28" s="255"/>
+      <c r="R28" s="179"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A29" s="208" t="s">
+      <c r="A29" s="211" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="210" t="s">
+      <c r="B29" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="180" t="s">
+      <c r="C29" s="185" t="s">
         <v>506</v>
       </c>
-      <c r="D29" s="212" t="s">
+      <c r="D29" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="213"/>
-      <c r="F29" s="213"/>
-      <c r="G29" s="213"/>
-      <c r="H29" s="213"/>
-      <c r="I29" s="213"/>
-      <c r="J29" s="213"/>
-      <c r="K29" s="213"/>
-      <c r="L29" s="213"/>
-      <c r="M29" s="213"/>
-      <c r="N29" s="213"/>
-      <c r="O29" s="214"/>
-      <c r="P29" s="215" cm="1">
+      <c r="E29" s="216"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="216"/>
+      <c r="H29" s="216"/>
+      <c r="I29" s="216"/>
+      <c r="J29" s="216"/>
+      <c r="K29" s="216"/>
+      <c r="L29" s="216"/>
+      <c r="M29" s="216"/>
+      <c r="N29" s="216"/>
+      <c r="O29" s="217"/>
+      <c r="P29" s="218" cm="1">
         <f t="array" ref="P29">SUMPRODUCT($D30:$O30, 2^(COLUMN($O30)-COLUMN($D30:$O30)))</f>
         <v>2650</v>
       </c>
-      <c r="Q29" s="257" t="str">
+      <c r="Q29" s="262" t="str">
         <f>"0x"&amp;DEC2HEX($P29, 3)</f>
         <v>0xA5A</v>
       </c>
-      <c r="R29" s="183"/>
+      <c r="R29" s="178"/>
     </row>
     <row r="30" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="209"/>
-      <c r="B30" s="211"/>
-      <c r="C30" s="181"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="214"/>
+      <c r="C30" s="186"/>
       <c r="D30" s="20">
         <v>1</v>
       </c>
@@ -20480,41 +20480,41 @@
       <c r="O30" s="29">
         <v>0</v>
       </c>
-      <c r="P30" s="216"/>
-      <c r="Q30" s="258"/>
-      <c r="R30" s="184"/>
+      <c r="P30" s="219"/>
+      <c r="Q30" s="263"/>
+      <c r="R30" s="179"/>
     </row>
     <row r="32" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="33" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="254" t="s">
+      <c r="A33" s="259" t="s">
         <v>458</v>
       </c>
-      <c r="B33" s="255"/>
-      <c r="C33" s="255"/>
-      <c r="D33" s="255"/>
-      <c r="E33" s="255"/>
-      <c r="F33" s="255"/>
-      <c r="G33" s="255"/>
-      <c r="H33" s="255"/>
-      <c r="I33" s="255"/>
-      <c r="J33" s="255"/>
-      <c r="K33" s="255"/>
-      <c r="L33" s="255"/>
-      <c r="M33" s="255"/>
-      <c r="N33" s="255"/>
-      <c r="O33" s="255"/>
-      <c r="P33" s="255"/>
-      <c r="Q33" s="255"/>
-      <c r="R33" s="256"/>
+      <c r="B33" s="260"/>
+      <c r="C33" s="260"/>
+      <c r="D33" s="260"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="260"/>
+      <c r="G33" s="260"/>
+      <c r="H33" s="260"/>
+      <c r="I33" s="260"/>
+      <c r="J33" s="260"/>
+      <c r="K33" s="260"/>
+      <c r="L33" s="260"/>
+      <c r="M33" s="260"/>
+      <c r="N33" s="260"/>
+      <c r="O33" s="260"/>
+      <c r="P33" s="260"/>
+      <c r="Q33" s="260"/>
+      <c r="R33" s="261"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A34" s="208" t="s">
+      <c r="A34" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="B34" s="210" t="s">
+      <c r="B34" s="213" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="241" t="s">
+      <c r="C34" s="242" t="s">
         <v>355</v>
       </c>
       <c r="D34" s="38" t="s">
@@ -20538,27 +20538,27 @@
       <c r="J34" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="K34" s="219" t="s">
+      <c r="K34" s="222" t="s">
         <v>350</v>
       </c>
-      <c r="L34" s="219"/>
-      <c r="M34" s="219"/>
-      <c r="N34" s="219"/>
-      <c r="O34" s="217"/>
-      <c r="P34" s="215" cm="1">
+      <c r="L34" s="222"/>
+      <c r="M34" s="222"/>
+      <c r="N34" s="222"/>
+      <c r="O34" s="220"/>
+      <c r="P34" s="218" cm="1">
         <f t="array" ref="P34">SUMPRODUCT($D35:$O35, 2^(COLUMN($O35)-COLUMN($D35:$O35)))</f>
         <v>2048</v>
       </c>
-      <c r="Q34" s="249" t="str">
+      <c r="Q34" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P34, 3)</f>
         <v>0x800</v>
       </c>
-      <c r="R34" s="183"/>
+      <c r="R34" s="178"/>
     </row>
     <row r="35" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="240"/>
-      <c r="B35" s="211"/>
-      <c r="C35" s="181"/>
+      <c r="A35" s="241"/>
+      <c r="B35" s="214"/>
+      <c r="C35" s="186"/>
       <c r="D35" s="75">
         <v>1</v>
       </c>
@@ -20595,18 +20595,18 @@
       <c r="O35" s="53">
         <v>0</v>
       </c>
-      <c r="P35" s="216"/>
-      <c r="Q35" s="250"/>
-      <c r="R35" s="184"/>
+      <c r="P35" s="219"/>
+      <c r="Q35" s="255"/>
+      <c r="R35" s="179"/>
     </row>
     <row r="36" spans="1:18" ht="26" x14ac:dyDescent="0.45">
-      <c r="A36" s="208" t="s">
+      <c r="A36" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="210" t="s">
+      <c r="B36" s="213" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="180" t="s">
+      <c r="C36" s="185" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="41" t="s">
@@ -20645,20 +20645,20 @@
       <c r="O36" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="P36" s="189" cm="1">
+      <c r="P36" s="192" cm="1">
         <f t="array" ref="P36">SUMPRODUCT($D37:$O37, 2^(COLUMN($O37)-COLUMN($D37:$O37)))</f>
         <v>63</v>
       </c>
-      <c r="Q36" s="249" t="str">
+      <c r="Q36" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P36, 3)</f>
         <v>0x03F</v>
       </c>
-      <c r="R36" s="183"/>
+      <c r="R36" s="178"/>
     </row>
     <row r="37" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="209"/>
-      <c r="B37" s="211"/>
-      <c r="C37" s="181"/>
+      <c r="A37" s="212"/>
+      <c r="B37" s="214"/>
+      <c r="C37" s="186"/>
       <c r="D37" s="40">
         <v>0</v>
       </c>
@@ -20695,18 +20695,18 @@
       <c r="O37" s="70">
         <v>1</v>
       </c>
-      <c r="P37" s="190"/>
-      <c r="Q37" s="250"/>
-      <c r="R37" s="184"/>
+      <c r="P37" s="193"/>
+      <c r="Q37" s="255"/>
+      <c r="R37" s="179"/>
     </row>
     <row r="38" spans="1:18" ht="26" x14ac:dyDescent="0.45">
       <c r="A38" s="230" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="210" t="s">
+      <c r="B38" s="213" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="251" t="s">
+      <c r="C38" s="256" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="69" t="s">
@@ -20727,30 +20727,30 @@
       <c r="I38" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="J38" s="217" t="s">
+      <c r="J38" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="K38" s="222"/>
-      <c r="L38" s="217" t="s">
+      <c r="K38" s="231"/>
+      <c r="L38" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="M38" s="213"/>
-      <c r="N38" s="213"/>
-      <c r="O38" s="214"/>
-      <c r="P38" s="189" cm="1">
+      <c r="M38" s="216"/>
+      <c r="N38" s="216"/>
+      <c r="O38" s="217"/>
+      <c r="P38" s="192" cm="1">
         <f t="array" ref="P38">SUMPRODUCT($D39:$O39, 2^(COLUMN($O39)-COLUMN($D39:$O39)))</f>
         <v>8</v>
       </c>
-      <c r="Q38" s="249" t="str">
+      <c r="Q38" s="254" t="str">
         <f>"0x"&amp;DEC2HEX($P38, 3)</f>
         <v>0x008</v>
       </c>
-      <c r="R38" s="183"/>
+      <c r="R38" s="178"/>
     </row>
     <row r="39" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="229"/>
-      <c r="B39" s="211"/>
-      <c r="C39" s="252"/>
+      <c r="A39" s="181"/>
+      <c r="B39" s="214"/>
+      <c r="C39" s="257"/>
       <c r="D39" s="68">
         <v>0</v>
       </c>
@@ -20787,9 +20787,9 @@
       <c r="O39" s="29">
         <v>0</v>
       </c>
-      <c r="P39" s="190"/>
-      <c r="Q39" s="250"/>
-      <c r="R39" s="184"/>
+      <c r="P39" s="193"/>
+      <c r="Q39" s="255"/>
+      <c r="R39" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="108">
@@ -21660,13 +21660,13 @@
         <v>476</v>
       </c>
       <c r="Z3" s="99"/>
-      <c r="AA3" s="261" t="s">
+      <c r="AA3" s="266" t="s">
         <v>477</v>
       </c>
-      <c r="AB3" s="261"/>
-      <c r="AC3" s="261"/>
-      <c r="AD3" s="261"/>
-      <c r="AE3" s="261"/>
+      <c r="AB3" s="266"/>
+      <c r="AC3" s="266"/>
+      <c r="AD3" s="266"/>
+      <c r="AE3" s="266"/>
       <c r="AF3" s="105"/>
       <c r="AG3" s="102"/>
       <c r="AH3" s="105"/>
@@ -33453,14 +33453,14 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="265" t="s">
+      <c r="B5" s="270" t="s">
         <v>508</v>
       </c>
-      <c r="C5" s="265"/>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
+      <c r="C5" s="270"/>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B6" s="175" t="s">
@@ -33525,7 +33525,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C9, 3))</f>
         <v>0xB0B</v>
       </c>
-      <c r="G9" s="262" t="s">
+      <c r="G9" s="267" t="s">
         <v>358</v>
       </c>
     </row>
@@ -33547,7 +33547,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C10, 3))</f>
         <v>0x028</v>
       </c>
-      <c r="G10" s="263"/>
+      <c r="G10" s="268"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.45">
       <c r="E11" s="176" t="s">
@@ -33557,17 +33557,17 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(_xlfn.BITOR(_xlfn.BITOR(_xlfn.BITLSHIFT($C$2,11),_xlfn.BITLSHIFT($C$3,9)),C10)))</f>
         <v>0xC28</v>
       </c>
-      <c r="G11" s="264"/>
+      <c r="G11" s="269"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B15" s="265" t="s">
+      <c r="B15" s="270" t="s">
         <v>521</v>
       </c>
-      <c r="C15" s="265"/>
-      <c r="D15" s="265"/>
-      <c r="E15" s="265"/>
-      <c r="F15" s="265"/>
-      <c r="G15" s="265"/>
+      <c r="C15" s="270"/>
+      <c r="D15" s="270"/>
+      <c r="E15" s="270"/>
+      <c r="F15" s="270"/>
+      <c r="G15" s="270"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B16" s="175" t="s">
@@ -33632,7 +33632,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C19, 3))</f>
         <v>0xDCD</v>
       </c>
-      <c r="G19" s="262" t="s">
+      <c r="G19" s="267" t="s">
         <v>358</v>
       </c>
     </row>
@@ -33654,7 +33654,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C20, 3))</f>
         <v>0x032</v>
       </c>
-      <c r="G20" s="263"/>
+      <c r="G20" s="268"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="E21" s="176" t="s">
@@ -33664,17 +33664,17 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(_xlfn.BITOR(_xlfn.BITOR(_xlfn.BITLSHIFT($C$2,11),_xlfn.BITLSHIFT($C$3,9)),C20)))</f>
         <v>0xC32</v>
       </c>
-      <c r="G21" s="264"/>
+      <c r="G21" s="269"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B25" s="265" t="s">
+      <c r="B25" s="270" t="s">
         <v>522</v>
       </c>
-      <c r="C25" s="265"/>
-      <c r="D25" s="265"/>
-      <c r="E25" s="265"/>
-      <c r="F25" s="265"/>
-      <c r="G25" s="265"/>
+      <c r="C25" s="270"/>
+      <c r="D25" s="270"/>
+      <c r="E25" s="270"/>
+      <c r="F25" s="270"/>
+      <c r="G25" s="270"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" s="175" t="s">
@@ -33739,7 +33739,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C29, 3))</f>
         <v>0x090</v>
       </c>
-      <c r="G29" s="262" t="s">
+      <c r="G29" s="267" t="s">
         <v>358</v>
       </c>
     </row>
@@ -33761,7 +33761,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(C30, 3))</f>
         <v>0x03D</v>
       </c>
-      <c r="G30" s="263"/>
+      <c r="G30" s="268"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.45">
       <c r="E31" s="176" t="s">
@@ -33771,7 +33771,7 @@
         <f>_xlfn.CONCAT("0x", DEC2HEX(_xlfn.BITOR(_xlfn.BITOR(_xlfn.BITLSHIFT($C$2,11),_xlfn.BITLSHIFT($C$3,9)),C30)))</f>
         <v>0xC3D</v>
       </c>
-      <c r="G31" s="264"/>
+      <c r="G31" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="6">
